--- a/begrippen-nlsbb.xlsx
+++ b/begrippen-nlsbb.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\apps\github\IMProRail\spoorse-begrippen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E0F50C3-853E-4D4A-832A-68632937115F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A4D7E21-B64F-4800-9207-D52B07767D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-3255" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{647FEE87-BCEB-4E3A-ABA6-7EA97748041A}"/>
   </bookViews>
@@ -7055,21 +7055,6 @@
   </si>
   <si>
     <t xml:space="preserve">Zie ook: https://otl.prorail.nl/otl/vigerend/Bevloering </t>
-  </si>
-  <si>
-    <t>Er zijn twee soorten bewegingen:
-•	trein;
-•	rangeerbeweging.
-Toelichting
-Van Dale:
-1.	Het bewegen, zich verplaatsen 
-2.	Groep die naar iets streeft, zich ergens voor inzet 
-3.	Drukte, vertier
-Definitie in lijn met 1, maar met voorkeur voor 3.
-Binnen de keten van het vervoersproces heeft een beweging verschillende opeenvolgende voorkomens of statussen:
-•	In eerste instantie een administratief bestaan, nog ontkoppeld van het fysieke materieel dat erbij betrokken is: dus alleen de modelmatige afbeelding van de verplaatsing over de railinfrastruc-tuur en de materieeleenheden slechts o.b.v. een soortaanduiding;
-•	Daarna een administratief bestaan, maar vanuit een materieelplan gekoppeld aan materieel;
-•	Tenslotte (tijdens de uitvoering) de fysieke beweging buiten op de infra, onder regie van het in-fraplan en het materieelplan, met concrete spoorvoertuig(en).</t>
   </si>
   <si>
     <t>Er zijn 3 soorten bewegingmaterieelrelaties: 
@@ -9208,6 +9193,21 @@
 3. Wat een verbinding, contact tot stand brengt
 Definitie inframanagement (binnen EV TB): 3
 Definitie reizigersinformatie  2 (zie ook “reizigersaansluiting”)</t>
+  </si>
+  <si>
+    <t>Er zijn twee soorten bewegingen:
+* trein;
+* rangeerbeweging.
+Toelichting
+Van Dale:
+1.	Het bewegen, zich verplaatsen 
+2.	Groep die naar iets streeft, zich ergens voor inzet 
+3.	Drukte, vertier
+Definitie in lijn met 1, maar met voorkeur voor 3.
+Binnen de keten van het vervoersproces heeft een beweging verschillende opeenvolgende voorkomens of statussen:
+•	In eerste instantie een administratief bestaan, nog ontkoppeld van het fysieke materieel dat erbij betrokken is: dus alleen de modelmatige afbeelding van de verplaatsing over de railinfrastruc-tuur en de materieeleenheden slechts o.b.v. een soortaanduiding;
+•	Daarna een administratief bestaan, maar vanuit een materieelplan gekoppeld aan materieel;
+•	Tenslotte (tijdens de uitvoering) de fysieke beweging buiten op de infra, onder regie van het in-fraplan en het materieelplan, met concrete spoorvoertuig(en).</t>
   </si>
 </sst>
 </file>
@@ -9329,12 +9329,6 @@
   </cellStyles>
   <dxfs count="21">
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -9393,6 +9387,12 @@
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -9523,28 +9523,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F4523D09-A7D5-488B-A95B-08F3E51784AE}" name="Tabel1" displayName="Tabel1" ref="A1:S757" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F4523D09-A7D5-488B-A95B-08F3E51784AE}" name="Tabel1" displayName="Tabel1" ref="A1:S757" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <autoFilter ref="A1:S757" xr:uid="{F4523D09-A7D5-488B-A95B-08F3E51784AE}"/>
   <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{13E13C61-63F9-441A-8D70-55E4B10E4CE2}" name="voorkeursterm" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{1F12A0D0-4DAA-4803-ACCD-B98EBB743363}" name="alternatieve term" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{4C474793-3F4E-492A-B5F8-E997C953EF11}" name="in kader" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{F1329824-5D3D-4A69-8EFF-0E86FE213D1E}" name="definitie" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{0A09F509-424B-4E52-B56E-BE588BA64F1E}" name="heeft bron" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{5D9AB9FE-9738-48A9-8931-FED6C67EDB6C}" name="heeft bovenliggend begrip" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{1FC1C457-1807-4EA8-8E4E-C4D6B2433810}" name="heeft onderliggend begrip" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{E3775D3B-C96F-40B6-A6B8-1DF48F432A36}" name="is gerelateerd aan" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{F8B9BB72-EF33-47B0-9A37-F89E864CDC93}" name="toelichting" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{08FE5C39-DA6C-4C47-8B84-8644706E9B2C}" name="voorbeeld" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{CD833623-6BE4-4A2D-B8DF-2E774D9D1CF3}" name="is exact overeenkomstig" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{732C4B90-5DAB-4953-8CD5-8C970593E64B}" name="is overeenkomstig verwant" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{1BB1DB70-5E63-4DBA-82DE-2BF9E904E56B}" name="is specialisatie van" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{1A897CA1-B0F1-422B-BE0C-D5AEB7396FBE}" name="is generalisatie van" dataDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{4E7F8A39-CAD7-4CB9-B1C9-201E2A96F7A8}" name="is onderdeel van" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{25EEA2F5-F288-488C-97AB-CFFB67E358C7}" name="omvat" dataDxfId="5"/>
-    <tableColumn id="17" xr3:uid="{F6FE560F-420A-4D9A-8B89-C5307A0286B4}" name="is exemplaar van" dataDxfId="4"/>
-    <tableColumn id="18" xr3:uid="{0C57A3C2-4D9D-4882-8285-9996408377A0}" name="is categorie van" dataDxfId="3"/>
-    <tableColumn id="19" xr3:uid="{AA9E9141-13F2-4B2B-A515-463D56DFA4AB}" name="naam" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{13E13C61-63F9-441A-8D70-55E4B10E4CE2}" name="voorkeursterm" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{1F12A0D0-4DAA-4803-ACCD-B98EBB743363}" name="alternatieve term" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{4C474793-3F4E-492A-B5F8-E997C953EF11}" name="in kader" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{F1329824-5D3D-4A69-8EFF-0E86FE213D1E}" name="definitie" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{0A09F509-424B-4E52-B56E-BE588BA64F1E}" name="heeft bron" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{5D9AB9FE-9738-48A9-8931-FED6C67EDB6C}" name="heeft bovenliggend begrip" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{1FC1C457-1807-4EA8-8E4E-C4D6B2433810}" name="heeft onderliggend begrip" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{E3775D3B-C96F-40B6-A6B8-1DF48F432A36}" name="is gerelateerd aan" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{F8B9BB72-EF33-47B0-9A37-F89E864CDC93}" name="toelichting" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{08FE5C39-DA6C-4C47-8B84-8644706E9B2C}" name="voorbeeld" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{CD833623-6BE4-4A2D-B8DF-2E774D9D1CF3}" name="is exact overeenkomstig" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{732C4B90-5DAB-4953-8CD5-8C970593E64B}" name="is overeenkomstig verwant" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{1BB1DB70-5E63-4DBA-82DE-2BF9E904E56B}" name="is specialisatie van" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{1A897CA1-B0F1-422B-BE0C-D5AEB7396FBE}" name="is generalisatie van" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{4E7F8A39-CAD7-4CB9-B1C9-201E2A96F7A8}" name="is onderdeel van" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{25EEA2F5-F288-488C-97AB-CFFB67E358C7}" name="omvat" dataDxfId="3"/>
+    <tableColumn id="17" xr3:uid="{F6FE560F-420A-4D9A-8B89-C5307A0286B4}" name="is exemplaar van" dataDxfId="2"/>
+    <tableColumn id="18" xr3:uid="{0C57A3C2-4D9D-4882-8285-9996408377A0}" name="is categorie van" dataDxfId="1"/>
+    <tableColumn id="19" xr3:uid="{AA9E9141-13F2-4B2B-A515-463D56DFA4AB}" name="naam" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9893,61 +9893,61 @@
   <sheetData>
     <row r="1" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>2526</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>2527</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2528</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2529</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>2530</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>2531</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>2532</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>2533</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="4" t="s">
         <v>2534</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>2535</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="1" t="s">
         <v>2536</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>2537</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>2538</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>2539</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>2540</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>2541</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>2542</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>2543</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>2544</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>2545</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="38.25" x14ac:dyDescent="0.2">
@@ -10080,7 +10080,7 @@
         <v>872</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="2"/>
@@ -12568,7 +12568,7 @@
         <v>1025</v>
       </c>
       <c r="I92" s="5" t="s">
-        <v>2142</v>
+        <v>2546</v>
       </c>
       <c r="J92" s="5"/>
       <c r="K92" s="2"/>
@@ -12599,10 +12599,10 @@
         <v>1028</v>
       </c>
       <c r="I93" s="5" t="s">
+        <v>2142</v>
+      </c>
+      <c r="J93" s="5" t="s">
         <v>2143</v>
-      </c>
-      <c r="J93" s="5" t="s">
-        <v>2144</v>
       </c>
       <c r="K93" s="2"/>
       <c r="L93" s="2"/>
@@ -12631,7 +12631,7 @@
       </c>
       <c r="I94" s="5"/>
       <c r="J94" s="5" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="K94" s="2"/>
       <c r="L94" s="2"/>
@@ -12771,7 +12771,7 @@
         <v>1041</v>
       </c>
       <c r="I99" s="5" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="J99" s="5"/>
       <c r="K99" s="2"/>
@@ -12803,7 +12803,7 @@
       </c>
       <c r="I100" s="5"/>
       <c r="J100" s="5" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="K100" s="2"/>
       <c r="L100" s="2"/>
@@ -12831,7 +12831,7 @@
         <v>1045</v>
       </c>
       <c r="I101" s="5" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="J101" s="5"/>
       <c r="K101" s="2"/>
@@ -12891,7 +12891,7 @@
         <v>1049</v>
       </c>
       <c r="I103" s="5" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="J103" s="5"/>
       <c r="K103" s="2"/>
@@ -12980,7 +12980,7 @@
         <v>1056</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="J106" s="5"/>
       <c r="K106" s="2"/>
@@ -13034,7 +13034,7 @@
         <v>1058</v>
       </c>
       <c r="I108" s="5" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="J108" s="5"/>
       <c r="K108" s="2"/>
@@ -13090,10 +13090,10 @@
         <v>1060</v>
       </c>
       <c r="I110" s="5" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="J110" s="5" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="K110" s="2"/>
       <c r="L110" s="2"/>
@@ -13121,7 +13121,7 @@
         <v>1063</v>
       </c>
       <c r="I111" s="5" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="J111" s="5"/>
       <c r="K111" s="2"/>
@@ -13150,10 +13150,10 @@
         <v>1065</v>
       </c>
       <c r="I112" s="5" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="J112" s="5" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="K112" s="2"/>
       <c r="L112" s="2"/>
@@ -13181,7 +13181,7 @@
         <v>1067</v>
       </c>
       <c r="I113" s="5" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="J113" s="5"/>
       <c r="K113" s="2"/>
@@ -13239,7 +13239,7 @@
         <v>510</v>
       </c>
       <c r="I115" s="5" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="J115" s="5"/>
       <c r="K115" s="2"/>
@@ -13297,7 +13297,7 @@
         <v>1075</v>
       </c>
       <c r="I117" s="5" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="J117" s="5"/>
       <c r="K117" s="2"/>
@@ -13357,7 +13357,7 @@
         <v>1079</v>
       </c>
       <c r="I119" s="5" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="J119" s="5"/>
       <c r="K119" s="2"/>
@@ -13417,7 +13417,7 @@
         <v>1082</v>
       </c>
       <c r="I121" s="5" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="J121" s="5"/>
       <c r="K121" s="2"/>
@@ -13446,7 +13446,7 @@
         <v>1084</v>
       </c>
       <c r="I122" s="5" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="J122" s="5"/>
       <c r="K122" s="2"/>
@@ -13475,7 +13475,7 @@
         <v>1086</v>
       </c>
       <c r="I123" s="5" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="J123" s="5"/>
       <c r="K123" s="2"/>
@@ -13505,7 +13505,7 @@
       <c r="H124" s="2"/>
       <c r="I124" s="5"/>
       <c r="J124" s="5" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="K124" s="2"/>
       <c r="L124" s="2"/>
@@ -13589,7 +13589,7 @@
         <v>1093</v>
       </c>
       <c r="I127" s="5" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="J127" s="5"/>
       <c r="K127" s="2"/>
@@ -13681,7 +13681,7 @@
       <c r="R130" s="2"/>
       <c r="S130" s="2"/>
     </row>
-    <row r="131" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:19" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
         <v>145</v>
       </c>
@@ -13701,7 +13701,7 @@
         <v>1099</v>
       </c>
       <c r="I131" s="5" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="J131" s="5"/>
       <c r="K131" s="2"/>
@@ -13732,7 +13732,7 @@
         <v>1102</v>
       </c>
       <c r="I132" s="5" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="J132" s="5"/>
       <c r="K132" s="2"/>
@@ -13790,7 +13790,7 @@
         <v>1106</v>
       </c>
       <c r="I134" s="5" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="J134" s="5"/>
       <c r="K134" s="2"/>
@@ -13819,7 +13819,7 @@
         <v>1108</v>
       </c>
       <c r="I135" s="5" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="J135" s="5"/>
       <c r="K135" s="2"/>
@@ -13902,7 +13902,7 @@
         <v>1113</v>
       </c>
       <c r="I138" s="5" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="J138" s="5"/>
       <c r="K138" s="2"/>
@@ -13987,7 +13987,7 @@
         <v>1118</v>
       </c>
       <c r="I141" s="5" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="J141" s="5"/>
       <c r="K141" s="2"/>
@@ -14043,7 +14043,7 @@
         <v>1122</v>
       </c>
       <c r="I143" s="5" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="J143" s="5"/>
       <c r="K143" s="2"/>
@@ -14151,7 +14151,7 @@
         <v>1129</v>
       </c>
       <c r="I147" s="5" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="J147" s="5"/>
       <c r="K147" s="2"/>
@@ -14180,7 +14180,7 @@
         <v>1131</v>
       </c>
       <c r="I148" s="5" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="J148" s="5"/>
       <c r="K148" s="2"/>
@@ -14236,7 +14236,7 @@
         <v>1135</v>
       </c>
       <c r="I150" s="5" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="J150" s="5"/>
       <c r="K150" s="2"/>
@@ -14265,10 +14265,10 @@
         <v>1137</v>
       </c>
       <c r="I151" s="5" t="s">
+        <v>2172</v>
+      </c>
+      <c r="J151" s="5" t="s">
         <v>2173</v>
-      </c>
-      <c r="J151" s="5" t="s">
-        <v>2174</v>
       </c>
       <c r="K151" s="2"/>
       <c r="L151" s="2"/>
@@ -14323,7 +14323,7 @@
         <v>1140</v>
       </c>
       <c r="I153" s="5" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="J153" s="5"/>
       <c r="K153" s="2"/>
@@ -14352,7 +14352,7 @@
         <v>1142</v>
       </c>
       <c r="I154" s="5" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="J154" s="5"/>
       <c r="K154" s="2"/>
@@ -14381,7 +14381,7 @@
         <v>1144</v>
       </c>
       <c r="I155" s="5" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="J155" s="5"/>
       <c r="K155" s="2"/>
@@ -14468,7 +14468,7 @@
         <v>1150</v>
       </c>
       <c r="I158" s="5" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="J158" s="5"/>
       <c r="K158" s="2"/>
@@ -14497,10 +14497,10 @@
         <v>1152</v>
       </c>
       <c r="I159" s="5" t="s">
+        <v>2178</v>
+      </c>
+      <c r="J159" s="5" t="s">
         <v>2179</v>
-      </c>
-      <c r="J159" s="5" t="s">
-        <v>2180</v>
       </c>
       <c r="K159" s="2"/>
       <c r="L159" s="2"/>
@@ -14528,7 +14528,7 @@
         <v>1154</v>
       </c>
       <c r="I160" s="5" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="J160" s="5"/>
       <c r="K160" s="2"/>
@@ -14557,7 +14557,7 @@
         <v>1156</v>
       </c>
       <c r="I161" s="5" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="J161" s="5"/>
       <c r="K161" s="2"/>
@@ -14640,7 +14640,7 @@
         <v>1160</v>
       </c>
       <c r="I164" s="5" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="J164" s="5"/>
       <c r="K164" s="2"/>
@@ -14671,7 +14671,7 @@
         <v>1163</v>
       </c>
       <c r="I165" s="5" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="J165" s="5"/>
       <c r="K165" s="2"/>
@@ -14729,7 +14729,7 @@
         <v>1167</v>
       </c>
       <c r="I167" s="5" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="J167" s="5"/>
       <c r="K167" s="2"/>
@@ -14810,7 +14810,7 @@
         <v>1172</v>
       </c>
       <c r="I170" s="5" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="J170" s="5"/>
       <c r="K170" s="2"/>
@@ -14839,7 +14839,7 @@
         <v>1174</v>
       </c>
       <c r="I171" s="5" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="J171" s="5"/>
       <c r="K171" s="2"/>
@@ -14897,7 +14897,7 @@
         <v>1178</v>
       </c>
       <c r="I173" s="5" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="J173" s="5"/>
       <c r="K173" s="2"/>
@@ -14924,7 +14924,7 @@
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
       <c r="I174" s="5" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="J174" s="5"/>
       <c r="K174" s="2"/>
@@ -14953,7 +14953,7 @@
         <v>1181</v>
       </c>
       <c r="I175" s="5" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="J175" s="5"/>
       <c r="K175" s="2"/>
@@ -14982,7 +14982,7 @@
         <v>1183</v>
       </c>
       <c r="I176" s="5" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="J176" s="5"/>
       <c r="K176" s="2"/>
@@ -15011,7 +15011,7 @@
         <v>1185</v>
       </c>
       <c r="I177" s="5" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="J177" s="5"/>
       <c r="K177" s="2"/>
@@ -15096,7 +15096,7 @@
         <v>1191</v>
       </c>
       <c r="I180" s="5" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="J180" s="5"/>
       <c r="K180" s="2"/>
@@ -15129,7 +15129,7 @@
         <v>1194</v>
       </c>
       <c r="I181" s="5" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="J181" s="5"/>
       <c r="K181" s="2"/>
@@ -15160,7 +15160,7 @@
         <v>1197</v>
       </c>
       <c r="I182" s="5" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="J182" s="5"/>
       <c r="K182" s="2"/>
@@ -15189,7 +15189,7 @@
       <c r="G183" s="2"/>
       <c r="H183" s="2"/>
       <c r="I183" s="5" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="J183" s="5"/>
       <c r="K183" s="2"/>
@@ -15249,7 +15249,7 @@
         <v>1203</v>
       </c>
       <c r="I185" s="5" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="J185" s="5"/>
       <c r="K185" s="2"/>
@@ -15307,7 +15307,7 @@
         <v>1206</v>
       </c>
       <c r="I187" s="5" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="J187" s="5"/>
       <c r="K187" s="2"/>
@@ -15367,7 +15367,7 @@
         <v>1209</v>
       </c>
       <c r="I189" s="5" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="J189" s="5"/>
       <c r="K189" s="2"/>
@@ -15398,7 +15398,7 @@
         <v>1212</v>
       </c>
       <c r="I190" s="5" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="J190" s="5"/>
       <c r="K190" s="2"/>
@@ -15429,7 +15429,7 @@
         <v>1214</v>
       </c>
       <c r="I191" s="5" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="J191" s="5"/>
       <c r="K191" s="2"/>
@@ -15458,7 +15458,7 @@
         <v>920</v>
       </c>
       <c r="I192" s="5" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="J192" s="5"/>
       <c r="K192" s="2"/>
@@ -15489,7 +15489,7 @@
         <v>1217</v>
       </c>
       <c r="I193" s="5" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="J193" s="5"/>
       <c r="K193" s="2"/>
@@ -15518,7 +15518,7 @@
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
       <c r="I194" s="5" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="J194" s="5"/>
       <c r="K194" s="2"/>
@@ -15576,7 +15576,7 @@
         <v>1223</v>
       </c>
       <c r="I196" s="5" t="s">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="J196" s="5"/>
       <c r="K196" s="2"/>
@@ -15659,7 +15659,7 @@
         <v>1229</v>
       </c>
       <c r="I199" s="5" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="J199" s="5"/>
       <c r="K199" s="2"/>
@@ -15717,7 +15717,7 @@
         <v>1233</v>
       </c>
       <c r="I201" s="5" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="J201" s="5"/>
       <c r="K201" s="2"/>
@@ -15833,7 +15833,7 @@
         <v>1237</v>
       </c>
       <c r="I205" s="5" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="J205" s="5"/>
       <c r="K205" s="2"/>
@@ -15862,7 +15862,7 @@
         <v>1239</v>
       </c>
       <c r="I206" s="5" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="J206" s="5"/>
       <c r="K206" s="2"/>
@@ -15949,7 +15949,7 @@
         <v>1245</v>
       </c>
       <c r="I209" s="5" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="J209" s="5"/>
       <c r="K209" s="2"/>
@@ -15980,7 +15980,7 @@
         <v>1248</v>
       </c>
       <c r="I210" s="5" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="J210" s="5"/>
       <c r="K210" s="2"/>
@@ -16011,10 +16011,10 @@
         <v>1251</v>
       </c>
       <c r="I211" s="5" t="s">
+        <v>2210</v>
+      </c>
+      <c r="J211" s="5" t="s">
         <v>2211</v>
-      </c>
-      <c r="J211" s="5" t="s">
-        <v>2212</v>
       </c>
       <c r="K211" s="2"/>
       <c r="L211" s="2"/>
@@ -16040,7 +16040,7 @@
       <c r="G212" s="2"/>
       <c r="H212" s="2"/>
       <c r="I212" s="5" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="J212" s="5"/>
       <c r="K212" s="2"/>
@@ -16069,7 +16069,7 @@
         <v>944</v>
       </c>
       <c r="I213" s="5" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="J213" s="5"/>
       <c r="K213" s="2"/>
@@ -16127,7 +16127,7 @@
         <v>1196</v>
       </c>
       <c r="I215" s="5" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="J215" s="5"/>
       <c r="K215" s="2"/>
@@ -16156,10 +16156,10 @@
         <v>1258</v>
       </c>
       <c r="I216" s="5" t="s">
+        <v>2215</v>
+      </c>
+      <c r="J216" s="5" t="s">
         <v>2216</v>
-      </c>
-      <c r="J216" s="5" t="s">
-        <v>2217</v>
       </c>
       <c r="K216" s="2"/>
       <c r="L216" s="2"/>
@@ -16185,7 +16185,7 @@
       <c r="G217" s="2"/>
       <c r="H217" s="2"/>
       <c r="I217" s="5" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="J217" s="5"/>
       <c r="K217" s="2"/>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="I219" s="5"/>
       <c r="J219" s="5" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="K219" s="2"/>
       <c r="L219" s="2"/>
@@ -16330,7 +16330,7 @@
         <v>1271</v>
       </c>
       <c r="I222" s="5" t="s">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="J222" s="5"/>
       <c r="K222" s="2"/>
@@ -16409,7 +16409,7 @@
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
       <c r="I225" s="5" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="J225" s="5"/>
       <c r="K225" s="2"/>
@@ -16440,7 +16440,7 @@
         <v>1101</v>
       </c>
       <c r="I226" s="5" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="J226" s="5"/>
       <c r="K226" s="2"/>
@@ -16471,7 +16471,7 @@
         <v>1278</v>
       </c>
       <c r="I227" s="5" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="J227" s="5"/>
       <c r="K227" s="2"/>
@@ -16498,7 +16498,7 @@
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
       <c r="I228" s="5" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="J228" s="5"/>
       <c r="K228" s="2"/>
@@ -16527,7 +16527,7 @@
       </c>
       <c r="H229" s="2"/>
       <c r="I229" s="5" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="J229" s="5"/>
       <c r="K229" s="2"/>
@@ -16558,7 +16558,7 @@
         <v>1284</v>
       </c>
       <c r="I230" s="5" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="J230" s="5"/>
       <c r="K230" s="2"/>
@@ -16647,7 +16647,7 @@
         <v>1289</v>
       </c>
       <c r="I233" s="5" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="J233" s="5"/>
       <c r="K233" s="2"/>
@@ -16761,7 +16761,7 @@
         <v>1296</v>
       </c>
       <c r="I237" s="5" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="J237" s="5"/>
       <c r="K237" s="2"/>
@@ -16790,7 +16790,7 @@
         <v>1298</v>
       </c>
       <c r="I238" s="5" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
       <c r="J238" s="5"/>
       <c r="K238" s="2"/>
@@ -16873,7 +16873,7 @@
         <v>1304</v>
       </c>
       <c r="I241" s="5" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="J241" s="5"/>
       <c r="K241" s="2"/>
@@ -16929,7 +16929,7 @@
         <v>1308</v>
       </c>
       <c r="I243" s="5" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="J243" s="5"/>
       <c r="K243" s="2"/>
@@ -16960,7 +16960,7 @@
         <v>1311</v>
       </c>
       <c r="I244" s="5" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="J244" s="5"/>
       <c r="K244" s="2"/>
@@ -16989,7 +16989,7 @@
         <v>1313</v>
       </c>
       <c r="I245" s="5" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="J245" s="5"/>
       <c r="K245" s="2"/>
@@ -17074,7 +17074,7 @@
         <v>1319</v>
       </c>
       <c r="I248" s="5" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="J248" s="5"/>
       <c r="K248" s="2"/>
@@ -17103,7 +17103,7 @@
         <v>1321</v>
       </c>
       <c r="I249" s="5" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="J249" s="5"/>
       <c r="K249" s="2"/>
@@ -17132,7 +17132,7 @@
       <c r="G250" s="2"/>
       <c r="H250" s="2"/>
       <c r="I250" s="5" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="J250" s="5"/>
       <c r="K250" s="2"/>
@@ -17161,7 +17161,7 @@
       <c r="G251" s="2"/>
       <c r="H251" s="2"/>
       <c r="I251" s="5" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="J251" s="5"/>
       <c r="K251" s="2"/>
@@ -17194,7 +17194,7 @@
         <v>1325</v>
       </c>
       <c r="I252" s="5" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="J252" s="5"/>
       <c r="K252" s="2"/>
@@ -17248,7 +17248,7 @@
         <v>1328</v>
       </c>
       <c r="I254" s="5" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="J254" s="5"/>
       <c r="K254" s="2"/>
@@ -17279,7 +17279,7 @@
         <v>1330</v>
       </c>
       <c r="I255" s="5" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="J255" s="5"/>
       <c r="K255" s="2"/>
@@ -17426,7 +17426,7 @@
         <v>1339</v>
       </c>
       <c r="I260" s="5" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="J260" s="5"/>
       <c r="K260" s="2"/>
@@ -17534,7 +17534,7 @@
         <v>1344</v>
       </c>
       <c r="I264" s="5" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="J264" s="5"/>
       <c r="K264" s="2"/>
@@ -17563,7 +17563,7 @@
         <v>1346</v>
       </c>
       <c r="I265" s="5" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="J265" s="5"/>
       <c r="K265" s="2"/>
@@ -17592,7 +17592,7 @@
         <v>1348</v>
       </c>
       <c r="I266" s="5" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="J266" s="5"/>
       <c r="K266" s="2"/>
@@ -17621,7 +17621,7 @@
         <v>1350</v>
       </c>
       <c r="I267" s="5" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="J267" s="5"/>
       <c r="K267" s="2"/>
@@ -17680,7 +17680,7 @@
       </c>
       <c r="I269" s="5"/>
       <c r="J269" s="5" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="K269" s="2"/>
       <c r="L269" s="2"/>
@@ -17692,7 +17692,7 @@
       <c r="R269" s="2"/>
       <c r="S269" s="2"/>
     </row>
-    <row r="270" spans="1:19" ht="63.75" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A270" s="2" t="s">
         <v>292</v>
       </c>
@@ -17791,7 +17791,7 @@
         <v>1363</v>
       </c>
       <c r="I273" s="5" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="J273" s="5"/>
       <c r="K273" s="2"/>
@@ -17820,10 +17820,10 @@
         <v>1365</v>
       </c>
       <c r="I274" s="5" t="s">
+        <v>2245</v>
+      </c>
+      <c r="J274" s="5" t="s">
         <v>2246</v>
-      </c>
-      <c r="J274" s="5" t="s">
-        <v>2247</v>
       </c>
       <c r="K274" s="2"/>
       <c r="L274" s="2"/>
@@ -17853,7 +17853,7 @@
         <v>1367</v>
       </c>
       <c r="I275" s="5" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="J275" s="5"/>
       <c r="K275" s="2"/>
@@ -17882,10 +17882,10 @@
         <v>1369</v>
       </c>
       <c r="I276" s="5" t="s">
+        <v>2248</v>
+      </c>
+      <c r="J276" s="5" t="s">
         <v>2249</v>
-      </c>
-      <c r="J276" s="5" t="s">
-        <v>2250</v>
       </c>
       <c r="K276" s="2"/>
       <c r="L276" s="2"/>
@@ -18125,7 +18125,7 @@
         <v>1379</v>
       </c>
       <c r="I285" s="5" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="J285" s="5"/>
       <c r="K285" s="2"/>
@@ -18208,7 +18208,7 @@
         <v>1385</v>
       </c>
       <c r="I288" s="5" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="J288" s="5"/>
       <c r="K288" s="2"/>
@@ -18239,7 +18239,7 @@
         <v>1388</v>
       </c>
       <c r="I289" s="5" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="J289" s="5"/>
       <c r="K289" s="2"/>
@@ -18372,7 +18372,7 @@
         <v>1395</v>
       </c>
       <c r="I294" s="5" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="J294" s="5"/>
       <c r="K294" s="2"/>
@@ -18430,7 +18430,7 @@
         <v>1398</v>
       </c>
       <c r="I296" s="5" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
       <c r="J296" s="5"/>
       <c r="K296" s="2"/>
@@ -18459,7 +18459,7 @@
         <v>1400</v>
       </c>
       <c r="I297" s="5" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="J297" s="5"/>
       <c r="K297" s="2"/>
@@ -18488,7 +18488,7 @@
         <v>1116</v>
       </c>
       <c r="I298" s="5" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="J298" s="5"/>
       <c r="K298" s="2"/>
@@ -18517,7 +18517,7 @@
         <v>1223</v>
       </c>
       <c r="I299" s="5" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="J299" s="5"/>
       <c r="K299" s="2"/>
@@ -18546,7 +18546,7 @@
         <v>1404</v>
       </c>
       <c r="I300" s="5" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="J300" s="5"/>
       <c r="K300" s="2"/>
@@ -18579,7 +18579,7 @@
         <v>1407</v>
       </c>
       <c r="I301" s="5" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="J301" s="5"/>
       <c r="K301" s="2"/>
@@ -18610,7 +18610,7 @@
         <v>1410</v>
       </c>
       <c r="I302" s="5" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="J302" s="5"/>
       <c r="K302" s="2"/>
@@ -18668,7 +18668,7 @@
         <v>1414</v>
       </c>
       <c r="I304" s="5" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="J304" s="5"/>
       <c r="K304" s="2"/>
@@ -18724,7 +18724,7 @@
         <v>1418</v>
       </c>
       <c r="I306" s="5" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="J306" s="5"/>
       <c r="K306" s="2"/>
@@ -18780,10 +18780,10 @@
       <c r="G308" s="2"/>
       <c r="H308" s="2"/>
       <c r="I308" s="5" t="s">
+        <v>2263</v>
+      </c>
+      <c r="J308" s="5" t="s">
         <v>2264</v>
-      </c>
-      <c r="J308" s="5" t="s">
-        <v>2265</v>
       </c>
       <c r="K308" s="2"/>
       <c r="L308" s="2"/>
@@ -18813,7 +18813,7 @@
         <v>1423</v>
       </c>
       <c r="I309" s="5" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="J309" s="5"/>
       <c r="K309" s="2"/>
@@ -18842,7 +18842,7 @@
         <v>1425</v>
       </c>
       <c r="I310" s="5" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="J310" s="5"/>
       <c r="K310" s="2"/>
@@ -18898,7 +18898,7 @@
         <v>1428</v>
       </c>
       <c r="I312" s="5" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="J312" s="5"/>
       <c r="K312" s="2"/>
@@ -18925,7 +18925,7 @@
       <c r="G313" s="2"/>
       <c r="H313" s="2"/>
       <c r="I313" s="5" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="J313" s="5"/>
       <c r="K313" s="2"/>
@@ -18952,10 +18952,10 @@
       <c r="G314" s="2"/>
       <c r="H314" s="2"/>
       <c r="I314" s="5" t="s">
+        <v>2269</v>
+      </c>
+      <c r="J314" s="5" t="s">
         <v>2270</v>
-      </c>
-      <c r="J314" s="5" t="s">
-        <v>2271</v>
       </c>
       <c r="K314" s="2"/>
       <c r="L314" s="2"/>
@@ -18985,7 +18985,7 @@
         <v>1431</v>
       </c>
       <c r="I315" s="5" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="J315" s="5"/>
       <c r="K315" s="2"/>
@@ -19016,7 +19016,7 @@
         <v>1434</v>
       </c>
       <c r="I316" s="5" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="J316" s="5"/>
       <c r="K316" s="2"/>
@@ -19070,7 +19070,7 @@
         <v>1436</v>
       </c>
       <c r="I318" s="5" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="J318" s="5"/>
       <c r="K318" s="2"/>
@@ -19101,7 +19101,7 @@
         <v>510</v>
       </c>
       <c r="I319" s="5" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="J319" s="5"/>
       <c r="K319" s="2"/>
@@ -19184,7 +19184,7 @@
       <c r="G322" s="2"/>
       <c r="H322" s="2"/>
       <c r="I322" s="5" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="J322" s="5"/>
       <c r="K322" s="2"/>
@@ -19215,7 +19215,7 @@
         <v>1049</v>
       </c>
       <c r="I323" s="5" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="J323" s="5"/>
       <c r="K323" s="2"/>
@@ -19244,7 +19244,7 @@
         <v>1445</v>
       </c>
       <c r="I324" s="5" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="J324" s="5"/>
       <c r="K324" s="2"/>
@@ -19273,10 +19273,10 @@
         <v>1447</v>
       </c>
       <c r="I325" s="5" t="s">
+        <v>2278</v>
+      </c>
+      <c r="J325" s="9" t="s">
         <v>2279</v>
-      </c>
-      <c r="J325" s="9" t="s">
-        <v>2280</v>
       </c>
       <c r="K325" s="2"/>
       <c r="L325" s="2"/>
@@ -19422,7 +19422,7 @@
         <v>1434</v>
       </c>
       <c r="I330" s="5" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="J330" s="5"/>
       <c r="K330" s="2"/>
@@ -19476,7 +19476,7 @@
         <v>1456</v>
       </c>
       <c r="I332" s="5" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="J332" s="5"/>
       <c r="K332" s="2"/>
@@ -19505,7 +19505,7 @@
         <v>1458</v>
       </c>
       <c r="I333" s="5" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="J333" s="5"/>
       <c r="K333" s="2"/>
@@ -19534,10 +19534,10 @@
         <v>1460</v>
       </c>
       <c r="I334" s="5" t="s">
+        <v>2282</v>
+      </c>
+      <c r="J334" s="5" t="s">
         <v>2283</v>
-      </c>
-      <c r="J334" s="5" t="s">
-        <v>2284</v>
       </c>
       <c r="K334" s="2"/>
       <c r="L334" s="2"/>
@@ -19565,7 +19565,7 @@
         <v>1462</v>
       </c>
       <c r="I335" s="5" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
       <c r="J335" s="5"/>
       <c r="K335" s="2"/>
@@ -19594,10 +19594,10 @@
         <v>1464</v>
       </c>
       <c r="I336" s="5" t="s">
+        <v>2285</v>
+      </c>
+      <c r="J336" s="9" t="s">
         <v>2286</v>
-      </c>
-      <c r="J336" s="9" t="s">
-        <v>2287</v>
       </c>
       <c r="K336" s="2"/>
       <c r="L336" s="2"/>
@@ -19706,7 +19706,7 @@
         <v>1471</v>
       </c>
       <c r="I340" s="5" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="J340" s="5"/>
       <c r="K340" s="2"/>
@@ -19735,7 +19735,7 @@
         <v>1473</v>
       </c>
       <c r="I341" s="5" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="J341" s="5"/>
       <c r="K341" s="2"/>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="I342" s="5"/>
       <c r="J342" s="5" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="K342" s="2"/>
       <c r="L342" s="2"/>
@@ -19822,7 +19822,7 @@
         <v>1478</v>
       </c>
       <c r="I344" s="5" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="J344" s="5"/>
       <c r="K344" s="2"/>
@@ -19932,10 +19932,10 @@
         <v>1485</v>
       </c>
       <c r="I348" s="5" t="s">
+        <v>2291</v>
+      </c>
+      <c r="J348" s="5" t="s">
         <v>2292</v>
-      </c>
-      <c r="J348" s="5" t="s">
-        <v>2293</v>
       </c>
       <c r="K348" s="2"/>
       <c r="L348" s="2"/>
@@ -19964,7 +19964,7 @@
       </c>
       <c r="I349" s="5"/>
       <c r="J349" s="5" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="K349" s="2"/>
       <c r="L349" s="2"/>
@@ -20048,7 +20048,7 @@
         <v>1492</v>
       </c>
       <c r="I352" s="5" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="J352" s="5"/>
       <c r="K352" s="2"/>
@@ -20079,7 +20079,7 @@
         <v>1494</v>
       </c>
       <c r="I353" s="5" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="J353" s="5"/>
       <c r="K353" s="2"/>
@@ -20164,7 +20164,7 @@
         <v>1499</v>
       </c>
       <c r="I356" s="5" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="J356" s="5"/>
       <c r="K356" s="2"/>
@@ -20193,7 +20193,7 @@
       <c r="G357" s="2"/>
       <c r="H357" s="2"/>
       <c r="I357" s="5" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="J357" s="5"/>
       <c r="K357" s="2"/>
@@ -20333,7 +20333,7 @@
       </c>
       <c r="I362" s="5"/>
       <c r="J362" s="5" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="K362" s="2"/>
       <c r="L362" s="2"/>
@@ -20361,7 +20361,7 @@
       <c r="G363" s="2"/>
       <c r="H363" s="2"/>
       <c r="I363" s="5" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="J363" s="5"/>
       <c r="K363" s="2"/>
@@ -20390,7 +20390,7 @@
         <v>1513</v>
       </c>
       <c r="I364" s="5" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="J364" s="5"/>
       <c r="K364" s="2"/>
@@ -20444,7 +20444,7 @@
         <v>1515</v>
       </c>
       <c r="I366" s="5" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="J366" s="5"/>
       <c r="K366" s="2"/>
@@ -20554,7 +20554,7 @@
         <v>1520</v>
       </c>
       <c r="I370" s="5" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="J370" s="5"/>
       <c r="K370" s="2"/>
@@ -20583,7 +20583,7 @@
         <v>1522</v>
       </c>
       <c r="I371" s="5" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="J371" s="5"/>
       <c r="K371" s="2"/>
@@ -20668,7 +20668,7 @@
       <c r="G374" s="2"/>
       <c r="H374" s="2"/>
       <c r="I374" s="5" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="J374" s="5"/>
       <c r="K374" s="2"/>
@@ -20697,7 +20697,7 @@
         <v>1530</v>
       </c>
       <c r="I375" s="5" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="J375" s="5"/>
       <c r="K375" s="2"/>
@@ -20834,7 +20834,7 @@
         <v>1536</v>
       </c>
       <c r="I380" s="5" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="J380" s="5"/>
       <c r="K380" s="2"/>
@@ -20866,7 +20866,7 @@
       </c>
       <c r="I381" s="5"/>
       <c r="J381" s="5" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="K381" s="2"/>
       <c r="L381" s="2"/>
@@ -20894,7 +20894,7 @@
         <v>1539</v>
       </c>
       <c r="I382" s="5" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="J382" s="5"/>
       <c r="K382" s="2"/>
@@ -20925,7 +20925,7 @@
         <v>1541</v>
       </c>
       <c r="I383" s="5" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="J383" s="5"/>
       <c r="K383" s="2"/>
@@ -21010,7 +21010,7 @@
         <v>1547</v>
       </c>
       <c r="I386" s="5" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="J386" s="5"/>
       <c r="K386" s="2"/>
@@ -21039,7 +21039,7 @@
         <v>1549</v>
       </c>
       <c r="I387" s="5" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="J387" s="5"/>
       <c r="K387" s="2"/>
@@ -21070,7 +21070,7 @@
         <v>1551</v>
       </c>
       <c r="I388" s="5" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="J388" s="5"/>
       <c r="K388" s="2"/>
@@ -21101,7 +21101,7 @@
         <v>1554</v>
       </c>
       <c r="I389" s="5" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="J389" s="5"/>
       <c r="K389" s="2"/>
@@ -21130,7 +21130,7 @@
         <v>1556</v>
       </c>
       <c r="I390" s="5" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="J390" s="5"/>
       <c r="K390" s="2"/>
@@ -21161,7 +21161,7 @@
         <v>588</v>
       </c>
       <c r="I391" s="5" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="J391" s="5"/>
       <c r="K391" s="2"/>
@@ -21217,7 +21217,7 @@
         <v>1561</v>
       </c>
       <c r="I393" s="5" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="J393" s="5"/>
       <c r="K393" s="2"/>
@@ -21302,7 +21302,7 @@
         <v>1567</v>
       </c>
       <c r="I396" s="5" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="J396" s="5"/>
       <c r="K396" s="2"/>
@@ -21389,7 +21389,7 @@
         <v>1574</v>
       </c>
       <c r="I399" s="5" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="J399" s="5"/>
       <c r="K399" s="2"/>
@@ -21530,7 +21530,7 @@
         <v>1583</v>
       </c>
       <c r="I404" s="5" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="J404" s="5"/>
       <c r="K404" s="2"/>
@@ -21621,7 +21621,7 @@
         <v>1589</v>
       </c>
       <c r="I407" s="5" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="J407" s="5"/>
       <c r="K407" s="2"/>
@@ -21677,7 +21677,7 @@
         <v>1592</v>
       </c>
       <c r="I409" s="5" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="J409" s="5"/>
       <c r="K409" s="2"/>
@@ -21706,7 +21706,7 @@
       <c r="G410" s="2"/>
       <c r="H410" s="2"/>
       <c r="I410" s="5" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="J410" s="5"/>
       <c r="K410" s="2"/>
@@ -21735,7 +21735,7 @@
       <c r="G411" s="2"/>
       <c r="H411" s="2"/>
       <c r="I411" s="5" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
       <c r="J411" s="5"/>
       <c r="K411" s="2"/>
@@ -21766,7 +21766,7 @@
         <v>1597</v>
       </c>
       <c r="I412" s="5" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="J412" s="5"/>
       <c r="K412" s="2" t="s">
@@ -21799,7 +21799,7 @@
         <v>1599</v>
       </c>
       <c r="I413" s="5" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="J413" s="5"/>
       <c r="K413" s="2" t="s">
@@ -21857,7 +21857,7 @@
         <v>884</v>
       </c>
       <c r="I415" s="5" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="J415" s="5"/>
       <c r="K415" s="2"/>
@@ -21913,7 +21913,7 @@
         <v>1606</v>
       </c>
       <c r="I417" s="5" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
       <c r="J417" s="5"/>
       <c r="K417" s="2"/>
@@ -21926,7 +21926,7 @@
       <c r="R417" s="2"/>
       <c r="S417" s="2"/>
     </row>
-    <row r="418" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A418" s="2" t="s">
         <v>458</v>
       </c>
@@ -21998,10 +21998,10 @@
         <v>710</v>
       </c>
       <c r="I420" s="5" t="s">
+        <v>2325</v>
+      </c>
+      <c r="J420" s="5" t="s">
         <v>2326</v>
-      </c>
-      <c r="J420" s="5" t="s">
-        <v>2327</v>
       </c>
       <c r="K420" s="2"/>
       <c r="L420" s="2"/>
@@ -22031,7 +22031,7 @@
         <v>1609</v>
       </c>
       <c r="I421" s="5" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="J421" s="5"/>
       <c r="K421" s="2"/>
@@ -22060,7 +22060,7 @@
         <v>1611</v>
       </c>
       <c r="I422" s="5" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="J422" s="5"/>
       <c r="K422" s="2"/>
@@ -22116,7 +22116,7 @@
         <v>1613</v>
       </c>
       <c r="I424" s="5" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="J424" s="5"/>
       <c r="K424" s="2"/>
@@ -22145,7 +22145,7 @@
         <v>1615</v>
       </c>
       <c r="I425" s="5" t="s">
-        <v>2331</v>
+        <v>2330</v>
       </c>
       <c r="J425" s="5"/>
       <c r="K425" s="2"/>
@@ -22174,7 +22174,7 @@
         <v>1617</v>
       </c>
       <c r="I426" s="5" t="s">
-        <v>2332</v>
+        <v>2331</v>
       </c>
       <c r="J426" s="5"/>
       <c r="K426" s="2"/>
@@ -22203,7 +22203,7 @@
         <v>1619</v>
       </c>
       <c r="I427" s="5" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="J427" s="5"/>
       <c r="K427" s="2"/>
@@ -22299,7 +22299,7 @@
       <c r="R430" s="2"/>
       <c r="S430" s="2"/>
     </row>
-    <row r="431" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A431" s="2" t="s">
         <v>473</v>
       </c>
@@ -22340,7 +22340,7 @@
       <c r="G432" s="2"/>
       <c r="H432" s="2"/>
       <c r="I432" s="5" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="J432" s="5"/>
       <c r="K432" s="2"/>
@@ -22369,7 +22369,7 @@
       <c r="G433" s="2"/>
       <c r="H433" s="2"/>
       <c r="I433" s="5" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="J433" s="5"/>
       <c r="K433" s="2"/>
@@ -22423,7 +22423,7 @@
         <v>1569</v>
       </c>
       <c r="I435" s="5" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="J435" s="5"/>
       <c r="K435" s="2" t="s">
@@ -22452,7 +22452,7 @@
       <c r="G436" s="2"/>
       <c r="H436" s="2"/>
       <c r="I436" s="5" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
       <c r="J436" s="5"/>
       <c r="K436" s="2"/>
@@ -22539,7 +22539,7 @@
         <v>284</v>
       </c>
       <c r="I439" s="5" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="J439" s="5"/>
       <c r="K439" s="2"/>
@@ -22566,7 +22566,7 @@
       <c r="G440" s="2"/>
       <c r="H440" s="2"/>
       <c r="I440" s="5" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
       <c r="J440" s="5"/>
       <c r="K440" s="2"/>
@@ -22674,7 +22674,7 @@
       <c r="G444" s="2"/>
       <c r="H444" s="2"/>
       <c r="I444" s="5" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="J444" s="5"/>
       <c r="K444" s="2"/>
@@ -22701,7 +22701,7 @@
       <c r="G445" s="2"/>
       <c r="H445" s="2"/>
       <c r="I445" s="5" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="J445" s="5"/>
       <c r="K445" s="2"/>
@@ -22755,7 +22755,7 @@
       <c r="G447" s="2"/>
       <c r="H447" s="2"/>
       <c r="I447" s="5" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="J447" s="5"/>
       <c r="K447" s="2"/>
@@ -22839,7 +22839,7 @@
       </c>
       <c r="I450" s="5"/>
       <c r="J450" s="5" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="K450" s="2"/>
       <c r="L450" s="2"/>
@@ -22890,7 +22890,7 @@
       <c r="G452" s="2"/>
       <c r="H452" s="2"/>
       <c r="I452" s="5" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="J452" s="5"/>
       <c r="K452" s="2"/>
@@ -22948,7 +22948,7 @@
         <v>1651</v>
       </c>
       <c r="I454" s="5" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="J454" s="5"/>
       <c r="K454" s="2" t="s">
@@ -23002,7 +23002,7 @@
       <c r="G456" s="2"/>
       <c r="H456" s="2"/>
       <c r="I456" s="5" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="J456" s="5"/>
       <c r="K456" s="2"/>
@@ -23083,10 +23083,10 @@
         <v>1655</v>
       </c>
       <c r="I459" s="5" t="s">
+        <v>2346</v>
+      </c>
+      <c r="J459" s="5" t="s">
         <v>2347</v>
-      </c>
-      <c r="J459" s="5" t="s">
-        <v>2348</v>
       </c>
       <c r="K459" s="2"/>
       <c r="L459" s="2"/>
@@ -23139,7 +23139,7 @@
         <v>1660</v>
       </c>
       <c r="I461" s="5" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="J461" s="5"/>
       <c r="K461" s="2"/>
@@ -23168,7 +23168,7 @@
         <v>1662</v>
       </c>
       <c r="I462" s="5" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="J462" s="5"/>
       <c r="K462" s="2"/>
@@ -23199,7 +23199,7 @@
         <v>1664</v>
       </c>
       <c r="I463" s="5" t="s">
-        <v>2351</v>
+        <v>2350</v>
       </c>
       <c r="J463" s="5"/>
       <c r="K463" s="2"/>
@@ -23307,7 +23307,7 @@
       <c r="G467" s="2"/>
       <c r="H467" s="2"/>
       <c r="I467" s="5" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="J467" s="5"/>
       <c r="K467" s="2"/>
@@ -23336,7 +23336,7 @@
         <v>521</v>
       </c>
       <c r="I468" s="5" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="J468" s="5"/>
       <c r="K468" s="2"/>
@@ -23349,7 +23349,7 @@
       <c r="R468" s="2"/>
       <c r="S468" s="2"/>
     </row>
-    <row r="469" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A469" s="2" t="s">
         <v>516</v>
       </c>
@@ -23419,7 +23419,7 @@
         <v>1672</v>
       </c>
       <c r="I471" s="5" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="J471" s="5"/>
       <c r="K471" s="2"/>
@@ -23486,7 +23486,7 @@
       <c r="R473" s="2"/>
       <c r="S473" s="2"/>
     </row>
-    <row r="474" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A474" s="2" t="s">
         <v>523</v>
       </c>
@@ -23529,7 +23529,7 @@
         <v>1675</v>
       </c>
       <c r="I475" s="5" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="J475" s="5"/>
       <c r="K475" s="2"/>
@@ -23559,7 +23559,7 @@
       </c>
       <c r="I476" s="5"/>
       <c r="J476" s="5" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="K476" s="2"/>
       <c r="L476" s="2"/>
@@ -23695,7 +23695,7 @@
         <v>1686</v>
       </c>
       <c r="I481" s="5" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="J481" s="5"/>
       <c r="K481" s="2"/>
@@ -23726,7 +23726,7 @@
         <v>1688</v>
       </c>
       <c r="I482" s="5" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="J482" s="5"/>
       <c r="K482" s="2"/>
@@ -23757,7 +23757,7 @@
         <v>1690</v>
       </c>
       <c r="I483" s="5" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
       <c r="J483" s="5"/>
       <c r="K483" s="2"/>
@@ -23813,7 +23813,7 @@
         <v>1660</v>
       </c>
       <c r="I485" s="5" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="J485" s="5"/>
       <c r="K485" s="2"/>
@@ -23842,7 +23842,7 @@
         <v>1694</v>
       </c>
       <c r="I486" s="5" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="J486" s="5"/>
       <c r="K486" s="2"/>
@@ -23869,7 +23869,7 @@
       <c r="G487" s="2"/>
       <c r="H487" s="2"/>
       <c r="I487" s="5" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="J487" s="5"/>
       <c r="K487" s="2"/>
@@ -23925,7 +23925,7 @@
       <c r="G489" s="2"/>
       <c r="H489" s="2"/>
       <c r="I489" s="5" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="J489" s="5"/>
       <c r="K489" s="2"/>
@@ -23954,7 +23954,7 @@
         <v>1699</v>
       </c>
       <c r="I490" s="5" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="J490" s="5"/>
       <c r="K490" s="2"/>
@@ -24012,7 +24012,7 @@
         <v>1703</v>
       </c>
       <c r="I492" s="5" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="J492" s="5"/>
       <c r="K492" s="2"/>
@@ -24043,7 +24043,7 @@
         <v>1705</v>
       </c>
       <c r="I493" s="5" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="J493" s="5"/>
       <c r="K493" s="2"/>
@@ -24072,7 +24072,7 @@
         <v>1707</v>
       </c>
       <c r="I494" s="5" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="J494" s="5"/>
       <c r="K494" s="2"/>
@@ -24156,7 +24156,7 @@
       <c r="H497" s="2"/>
       <c r="I497" s="5"/>
       <c r="J497" s="5" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="K497" s="2"/>
       <c r="L497" s="2"/>
@@ -24211,7 +24211,7 @@
         <v>1716</v>
       </c>
       <c r="I499" s="5" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="J499" s="5"/>
       <c r="K499" s="2"/>
@@ -24240,7 +24240,7 @@
         <v>1086</v>
       </c>
       <c r="I500" s="5" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="J500" s="5"/>
       <c r="K500" s="2"/>
@@ -24269,7 +24269,7 @@
       <c r="G501" s="2"/>
       <c r="H501" s="2"/>
       <c r="I501" s="5" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="J501" s="5"/>
       <c r="K501" s="2"/>
@@ -24298,7 +24298,7 @@
         <v>1720</v>
       </c>
       <c r="I502" s="5" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="J502" s="5"/>
       <c r="K502" s="2"/>
@@ -24331,10 +24331,10 @@
         <v>1722</v>
       </c>
       <c r="I503" s="5" t="s">
+        <v>2371</v>
+      </c>
+      <c r="J503" s="5" t="s">
         <v>2372</v>
-      </c>
-      <c r="J503" s="5" t="s">
-        <v>2373</v>
       </c>
       <c r="K503" s="2" t="s">
         <v>556</v>
@@ -24362,7 +24362,7 @@
       <c r="G504" s="2"/>
       <c r="H504" s="2"/>
       <c r="I504" s="5" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="J504" s="5"/>
       <c r="K504" s="2"/>
@@ -24391,7 +24391,7 @@
         <v>1725</v>
       </c>
       <c r="I505" s="5" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="J505" s="5"/>
       <c r="K505" s="2"/>
@@ -24418,7 +24418,7 @@
       <c r="G506" s="2"/>
       <c r="H506" s="2"/>
       <c r="I506" s="5" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="J506" s="5"/>
       <c r="K506" s="2"/>
@@ -24447,7 +24447,7 @@
         <v>521</v>
       </c>
       <c r="I507" s="5" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="J507" s="5"/>
       <c r="K507" s="2"/>
@@ -24475,7 +24475,7 @@
       <c r="H508" s="2"/>
       <c r="I508" s="5"/>
       <c r="J508" s="5" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="K508" s="2"/>
       <c r="L508" s="2"/>
@@ -24505,7 +24505,7 @@
         <v>1730</v>
       </c>
       <c r="I509" s="5" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="J509" s="5"/>
       <c r="K509" s="2"/>
@@ -24534,7 +24534,7 @@
       <c r="G510" s="2"/>
       <c r="H510" s="2"/>
       <c r="I510" s="5" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="J510" s="5"/>
       <c r="K510" s="2"/>
@@ -24565,7 +24565,7 @@
         <v>1733</v>
       </c>
       <c r="I511" s="5" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="J511" s="10"/>
       <c r="K511" s="2"/>
@@ -24619,7 +24619,7 @@
       <c r="G513" s="2"/>
       <c r="H513" s="2"/>
       <c r="I513" s="5" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="J513" s="11"/>
       <c r="K513" s="2"/>
@@ -24723,7 +24723,7 @@
         <v>1740</v>
       </c>
       <c r="I517" s="5" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="J517" s="5"/>
       <c r="K517" s="2"/>
@@ -24808,7 +24808,7 @@
         <v>1746</v>
       </c>
       <c r="I520" s="5" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="J520" s="5"/>
       <c r="K520" s="2"/>
@@ -24837,7 +24837,7 @@
         <v>1748</v>
       </c>
       <c r="I521" s="5" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="J521" s="5"/>
       <c r="K521" s="2"/>
@@ -24864,10 +24864,10 @@
       <c r="G522" s="2"/>
       <c r="H522" s="2"/>
       <c r="I522" s="5" t="s">
+        <v>2385</v>
+      </c>
+      <c r="J522" s="5" t="s">
         <v>2386</v>
-      </c>
-      <c r="J522" s="5" t="s">
-        <v>2387</v>
       </c>
       <c r="K522" s="2"/>
       <c r="L522" s="2"/>
@@ -24898,7 +24898,7 @@
       </c>
       <c r="I523" s="5"/>
       <c r="J523" s="5" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="K523" s="2"/>
       <c r="L523" s="2"/>
@@ -24927,7 +24927,7 @@
       <c r="H524" s="2"/>
       <c r="I524" s="5"/>
       <c r="J524" s="5" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="K524" s="2"/>
       <c r="L524" s="2"/>
@@ -24982,7 +24982,7 @@
         <v>1756</v>
       </c>
       <c r="I526" s="5" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="J526" s="5"/>
       <c r="K526" s="2" t="s">
@@ -25013,7 +25013,7 @@
         <v>1758</v>
       </c>
       <c r="I527" s="5" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="J527" s="5"/>
       <c r="K527" s="2"/>
@@ -25065,7 +25065,7 @@
       <c r="G529" s="2"/>
       <c r="H529" s="2"/>
       <c r="I529" s="5" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="J529" s="5"/>
       <c r="K529" s="2"/>
@@ -25078,7 +25078,7 @@
       <c r="R529" s="2"/>
       <c r="S529" s="2"/>
     </row>
-    <row r="530" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A530" s="2" t="s">
         <v>585</v>
       </c>
@@ -25105,7 +25105,7 @@
       <c r="R530" s="2"/>
       <c r="S530" s="2"/>
     </row>
-    <row r="531" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A531" s="2" t="s">
         <v>587</v>
       </c>
@@ -25146,7 +25146,7 @@
       <c r="G532" s="2"/>
       <c r="H532" s="2"/>
       <c r="I532" s="5" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="J532" s="5"/>
       <c r="K532" s="2"/>
@@ -25173,7 +25173,7 @@
       <c r="G533" s="2"/>
       <c r="H533" s="2"/>
       <c r="I533" s="5" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="J533" s="5"/>
       <c r="K533" s="2"/>
@@ -25204,7 +25204,7 @@
         <v>1223</v>
       </c>
       <c r="I534" s="5" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="J534" s="5"/>
       <c r="K534" s="2"/>
@@ -25235,7 +25235,7 @@
         <v>1765</v>
       </c>
       <c r="I535" s="5" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="J535" s="5"/>
       <c r="K535" s="2"/>
@@ -25264,7 +25264,7 @@
       <c r="G536" s="2"/>
       <c r="H536" s="2"/>
       <c r="I536" s="5" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="J536" s="5"/>
       <c r="K536" s="2"/>
@@ -25293,7 +25293,7 @@
         <v>1768</v>
       </c>
       <c r="I537" s="5" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="J537" s="5"/>
       <c r="K537" s="2"/>
@@ -25322,7 +25322,7 @@
         <v>1770</v>
       </c>
       <c r="I538" s="5" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="J538" s="5"/>
       <c r="K538" s="2"/>
@@ -25351,7 +25351,7 @@
         <v>1772</v>
       </c>
       <c r="I539" s="5" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="J539" s="5"/>
       <c r="K539" s="2"/>
@@ -25436,7 +25436,7 @@
         <v>920</v>
       </c>
       <c r="I542" s="5" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="J542" s="5"/>
       <c r="K542" s="2"/>
@@ -25492,7 +25492,7 @@
         <v>1779</v>
       </c>
       <c r="I544" s="5" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
       <c r="J544" s="5"/>
       <c r="K544" s="2"/>
@@ -25548,7 +25548,7 @@
         <v>1783</v>
       </c>
       <c r="I546" s="5" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
       <c r="J546" s="5"/>
       <c r="K546" s="2"/>
@@ -25586,7 +25586,7 @@
       <c r="R547" s="2"/>
       <c r="S547" s="2"/>
     </row>
-    <row r="548" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A548" s="2" t="s">
         <v>608</v>
       </c>
@@ -25627,7 +25627,7 @@
       <c r="G549" s="2"/>
       <c r="H549" s="2"/>
       <c r="I549" s="5" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
       <c r="J549" s="5"/>
       <c r="K549" s="2"/>
@@ -25656,7 +25656,7 @@
         <v>284</v>
       </c>
       <c r="I550" s="5" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="J550" s="5"/>
       <c r="K550" s="2"/>
@@ -25698,7 +25698,7 @@
       <c r="R551" s="2"/>
       <c r="S551" s="2"/>
     </row>
-    <row r="552" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A552" s="2" t="s">
         <v>613</v>
       </c>
@@ -25741,7 +25741,7 @@
         <v>1790</v>
       </c>
       <c r="I553" s="5" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="J553" s="5"/>
       <c r="K553" s="2"/>
@@ -25772,7 +25772,7 @@
         <v>1541</v>
       </c>
       <c r="I554" s="5" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="J554" s="5"/>
       <c r="K554" s="2"/>
@@ -25828,7 +25828,7 @@
         <v>1794</v>
       </c>
       <c r="I556" s="5" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="J556" s="5"/>
       <c r="K556" s="2"/>
@@ -25855,7 +25855,7 @@
       <c r="G557" s="2"/>
       <c r="H557" s="2"/>
       <c r="I557" s="5" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="J557" s="5"/>
       <c r="K557" s="2"/>
@@ -25913,7 +25913,7 @@
         <v>521</v>
       </c>
       <c r="I559" s="5" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="J559" s="5"/>
       <c r="K559" s="2"/>
@@ -25996,7 +25996,7 @@
         <v>1801</v>
       </c>
       <c r="I562" s="5" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="J562" s="5"/>
       <c r="K562" s="2"/>
@@ -26009,7 +26009,7 @@
       <c r="R562" s="2"/>
       <c r="S562" s="2"/>
     </row>
-    <row r="563" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A563" s="2" t="s">
         <v>626</v>
       </c>
@@ -26054,7 +26054,7 @@
         <v>521</v>
       </c>
       <c r="I564" s="5" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="J564" s="5"/>
       <c r="K564" s="2"/>
@@ -26083,7 +26083,7 @@
         <v>1804</v>
       </c>
       <c r="I565" s="5" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
       <c r="J565" s="5"/>
       <c r="K565" s="2"/>
@@ -26114,7 +26114,7 @@
         <v>1158</v>
       </c>
       <c r="I566" s="5" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
       <c r="J566" s="5"/>
       <c r="K566" s="2"/>
@@ -26147,10 +26147,10 @@
         <v>1807</v>
       </c>
       <c r="I567" s="5" t="s">
+        <v>2413</v>
+      </c>
+      <c r="J567" s="5" t="s">
         <v>2414</v>
-      </c>
-      <c r="J567" s="5" t="s">
-        <v>2415</v>
       </c>
       <c r="K567" s="2"/>
       <c r="L567" s="2"/>
@@ -26232,7 +26232,7 @@
         <v>510</v>
       </c>
       <c r="I570" s="5" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="J570" s="5"/>
       <c r="K570" s="2"/>
@@ -26313,7 +26313,7 @@
       <c r="G573" s="2"/>
       <c r="H573" s="2"/>
       <c r="I573" s="5" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="J573" s="5"/>
       <c r="K573" s="2"/>
@@ -26396,10 +26396,10 @@
       <c r="G576" s="2"/>
       <c r="H576" s="2"/>
       <c r="I576" s="5" t="s">
+        <v>2417</v>
+      </c>
+      <c r="J576" s="5" t="s">
         <v>2418</v>
-      </c>
-      <c r="J576" s="5" t="s">
-        <v>2419</v>
       </c>
       <c r="K576" s="2"/>
       <c r="L576" s="2"/>
@@ -26427,7 +26427,7 @@
       <c r="G577" s="2"/>
       <c r="H577" s="2"/>
       <c r="I577" s="5" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="J577" s="5"/>
       <c r="K577" s="2" t="s">
@@ -26485,7 +26485,7 @@
         <v>1824</v>
       </c>
       <c r="I579" s="5" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="J579" s="5"/>
       <c r="K579" s="2"/>
@@ -26539,7 +26539,7 @@
         <v>1827</v>
       </c>
       <c r="I581" s="5" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="J581" s="5"/>
       <c r="K581" s="2"/>
@@ -26568,7 +26568,7 @@
         <v>1829</v>
       </c>
       <c r="I582" s="5" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="J582" s="5"/>
       <c r="K582" s="2"/>
@@ -26597,7 +26597,7 @@
         <v>1831</v>
       </c>
       <c r="I583" s="5" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="J583" s="5"/>
       <c r="K583" s="2"/>
@@ -26626,7 +26626,7 @@
         <v>521</v>
       </c>
       <c r="I584" s="5" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="J584" s="5"/>
       <c r="K584" s="2"/>
@@ -26711,7 +26711,7 @@
         <v>1086</v>
       </c>
       <c r="I587" s="5" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="J587" s="5"/>
       <c r="K587" s="2"/>
@@ -26740,11 +26740,11 @@
       <c r="G588" s="2"/>
       <c r="H588" s="2"/>
       <c r="I588" s="5" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="J588" s="5"/>
       <c r="K588" s="2" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="L588" s="2"/>
       <c r="M588" s="2"/>
@@ -26771,7 +26771,7 @@
         <v>1838</v>
       </c>
       <c r="I589" s="5" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="J589" s="5"/>
       <c r="K589" s="2"/>
@@ -26798,10 +26798,10 @@
       <c r="G590" s="2"/>
       <c r="H590" s="2"/>
       <c r="I590" s="5" t="s">
+        <v>2428</v>
+      </c>
+      <c r="J590" s="5" t="s">
         <v>2429</v>
-      </c>
-      <c r="J590" s="5" t="s">
-        <v>2430</v>
       </c>
       <c r="K590" s="2"/>
       <c r="L590" s="2"/>
@@ -26829,7 +26829,7 @@
       <c r="G591" s="2"/>
       <c r="H591" s="2"/>
       <c r="I591" s="5" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="J591" s="5"/>
       <c r="K591" s="2"/>
@@ -26856,7 +26856,7 @@
       <c r="G592" s="2"/>
       <c r="H592" s="2"/>
       <c r="I592" s="5" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="J592" s="5"/>
       <c r="K592" s="2"/>
@@ -26885,7 +26885,7 @@
         <v>375</v>
       </c>
       <c r="I593" s="5" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="J593" s="5"/>
       <c r="K593" s="2"/>
@@ -26914,7 +26914,7 @@
         <v>1844</v>
       </c>
       <c r="I594" s="5" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="J594" s="5"/>
       <c r="K594" s="2"/>
@@ -26941,7 +26941,7 @@
       <c r="G595" s="2"/>
       <c r="H595" s="2"/>
       <c r="I595" s="5" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="J595" s="5"/>
       <c r="K595" s="2"/>
@@ -27047,7 +27047,7 @@
         <v>1850</v>
       </c>
       <c r="I599" s="5" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="J599" s="5"/>
       <c r="K599" s="2"/>
@@ -27076,7 +27076,7 @@
         <v>1852</v>
       </c>
       <c r="I600" s="5" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
       <c r="J600" s="5"/>
       <c r="K600" s="2"/>
@@ -27103,7 +27103,7 @@
       <c r="G601" s="2"/>
       <c r="H601" s="2"/>
       <c r="I601" s="5" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="J601" s="5"/>
       <c r="K601" s="2"/>
@@ -27159,7 +27159,7 @@
         <v>1725</v>
       </c>
       <c r="I603" s="5" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="J603" s="5"/>
       <c r="K603" s="2"/>
@@ -27215,7 +27215,7 @@
         <v>1860</v>
       </c>
       <c r="I605" s="5" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="J605" s="5"/>
       <c r="K605" s="2"/>
@@ -27246,7 +27246,7 @@
         <v>911</v>
       </c>
       <c r="I606" s="5" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="J606" s="5"/>
       <c r="K606" s="2"/>
@@ -27302,10 +27302,10 @@
       <c r="G608" s="2"/>
       <c r="H608" s="2"/>
       <c r="I608" s="5" t="s">
+        <v>2441</v>
+      </c>
+      <c r="J608" s="5" t="s">
         <v>2442</v>
-      </c>
-      <c r="J608" s="5" t="s">
-        <v>2443</v>
       </c>
       <c r="K608" s="2"/>
       <c r="L608" s="2"/>
@@ -27335,7 +27335,7 @@
         <v>1855</v>
       </c>
       <c r="I609" s="5" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="J609" s="5"/>
       <c r="K609" s="2"/>
@@ -27418,7 +27418,7 @@
         <v>1870</v>
       </c>
       <c r="I612" s="5" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="J612" s="5"/>
       <c r="K612" s="2"/>
@@ -27447,7 +27447,7 @@
         <v>1872</v>
       </c>
       <c r="I613" s="5" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="J613" s="5"/>
       <c r="K613" s="2"/>
@@ -27474,7 +27474,7 @@
       <c r="G614" s="2"/>
       <c r="H614" s="2"/>
       <c r="I614" s="5" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="J614" s="5"/>
       <c r="K614" s="2"/>
@@ -27532,7 +27532,7 @@
         <v>1876</v>
       </c>
       <c r="I616" s="5" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="J616" s="5"/>
       <c r="K616" s="2"/>
@@ -27588,7 +27588,7 @@
         <v>1880</v>
       </c>
       <c r="I618" s="5" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="J618" s="5"/>
       <c r="K618" s="2"/>
@@ -27617,10 +27617,10 @@
         <v>1074</v>
       </c>
       <c r="I619" s="5" t="s">
+        <v>2449</v>
+      </c>
+      <c r="J619" s="5" t="s">
         <v>2450</v>
-      </c>
-      <c r="J619" s="5" t="s">
-        <v>2451</v>
       </c>
       <c r="K619" s="2"/>
       <c r="L619" s="2"/>
@@ -27673,7 +27673,7 @@
       <c r="G621" s="2"/>
       <c r="H621" s="2"/>
       <c r="I621" s="5" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="J621" s="5"/>
       <c r="K621" s="2"/>
@@ -27686,7 +27686,7 @@
       <c r="R621" s="2"/>
       <c r="S621" s="2"/>
     </row>
-    <row r="622" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A622" s="2" t="s">
         <v>693</v>
       </c>
@@ -27731,7 +27731,7 @@
         <v>1885</v>
       </c>
       <c r="I623" s="5" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="J623" s="5"/>
       <c r="K623" s="2"/>
@@ -27820,7 +27820,7 @@
         <v>1086</v>
       </c>
       <c r="I626" s="5" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="J626" s="5"/>
       <c r="K626" s="2"/>
@@ -27880,10 +27880,10 @@
         <v>1888</v>
       </c>
       <c r="I628" s="5" t="s">
+        <v>2454</v>
+      </c>
+      <c r="J628" s="5" t="s">
         <v>2455</v>
-      </c>
-      <c r="J628" s="5" t="s">
-        <v>2456</v>
       </c>
       <c r="K628" s="2" t="s">
         <v>1086</v>
@@ -27911,7 +27911,7 @@
       <c r="G629" s="2"/>
       <c r="H629" s="2"/>
       <c r="I629" s="5" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
       <c r="J629" s="5"/>
       <c r="K629" s="2"/>
@@ -27940,7 +27940,7 @@
         <v>1894</v>
       </c>
       <c r="I630" s="5" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="J630" s="5"/>
       <c r="K630" s="2"/>
@@ -28102,10 +28102,10 @@
         <v>1086</v>
       </c>
       <c r="I636" s="5" t="s">
+        <v>2458</v>
+      </c>
+      <c r="J636" s="5" t="s">
         <v>2459</v>
-      </c>
-      <c r="J636" s="5" t="s">
-        <v>2460</v>
       </c>
       <c r="K636" s="2"/>
       <c r="L636" s="2"/>
@@ -28160,10 +28160,10 @@
         <v>1686</v>
       </c>
       <c r="I638" s="5" t="s">
+        <v>2460</v>
+      </c>
+      <c r="J638" s="5" t="s">
         <v>2461</v>
-      </c>
-      <c r="J638" s="5" t="s">
-        <v>2462</v>
       </c>
       <c r="K638" s="2"/>
       <c r="L638" s="2"/>
@@ -28191,10 +28191,10 @@
         <v>1906</v>
       </c>
       <c r="I639" s="5" t="s">
+        <v>2462</v>
+      </c>
+      <c r="J639" s="5" t="s">
         <v>2463</v>
-      </c>
-      <c r="J639" s="5" t="s">
-        <v>2464</v>
       </c>
       <c r="K639" s="2"/>
       <c r="L639" s="2"/>
@@ -28249,10 +28249,10 @@
         <v>1909</v>
       </c>
       <c r="I641" s="5" t="s">
+        <v>2464</v>
+      </c>
+      <c r="J641" s="5" t="s">
         <v>2465</v>
-      </c>
-      <c r="J641" s="5" t="s">
-        <v>2466</v>
       </c>
       <c r="K641" s="2"/>
       <c r="L641" s="2"/>
@@ -28386,7 +28386,7 @@
       <c r="G646" s="2"/>
       <c r="H646" s="2"/>
       <c r="I646" s="5" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="J646" s="5"/>
       <c r="K646" s="2"/>
@@ -28446,7 +28446,7 @@
         <v>1316</v>
       </c>
       <c r="I648" s="5" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="J648" s="5"/>
       <c r="K648" s="2"/>
@@ -28473,7 +28473,7 @@
       <c r="G649" s="2"/>
       <c r="H649" s="2"/>
       <c r="I649" s="5" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="J649" s="5"/>
       <c r="K649" s="2"/>
@@ -28504,11 +28504,11 @@
         <v>1920</v>
       </c>
       <c r="I650" s="5" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="J650" s="5"/>
       <c r="K650" s="2" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
       <c r="L650" s="2"/>
       <c r="M650" s="2"/>
@@ -28533,7 +28533,7 @@
       <c r="G651" s="2"/>
       <c r="H651" s="2"/>
       <c r="I651" s="5" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="J651" s="5"/>
       <c r="K651" s="2"/>
@@ -28560,7 +28560,7 @@
       <c r="G652" s="2"/>
       <c r="H652" s="2"/>
       <c r="I652" s="5" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="J652" s="5"/>
       <c r="K652" s="2"/>
@@ -28589,7 +28589,7 @@
       <c r="G653" s="2"/>
       <c r="H653" s="2"/>
       <c r="I653" s="5" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
       <c r="J653" s="5"/>
       <c r="K653" s="2"/>
@@ -28697,7 +28697,7 @@
       <c r="G657" s="2"/>
       <c r="H657" s="2"/>
       <c r="I657" s="5" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="J657" s="5"/>
       <c r="K657" s="2"/>
@@ -28724,7 +28724,7 @@
       <c r="G658" s="2"/>
       <c r="H658" s="2"/>
       <c r="I658" s="5" t="s">
-        <v>2474</v>
+        <v>2473</v>
       </c>
       <c r="J658" s="5"/>
       <c r="K658" s="2"/>
@@ -28811,7 +28811,7 @@
         <v>875</v>
       </c>
       <c r="I661" s="5" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="J661" s="5"/>
       <c r="K661" s="2"/>
@@ -28894,7 +28894,7 @@
       <c r="G664" s="2"/>
       <c r="H664" s="2"/>
       <c r="I664" s="5" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="J664" s="5"/>
       <c r="K664" s="2"/>
@@ -29056,7 +29056,7 @@
         <v>1949</v>
       </c>
       <c r="I670" s="5" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="J670" s="5"/>
       <c r="K670" s="2"/>
@@ -29085,7 +29085,7 @@
         <v>1951</v>
       </c>
       <c r="I671" s="5" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="J671" s="5"/>
       <c r="K671" s="2"/>
@@ -29114,7 +29114,7 @@
         <v>1794</v>
       </c>
       <c r="I672" s="5" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="J672" s="5"/>
       <c r="K672" s="2"/>
@@ -29143,7 +29143,7 @@
         <v>1954</v>
       </c>
       <c r="I673" s="5" t="s">
-        <v>2480</v>
+        <v>2479</v>
       </c>
       <c r="J673" s="5"/>
       <c r="K673" s="2"/>
@@ -29199,7 +29199,7 @@
         <v>1957</v>
       </c>
       <c r="I675" s="5" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
       <c r="J675" s="5"/>
       <c r="K675" s="2"/>
@@ -29228,10 +29228,10 @@
         <v>1959</v>
       </c>
       <c r="I676" s="5" t="s">
+        <v>2481</v>
+      </c>
+      <c r="J676" s="5" t="s">
         <v>2482</v>
-      </c>
-      <c r="J676" s="5" t="s">
-        <v>2483</v>
       </c>
       <c r="K676" s="2"/>
       <c r="L676" s="2"/>
@@ -29315,7 +29315,7 @@
         <v>1965</v>
       </c>
       <c r="I679" s="5" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="J679" s="5"/>
       <c r="K679" s="2"/>
@@ -29344,7 +29344,7 @@
       <c r="G680" s="2"/>
       <c r="H680" s="2"/>
       <c r="I680" s="5" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="J680" s="5"/>
       <c r="K680" s="2"/>
@@ -29427,7 +29427,7 @@
         <v>1972</v>
       </c>
       <c r="I683" s="5" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="J683" s="5"/>
       <c r="K683" s="2"/>
@@ -29485,7 +29485,7 @@
         <v>1977</v>
       </c>
       <c r="I685" s="5" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="J685" s="5"/>
       <c r="K685" s="2"/>
@@ -29514,7 +29514,7 @@
         <v>1979</v>
       </c>
       <c r="I686" s="5" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="J686" s="5"/>
       <c r="K686" s="2"/>
@@ -29599,7 +29599,7 @@
       <c r="G689" s="2"/>
       <c r="H689" s="2"/>
       <c r="I689" s="5" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="J689" s="5"/>
       <c r="K689" s="2"/>
@@ -29626,7 +29626,7 @@
       <c r="G690" s="2"/>
       <c r="H690" s="2"/>
       <c r="I690" s="5" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="J690" s="5"/>
       <c r="K690" s="2"/>
@@ -29653,7 +29653,7 @@
       <c r="G691" s="2"/>
       <c r="H691" s="2"/>
       <c r="I691" s="5" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
       <c r="J691" s="5"/>
       <c r="K691" s="2" t="s">
@@ -29684,10 +29684,10 @@
         <v>1987</v>
       </c>
       <c r="I692" s="5" t="s">
+        <v>2491</v>
+      </c>
+      <c r="J692" s="5" t="s">
         <v>2492</v>
-      </c>
-      <c r="J692" s="5" t="s">
-        <v>2493</v>
       </c>
       <c r="K692" s="2"/>
       <c r="L692" s="2"/>
@@ -29765,7 +29765,7 @@
       <c r="G695" s="2"/>
       <c r="H695" s="2"/>
       <c r="I695" s="5" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="J695" s="5"/>
       <c r="K695" s="2"/>
@@ -29823,7 +29823,7 @@
         <v>1994</v>
       </c>
       <c r="I697" s="5" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
       <c r="J697" s="5"/>
       <c r="K697" s="2"/>
@@ -29879,7 +29879,7 @@
         <v>1510</v>
       </c>
       <c r="I699" s="5" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="J699" s="5"/>
       <c r="K699" s="2"/>
@@ -29910,7 +29910,7 @@
         <v>1999</v>
       </c>
       <c r="I700" s="5" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="J700" s="5"/>
       <c r="K700" s="2"/>
@@ -29941,7 +29941,7 @@
         <v>2001</v>
       </c>
       <c r="I701" s="5" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="J701" s="5"/>
       <c r="K701" s="2"/>
@@ -29970,7 +29970,7 @@
       <c r="G702" s="2"/>
       <c r="H702" s="2"/>
       <c r="I702" s="5" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
       <c r="J702" s="5"/>
       <c r="K702" s="2" t="s">
@@ -30001,7 +30001,7 @@
       <c r="G703" s="2"/>
       <c r="H703" s="2"/>
       <c r="I703" s="5" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="J703" s="5"/>
       <c r="K703" s="2"/>
@@ -30030,7 +30030,7 @@
         <v>2005</v>
       </c>
       <c r="I704" s="5" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="J704" s="5"/>
       <c r="K704" s="2"/>
@@ -30059,7 +30059,7 @@
         <v>2007</v>
       </c>
       <c r="I705" s="5" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="J705" s="5"/>
       <c r="K705" s="2"/>
@@ -30088,7 +30088,7 @@
       <c r="G706" s="2"/>
       <c r="H706" s="2"/>
       <c r="I706" s="5" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="J706" s="5"/>
       <c r="K706" s="2"/>
@@ -30115,7 +30115,7 @@
       <c r="G707" s="2"/>
       <c r="H707" s="2"/>
       <c r="I707" s="5" t="s">
-        <v>2504</v>
+        <v>2503</v>
       </c>
       <c r="J707" s="5"/>
       <c r="K707" s="2"/>
@@ -30144,7 +30144,7 @@
         <v>2011</v>
       </c>
       <c r="I708" s="5" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="J708" s="5"/>
       <c r="K708" s="2"/>
@@ -30198,7 +30198,7 @@
       <c r="G710" s="2"/>
       <c r="H710" s="2"/>
       <c r="I710" s="5" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="J710" s="5"/>
       <c r="K710" s="2"/>
@@ -30227,10 +30227,10 @@
         <v>375</v>
       </c>
       <c r="I711" s="5" t="s">
+        <v>2506</v>
+      </c>
+      <c r="J711" s="5" t="s">
         <v>2507</v>
-      </c>
-      <c r="J711" s="5" t="s">
-        <v>2508</v>
       </c>
       <c r="K711" s="2"/>
       <c r="L711" s="2"/>
@@ -30256,7 +30256,7 @@
       <c r="G712" s="2"/>
       <c r="H712" s="2"/>
       <c r="I712" s="5" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
       <c r="J712" s="5"/>
       <c r="K712" s="2"/>
@@ -30316,7 +30316,7 @@
         <v>1725</v>
       </c>
       <c r="I714" s="5" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="J714" s="5"/>
       <c r="K714" s="2"/>
@@ -30347,7 +30347,7 @@
         <v>2019</v>
       </c>
       <c r="I715" s="5" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="J715" s="5"/>
       <c r="K715" s="2"/>
@@ -30401,7 +30401,7 @@
         <v>2022</v>
       </c>
       <c r="I717" s="5" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="J717" s="5"/>
       <c r="K717" s="2"/>
@@ -30443,7 +30443,7 @@
       <c r="R718" s="2"/>
       <c r="S718" s="2"/>
     </row>
-    <row r="719" spans="1:19" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A719" s="2" t="s">
         <v>804</v>
       </c>
@@ -30542,7 +30542,7 @@
       <c r="G722" s="2"/>
       <c r="H722" s="2"/>
       <c r="I722" s="5" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="J722" s="5"/>
       <c r="K722" s="2"/>
@@ -30758,7 +30758,7 @@
         <v>2040</v>
       </c>
       <c r="I730" s="5" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="J730" s="5"/>
       <c r="K730" s="2"/>
@@ -30787,7 +30787,7 @@
         <v>284</v>
       </c>
       <c r="I731" s="5" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="J731" s="5"/>
       <c r="K731" s="2"/>
@@ -30845,7 +30845,7 @@
         <v>2045</v>
       </c>
       <c r="I733" s="5" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="J733" s="5"/>
       <c r="K733" s="2"/>
@@ -30949,7 +30949,7 @@
         <v>2049</v>
       </c>
       <c r="I737" s="5" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="J737" s="5"/>
       <c r="K737" s="2"/>
@@ -31038,7 +31038,7 @@
         <v>1196</v>
       </c>
       <c r="I740" s="5" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="J740" s="5"/>
       <c r="K740" s="2" t="s">
@@ -31096,7 +31096,7 @@
         <v>2058</v>
       </c>
       <c r="I742" s="5" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
       <c r="J742" s="5"/>
       <c r="K742" s="2"/>
@@ -31125,7 +31125,7 @@
         <v>2060</v>
       </c>
       <c r="I743" s="5" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="J743" s="5"/>
       <c r="K743" s="2"/>
@@ -31154,7 +31154,7 @@
         <v>2062</v>
       </c>
       <c r="I744" s="5" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="J744" s="5"/>
       <c r="K744" s="2"/>
@@ -31196,7 +31196,7 @@
       <c r="R745" s="2"/>
       <c r="S745" s="2"/>
     </row>
-    <row r="746" spans="1:19" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A746" s="2" t="s">
         <v>798</v>
       </c>
@@ -31239,7 +31239,7 @@
       <c r="G747" s="2"/>
       <c r="H747" s="2"/>
       <c r="I747" s="5" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="J747" s="5"/>
       <c r="K747" s="2"/>
@@ -31322,7 +31322,7 @@
       <c r="G750" s="2"/>
       <c r="H750" s="2"/>
       <c r="I750" s="5" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
       <c r="J750" s="5"/>
       <c r="K750" s="2"/>
@@ -31488,7 +31488,7 @@
         <v>2079</v>
       </c>
       <c r="I756" s="5" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="J756" s="5"/>
       <c r="K756" s="2"/>

--- a/begrippen-nlsbb.xlsx
+++ b/begrippen-nlsbb.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\apps\github\IMProRail\spoorse-begrippen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A4D7E21-B64F-4800-9207-D52B07767D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F0D62C3-DFBE-4BEB-8E20-04159030BC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-3255" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{647FEE87-BCEB-4E3A-ABA6-7EA97748041A}"/>
   </bookViews>
@@ -7066,9 +7066,6 @@
     <t>Bij aankomst gaat 12-JAN-1998 512 over in vertrek van 12-JAN-1998 517
 M.b.v. de bewegingmaterieelrelatie worden de “gerelateerde” rijwegen bepaald.
 De materieelrelatie van het soort overgaan wordt ook wel materieelovergang genoemd. Let op het ver-schil met een materieeldienstovergang: daarbij is de overgang van materieel over de daggrens (d.w.z. op twee verschillende patroon/verkeers –dagen) vastgelegd.</t>
-  </si>
-  <si>
-    <t>Voorbeelden van bewegingsactiviteiten: Vertrek in Asd spoor 5b om 7:23, Aankomst in Asa spoor 4 om 7:30, Vertrek in Asa spoor 4 om 7:31, Aankomst in Ut spoor 4 om 7:50, …. etc. van beweging (trein) 3023</t>
   </si>
   <si>
     <t>Er zijn drie soorten bijzondere voorvallen.
@@ -9208,6 +9205,13 @@
 •	In eerste instantie een administratief bestaan, nog ontkoppeld van het fysieke materieel dat erbij betrokken is: dus alleen de modelmatige afbeelding van de verplaatsing over de railinfrastruc-tuur en de materieeleenheden slechts o.b.v. een soortaanduiding;
 •	Daarna een administratief bestaan, maar vanuit een materieelplan gekoppeld aan materieel;
 •	Tenslotte (tijdens de uitvoering) de fysieke beweging buiten op de infra, onder regie van het in-fraplan en het materieelplan, met concrete spoorvoertuig(en).</t>
+  </si>
+  <si>
+    <t>Voorbeelden van bewegingsactiviteiten: 
+* Vertrek in Asd spoor 5b om 7:23, 
+* Aankomst in Asa spoor 4 om 7:30, 
+* Vertrek in Asa spoor 4 om 7:31, 
+* Aankomst in Ut spoor 4 om 7:50, …. etc. van beweging (trein) 3023</t>
   </si>
 </sst>
 </file>
@@ -9893,61 +9897,61 @@
   <sheetData>
     <row r="1" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>2525</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>2526</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2527</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2528</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>2529</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>2530</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>2531</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>2532</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="4" t="s">
         <v>2533</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>2534</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="1" t="s">
         <v>2535</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>2536</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>2537</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>2538</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>2539</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>2540</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>2541</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>2542</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>2543</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>2544</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="38.25" x14ac:dyDescent="0.2">
@@ -10080,7 +10084,7 @@
         <v>872</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="2"/>
@@ -12568,7 +12572,7 @@
         <v>1025</v>
       </c>
       <c r="I92" s="5" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="J92" s="5"/>
       <c r="K92" s="2"/>
@@ -12631,7 +12635,7 @@
       </c>
       <c r="I94" s="5"/>
       <c r="J94" s="5" t="s">
-        <v>2144</v>
+        <v>2546</v>
       </c>
       <c r="K94" s="2"/>
       <c r="L94" s="2"/>
@@ -12771,7 +12775,7 @@
         <v>1041</v>
       </c>
       <c r="I99" s="5" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="J99" s="5"/>
       <c r="K99" s="2"/>
@@ -12803,7 +12807,7 @@
       </c>
       <c r="I100" s="5"/>
       <c r="J100" s="5" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="K100" s="2"/>
       <c r="L100" s="2"/>
@@ -12831,7 +12835,7 @@
         <v>1045</v>
       </c>
       <c r="I101" s="5" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="J101" s="5"/>
       <c r="K101" s="2"/>
@@ -12891,7 +12895,7 @@
         <v>1049</v>
       </c>
       <c r="I103" s="5" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="J103" s="5"/>
       <c r="K103" s="2"/>
@@ -12980,7 +12984,7 @@
         <v>1056</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="J106" s="5"/>
       <c r="K106" s="2"/>
@@ -13034,7 +13038,7 @@
         <v>1058</v>
       </c>
       <c r="I108" s="5" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="J108" s="5"/>
       <c r="K108" s="2"/>
@@ -13090,10 +13094,10 @@
         <v>1060</v>
       </c>
       <c r="I110" s="5" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="J110" s="5" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="K110" s="2"/>
       <c r="L110" s="2"/>
@@ -13121,7 +13125,7 @@
         <v>1063</v>
       </c>
       <c r="I111" s="5" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="J111" s="5"/>
       <c r="K111" s="2"/>
@@ -13150,10 +13154,10 @@
         <v>1065</v>
       </c>
       <c r="I112" s="5" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="J112" s="5" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="K112" s="2"/>
       <c r="L112" s="2"/>
@@ -13181,7 +13185,7 @@
         <v>1067</v>
       </c>
       <c r="I113" s="5" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="J113" s="5"/>
       <c r="K113" s="2"/>
@@ -13239,7 +13243,7 @@
         <v>510</v>
       </c>
       <c r="I115" s="5" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="J115" s="5"/>
       <c r="K115" s="2"/>
@@ -13297,7 +13301,7 @@
         <v>1075</v>
       </c>
       <c r="I117" s="5" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="J117" s="5"/>
       <c r="K117" s="2"/>
@@ -13357,7 +13361,7 @@
         <v>1079</v>
       </c>
       <c r="I119" s="5" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="J119" s="5"/>
       <c r="K119" s="2"/>
@@ -13417,7 +13421,7 @@
         <v>1082</v>
       </c>
       <c r="I121" s="5" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="J121" s="5"/>
       <c r="K121" s="2"/>
@@ -13446,7 +13450,7 @@
         <v>1084</v>
       </c>
       <c r="I122" s="5" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="J122" s="5"/>
       <c r="K122" s="2"/>
@@ -13475,7 +13479,7 @@
         <v>1086</v>
       </c>
       <c r="I123" s="5" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="J123" s="5"/>
       <c r="K123" s="2"/>
@@ -13505,7 +13509,7 @@
       <c r="H124" s="2"/>
       <c r="I124" s="5"/>
       <c r="J124" s="5" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="K124" s="2"/>
       <c r="L124" s="2"/>
@@ -13589,7 +13593,7 @@
         <v>1093</v>
       </c>
       <c r="I127" s="5" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="J127" s="5"/>
       <c r="K127" s="2"/>
@@ -13701,7 +13705,7 @@
         <v>1099</v>
       </c>
       <c r="I131" s="5" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="J131" s="5"/>
       <c r="K131" s="2"/>
@@ -13732,7 +13736,7 @@
         <v>1102</v>
       </c>
       <c r="I132" s="5" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="J132" s="5"/>
       <c r="K132" s="2"/>
@@ -13790,7 +13794,7 @@
         <v>1106</v>
       </c>
       <c r="I134" s="5" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="J134" s="5"/>
       <c r="K134" s="2"/>
@@ -13819,7 +13823,7 @@
         <v>1108</v>
       </c>
       <c r="I135" s="5" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="J135" s="5"/>
       <c r="K135" s="2"/>
@@ -13902,7 +13906,7 @@
         <v>1113</v>
       </c>
       <c r="I138" s="5" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="J138" s="5"/>
       <c r="K138" s="2"/>
@@ -13987,7 +13991,7 @@
         <v>1118</v>
       </c>
       <c r="I141" s="5" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="J141" s="5"/>
       <c r="K141" s="2"/>
@@ -14043,7 +14047,7 @@
         <v>1122</v>
       </c>
       <c r="I143" s="5" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="J143" s="5"/>
       <c r="K143" s="2"/>
@@ -14151,7 +14155,7 @@
         <v>1129</v>
       </c>
       <c r="I147" s="5" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="J147" s="5"/>
       <c r="K147" s="2"/>
@@ -14180,7 +14184,7 @@
         <v>1131</v>
       </c>
       <c r="I148" s="5" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="J148" s="5"/>
       <c r="K148" s="2"/>
@@ -14236,7 +14240,7 @@
         <v>1135</v>
       </c>
       <c r="I150" s="5" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="J150" s="5"/>
       <c r="K150" s="2"/>
@@ -14265,10 +14269,10 @@
         <v>1137</v>
       </c>
       <c r="I151" s="5" t="s">
+        <v>2171</v>
+      </c>
+      <c r="J151" s="5" t="s">
         <v>2172</v>
-      </c>
-      <c r="J151" s="5" t="s">
-        <v>2173</v>
       </c>
       <c r="K151" s="2"/>
       <c r="L151" s="2"/>
@@ -14323,7 +14327,7 @@
         <v>1140</v>
       </c>
       <c r="I153" s="5" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="J153" s="5"/>
       <c r="K153" s="2"/>
@@ -14352,7 +14356,7 @@
         <v>1142</v>
       </c>
       <c r="I154" s="5" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="J154" s="5"/>
       <c r="K154" s="2"/>
@@ -14381,7 +14385,7 @@
         <v>1144</v>
       </c>
       <c r="I155" s="5" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="J155" s="5"/>
       <c r="K155" s="2"/>
@@ -14468,7 +14472,7 @@
         <v>1150</v>
       </c>
       <c r="I158" s="5" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="J158" s="5"/>
       <c r="K158" s="2"/>
@@ -14497,10 +14501,10 @@
         <v>1152</v>
       </c>
       <c r="I159" s="5" t="s">
+        <v>2177</v>
+      </c>
+      <c r="J159" s="5" t="s">
         <v>2178</v>
-      </c>
-      <c r="J159" s="5" t="s">
-        <v>2179</v>
       </c>
       <c r="K159" s="2"/>
       <c r="L159" s="2"/>
@@ -14528,7 +14532,7 @@
         <v>1154</v>
       </c>
       <c r="I160" s="5" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="J160" s="5"/>
       <c r="K160" s="2"/>
@@ -14557,7 +14561,7 @@
         <v>1156</v>
       </c>
       <c r="I161" s="5" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="J161" s="5"/>
       <c r="K161" s="2"/>
@@ -14640,7 +14644,7 @@
         <v>1160</v>
       </c>
       <c r="I164" s="5" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="J164" s="5"/>
       <c r="K164" s="2"/>
@@ -14671,7 +14675,7 @@
         <v>1163</v>
       </c>
       <c r="I165" s="5" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="J165" s="5"/>
       <c r="K165" s="2"/>
@@ -14729,7 +14733,7 @@
         <v>1167</v>
       </c>
       <c r="I167" s="5" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="J167" s="5"/>
       <c r="K167" s="2"/>
@@ -14810,7 +14814,7 @@
         <v>1172</v>
       </c>
       <c r="I170" s="5" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="J170" s="5"/>
       <c r="K170" s="2"/>
@@ -14839,7 +14843,7 @@
         <v>1174</v>
       </c>
       <c r="I171" s="5" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="J171" s="5"/>
       <c r="K171" s="2"/>
@@ -14897,7 +14901,7 @@
         <v>1178</v>
       </c>
       <c r="I173" s="5" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="J173" s="5"/>
       <c r="K173" s="2"/>
@@ -14924,7 +14928,7 @@
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
       <c r="I174" s="5" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="J174" s="5"/>
       <c r="K174" s="2"/>
@@ -14953,7 +14957,7 @@
         <v>1181</v>
       </c>
       <c r="I175" s="5" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="J175" s="5"/>
       <c r="K175" s="2"/>
@@ -14982,7 +14986,7 @@
         <v>1183</v>
       </c>
       <c r="I176" s="5" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="J176" s="5"/>
       <c r="K176" s="2"/>
@@ -15011,7 +15015,7 @@
         <v>1185</v>
       </c>
       <c r="I177" s="5" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="J177" s="5"/>
       <c r="K177" s="2"/>
@@ -15096,7 +15100,7 @@
         <v>1191</v>
       </c>
       <c r="I180" s="5" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="J180" s="5"/>
       <c r="K180" s="2"/>
@@ -15129,7 +15133,7 @@
         <v>1194</v>
       </c>
       <c r="I181" s="5" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="J181" s="5"/>
       <c r="K181" s="2"/>
@@ -15160,7 +15164,7 @@
         <v>1197</v>
       </c>
       <c r="I182" s="5" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="J182" s="5"/>
       <c r="K182" s="2"/>
@@ -15189,7 +15193,7 @@
       <c r="G183" s="2"/>
       <c r="H183" s="2"/>
       <c r="I183" s="5" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="J183" s="5"/>
       <c r="K183" s="2"/>
@@ -15249,7 +15253,7 @@
         <v>1203</v>
       </c>
       <c r="I185" s="5" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="J185" s="5"/>
       <c r="K185" s="2"/>
@@ -15307,7 +15311,7 @@
         <v>1206</v>
       </c>
       <c r="I187" s="5" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="J187" s="5"/>
       <c r="K187" s="2"/>
@@ -15367,7 +15371,7 @@
         <v>1209</v>
       </c>
       <c r="I189" s="5" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="J189" s="5"/>
       <c r="K189" s="2"/>
@@ -15398,7 +15402,7 @@
         <v>1212</v>
       </c>
       <c r="I190" s="5" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="J190" s="5"/>
       <c r="K190" s="2"/>
@@ -15429,7 +15433,7 @@
         <v>1214</v>
       </c>
       <c r="I191" s="5" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="J191" s="5"/>
       <c r="K191" s="2"/>
@@ -15458,7 +15462,7 @@
         <v>920</v>
       </c>
       <c r="I192" s="5" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="J192" s="5"/>
       <c r="K192" s="2"/>
@@ -15489,7 +15493,7 @@
         <v>1217</v>
       </c>
       <c r="I193" s="5" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="J193" s="5"/>
       <c r="K193" s="2"/>
@@ -15518,7 +15522,7 @@
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
       <c r="I194" s="5" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="J194" s="5"/>
       <c r="K194" s="2"/>
@@ -15576,7 +15580,7 @@
         <v>1223</v>
       </c>
       <c r="I196" s="5" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="J196" s="5"/>
       <c r="K196" s="2"/>
@@ -15659,7 +15663,7 @@
         <v>1229</v>
       </c>
       <c r="I199" s="5" t="s">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="J199" s="5"/>
       <c r="K199" s="2"/>
@@ -15717,7 +15721,7 @@
         <v>1233</v>
       </c>
       <c r="I201" s="5" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="J201" s="5"/>
       <c r="K201" s="2"/>
@@ -15833,7 +15837,7 @@
         <v>1237</v>
       </c>
       <c r="I205" s="5" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="J205" s="5"/>
       <c r="K205" s="2"/>
@@ -15862,7 +15866,7 @@
         <v>1239</v>
       </c>
       <c r="I206" s="5" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="J206" s="5"/>
       <c r="K206" s="2"/>
@@ -15949,7 +15953,7 @@
         <v>1245</v>
       </c>
       <c r="I209" s="5" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="J209" s="5"/>
       <c r="K209" s="2"/>
@@ -15980,7 +15984,7 @@
         <v>1248</v>
       </c>
       <c r="I210" s="5" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="J210" s="5"/>
       <c r="K210" s="2"/>
@@ -16011,10 +16015,10 @@
         <v>1251</v>
       </c>
       <c r="I211" s="5" t="s">
+        <v>2209</v>
+      </c>
+      <c r="J211" s="5" t="s">
         <v>2210</v>
-      </c>
-      <c r="J211" s="5" t="s">
-        <v>2211</v>
       </c>
       <c r="K211" s="2"/>
       <c r="L211" s="2"/>
@@ -16040,7 +16044,7 @@
       <c r="G212" s="2"/>
       <c r="H212" s="2"/>
       <c r="I212" s="5" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="J212" s="5"/>
       <c r="K212" s="2"/>
@@ -16069,7 +16073,7 @@
         <v>944</v>
       </c>
       <c r="I213" s="5" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="J213" s="5"/>
       <c r="K213" s="2"/>
@@ -16127,7 +16131,7 @@
         <v>1196</v>
       </c>
       <c r="I215" s="5" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="J215" s="5"/>
       <c r="K215" s="2"/>
@@ -16156,10 +16160,10 @@
         <v>1258</v>
       </c>
       <c r="I216" s="5" t="s">
+        <v>2214</v>
+      </c>
+      <c r="J216" s="5" t="s">
         <v>2215</v>
-      </c>
-      <c r="J216" s="5" t="s">
-        <v>2216</v>
       </c>
       <c r="K216" s="2"/>
       <c r="L216" s="2"/>
@@ -16185,7 +16189,7 @@
       <c r="G217" s="2"/>
       <c r="H217" s="2"/>
       <c r="I217" s="5" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="J217" s="5"/>
       <c r="K217" s="2"/>
@@ -16246,7 +16250,7 @@
       </c>
       <c r="I219" s="5"/>
       <c r="J219" s="5" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="K219" s="2"/>
       <c r="L219" s="2"/>
@@ -16330,7 +16334,7 @@
         <v>1271</v>
       </c>
       <c r="I222" s="5" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="J222" s="5"/>
       <c r="K222" s="2"/>
@@ -16409,7 +16413,7 @@
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
       <c r="I225" s="5" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="J225" s="5"/>
       <c r="K225" s="2"/>
@@ -16440,7 +16444,7 @@
         <v>1101</v>
       </c>
       <c r="I226" s="5" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="J226" s="5"/>
       <c r="K226" s="2"/>
@@ -16471,7 +16475,7 @@
         <v>1278</v>
       </c>
       <c r="I227" s="5" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="J227" s="5"/>
       <c r="K227" s="2"/>
@@ -16498,7 +16502,7 @@
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
       <c r="I228" s="5" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="J228" s="5"/>
       <c r="K228" s="2"/>
@@ -16527,7 +16531,7 @@
       </c>
       <c r="H229" s="2"/>
       <c r="I229" s="5" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="J229" s="5"/>
       <c r="K229" s="2"/>
@@ -16558,7 +16562,7 @@
         <v>1284</v>
       </c>
       <c r="I230" s="5" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="J230" s="5"/>
       <c r="K230" s="2"/>
@@ -16647,7 +16651,7 @@
         <v>1289</v>
       </c>
       <c r="I233" s="5" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="J233" s="5"/>
       <c r="K233" s="2"/>
@@ -16761,7 +16765,7 @@
         <v>1296</v>
       </c>
       <c r="I237" s="5" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="J237" s="5"/>
       <c r="K237" s="2"/>
@@ -16790,7 +16794,7 @@
         <v>1298</v>
       </c>
       <c r="I238" s="5" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="J238" s="5"/>
       <c r="K238" s="2"/>
@@ -16873,7 +16877,7 @@
         <v>1304</v>
       </c>
       <c r="I241" s="5" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
       <c r="J241" s="5"/>
       <c r="K241" s="2"/>
@@ -16929,7 +16933,7 @@
         <v>1308</v>
       </c>
       <c r="I243" s="5" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="J243" s="5"/>
       <c r="K243" s="2"/>
@@ -16960,7 +16964,7 @@
         <v>1311</v>
       </c>
       <c r="I244" s="5" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="J244" s="5"/>
       <c r="K244" s="2"/>
@@ -16989,7 +16993,7 @@
         <v>1313</v>
       </c>
       <c r="I245" s="5" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="J245" s="5"/>
       <c r="K245" s="2"/>
@@ -17074,7 +17078,7 @@
         <v>1319</v>
       </c>
       <c r="I248" s="5" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="J248" s="5"/>
       <c r="K248" s="2"/>
@@ -17103,7 +17107,7 @@
         <v>1321</v>
       </c>
       <c r="I249" s="5" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="J249" s="5"/>
       <c r="K249" s="2"/>
@@ -17132,7 +17136,7 @@
       <c r="G250" s="2"/>
       <c r="H250" s="2"/>
       <c r="I250" s="5" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="J250" s="5"/>
       <c r="K250" s="2"/>
@@ -17161,7 +17165,7 @@
       <c r="G251" s="2"/>
       <c r="H251" s="2"/>
       <c r="I251" s="5" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="J251" s="5"/>
       <c r="K251" s="2"/>
@@ -17194,7 +17198,7 @@
         <v>1325</v>
       </c>
       <c r="I252" s="5" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="J252" s="5"/>
       <c r="K252" s="2"/>
@@ -17248,7 +17252,7 @@
         <v>1328</v>
       </c>
       <c r="I254" s="5" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="J254" s="5"/>
       <c r="K254" s="2"/>
@@ -17279,7 +17283,7 @@
         <v>1330</v>
       </c>
       <c r="I255" s="5" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="J255" s="5"/>
       <c r="K255" s="2"/>
@@ -17426,7 +17430,7 @@
         <v>1339</v>
       </c>
       <c r="I260" s="5" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="J260" s="5"/>
       <c r="K260" s="2"/>
@@ -17534,7 +17538,7 @@
         <v>1344</v>
       </c>
       <c r="I264" s="5" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="J264" s="5"/>
       <c r="K264" s="2"/>
@@ -17563,7 +17567,7 @@
         <v>1346</v>
       </c>
       <c r="I265" s="5" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="J265" s="5"/>
       <c r="K265" s="2"/>
@@ -17592,7 +17596,7 @@
         <v>1348</v>
       </c>
       <c r="I266" s="5" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="J266" s="5"/>
       <c r="K266" s="2"/>
@@ -17621,7 +17625,7 @@
         <v>1350</v>
       </c>
       <c r="I267" s="5" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="J267" s="5"/>
       <c r="K267" s="2"/>
@@ -17680,7 +17684,7 @@
       </c>
       <c r="I269" s="5"/>
       <c r="J269" s="5" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="K269" s="2"/>
       <c r="L269" s="2"/>
@@ -17791,7 +17795,7 @@
         <v>1363</v>
       </c>
       <c r="I273" s="5" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="J273" s="5"/>
       <c r="K273" s="2"/>
@@ -17820,10 +17824,10 @@
         <v>1365</v>
       </c>
       <c r="I274" s="5" t="s">
+        <v>2244</v>
+      </c>
+      <c r="J274" s="5" t="s">
         <v>2245</v>
-      </c>
-      <c r="J274" s="5" t="s">
-        <v>2246</v>
       </c>
       <c r="K274" s="2"/>
       <c r="L274" s="2"/>
@@ -17853,7 +17857,7 @@
         <v>1367</v>
       </c>
       <c r="I275" s="5" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="J275" s="5"/>
       <c r="K275" s="2"/>
@@ -17882,10 +17886,10 @@
         <v>1369</v>
       </c>
       <c r="I276" s="5" t="s">
+        <v>2247</v>
+      </c>
+      <c r="J276" s="5" t="s">
         <v>2248</v>
-      </c>
-      <c r="J276" s="5" t="s">
-        <v>2249</v>
       </c>
       <c r="K276" s="2"/>
       <c r="L276" s="2"/>
@@ -18125,7 +18129,7 @@
         <v>1379</v>
       </c>
       <c r="I285" s="5" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="J285" s="5"/>
       <c r="K285" s="2"/>
@@ -18208,7 +18212,7 @@
         <v>1385</v>
       </c>
       <c r="I288" s="5" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="J288" s="5"/>
       <c r="K288" s="2"/>
@@ -18239,7 +18243,7 @@
         <v>1388</v>
       </c>
       <c r="I289" s="5" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="J289" s="5"/>
       <c r="K289" s="2"/>
@@ -18372,7 +18376,7 @@
         <v>1395</v>
       </c>
       <c r="I294" s="5" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="J294" s="5"/>
       <c r="K294" s="2"/>
@@ -18430,7 +18434,7 @@
         <v>1398</v>
       </c>
       <c r="I296" s="5" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="J296" s="5"/>
       <c r="K296" s="2"/>
@@ -18459,7 +18463,7 @@
         <v>1400</v>
       </c>
       <c r="I297" s="5" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
       <c r="J297" s="5"/>
       <c r="K297" s="2"/>
@@ -18488,7 +18492,7 @@
         <v>1116</v>
       </c>
       <c r="I298" s="5" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="J298" s="5"/>
       <c r="K298" s="2"/>
@@ -18517,7 +18521,7 @@
         <v>1223</v>
       </c>
       <c r="I299" s="5" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="J299" s="5"/>
       <c r="K299" s="2"/>
@@ -18546,7 +18550,7 @@
         <v>1404</v>
       </c>
       <c r="I300" s="5" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="J300" s="5"/>
       <c r="K300" s="2"/>
@@ -18579,7 +18583,7 @@
         <v>1407</v>
       </c>
       <c r="I301" s="5" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="J301" s="5"/>
       <c r="K301" s="2"/>
@@ -18610,7 +18614,7 @@
         <v>1410</v>
       </c>
       <c r="I302" s="5" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="J302" s="5"/>
       <c r="K302" s="2"/>
@@ -18668,7 +18672,7 @@
         <v>1414</v>
       </c>
       <c r="I304" s="5" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="J304" s="5"/>
       <c r="K304" s="2"/>
@@ -18724,7 +18728,7 @@
         <v>1418</v>
       </c>
       <c r="I306" s="5" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="J306" s="5"/>
       <c r="K306" s="2"/>
@@ -18780,10 +18784,10 @@
       <c r="G308" s="2"/>
       <c r="H308" s="2"/>
       <c r="I308" s="5" t="s">
+        <v>2262</v>
+      </c>
+      <c r="J308" s="5" t="s">
         <v>2263</v>
-      </c>
-      <c r="J308" s="5" t="s">
-        <v>2264</v>
       </c>
       <c r="K308" s="2"/>
       <c r="L308" s="2"/>
@@ -18813,7 +18817,7 @@
         <v>1423</v>
       </c>
       <c r="I309" s="5" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="J309" s="5"/>
       <c r="K309" s="2"/>
@@ -18842,7 +18846,7 @@
         <v>1425</v>
       </c>
       <c r="I310" s="5" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="J310" s="5"/>
       <c r="K310" s="2"/>
@@ -18898,7 +18902,7 @@
         <v>1428</v>
       </c>
       <c r="I312" s="5" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="J312" s="5"/>
       <c r="K312" s="2"/>
@@ -18925,7 +18929,7 @@
       <c r="G313" s="2"/>
       <c r="H313" s="2"/>
       <c r="I313" s="5" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="J313" s="5"/>
       <c r="K313" s="2"/>
@@ -18952,10 +18956,10 @@
       <c r="G314" s="2"/>
       <c r="H314" s="2"/>
       <c r="I314" s="5" t="s">
+        <v>2268</v>
+      </c>
+      <c r="J314" s="5" t="s">
         <v>2269</v>
-      </c>
-      <c r="J314" s="5" t="s">
-        <v>2270</v>
       </c>
       <c r="K314" s="2"/>
       <c r="L314" s="2"/>
@@ -18985,7 +18989,7 @@
         <v>1431</v>
       </c>
       <c r="I315" s="5" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="J315" s="5"/>
       <c r="K315" s="2"/>
@@ -19016,7 +19020,7 @@
         <v>1434</v>
       </c>
       <c r="I316" s="5" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="J316" s="5"/>
       <c r="K316" s="2"/>
@@ -19070,7 +19074,7 @@
         <v>1436</v>
       </c>
       <c r="I318" s="5" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="J318" s="5"/>
       <c r="K318" s="2"/>
@@ -19101,7 +19105,7 @@
         <v>510</v>
       </c>
       <c r="I319" s="5" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="J319" s="5"/>
       <c r="K319" s="2"/>
@@ -19184,7 +19188,7 @@
       <c r="G322" s="2"/>
       <c r="H322" s="2"/>
       <c r="I322" s="5" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="J322" s="5"/>
       <c r="K322" s="2"/>
@@ -19215,7 +19219,7 @@
         <v>1049</v>
       </c>
       <c r="I323" s="5" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="J323" s="5"/>
       <c r="K323" s="2"/>
@@ -19244,7 +19248,7 @@
         <v>1445</v>
       </c>
       <c r="I324" s="5" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="J324" s="5"/>
       <c r="K324" s="2"/>
@@ -19273,10 +19277,10 @@
         <v>1447</v>
       </c>
       <c r="I325" s="5" t="s">
+        <v>2277</v>
+      </c>
+      <c r="J325" s="9" t="s">
         <v>2278</v>
-      </c>
-      <c r="J325" s="9" t="s">
-        <v>2279</v>
       </c>
       <c r="K325" s="2"/>
       <c r="L325" s="2"/>
@@ -19422,7 +19426,7 @@
         <v>1434</v>
       </c>
       <c r="I330" s="5" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="J330" s="5"/>
       <c r="K330" s="2"/>
@@ -19476,7 +19480,7 @@
         <v>1456</v>
       </c>
       <c r="I332" s="5" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="J332" s="5"/>
       <c r="K332" s="2"/>
@@ -19505,7 +19509,7 @@
         <v>1458</v>
       </c>
       <c r="I333" s="5" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="J333" s="5"/>
       <c r="K333" s="2"/>
@@ -19534,10 +19538,10 @@
         <v>1460</v>
       </c>
       <c r="I334" s="5" t="s">
+        <v>2281</v>
+      </c>
+      <c r="J334" s="5" t="s">
         <v>2282</v>
-      </c>
-      <c r="J334" s="5" t="s">
-        <v>2283</v>
       </c>
       <c r="K334" s="2"/>
       <c r="L334" s="2"/>
@@ -19565,7 +19569,7 @@
         <v>1462</v>
       </c>
       <c r="I335" s="5" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="J335" s="5"/>
       <c r="K335" s="2"/>
@@ -19594,10 +19598,10 @@
         <v>1464</v>
       </c>
       <c r="I336" s="5" t="s">
+        <v>2284</v>
+      </c>
+      <c r="J336" s="9" t="s">
         <v>2285</v>
-      </c>
-      <c r="J336" s="9" t="s">
-        <v>2286</v>
       </c>
       <c r="K336" s="2"/>
       <c r="L336" s="2"/>
@@ -19706,7 +19710,7 @@
         <v>1471</v>
       </c>
       <c r="I340" s="5" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="J340" s="5"/>
       <c r="K340" s="2"/>
@@ -19735,7 +19739,7 @@
         <v>1473</v>
       </c>
       <c r="I341" s="5" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="J341" s="5"/>
       <c r="K341" s="2"/>
@@ -19767,7 +19771,7 @@
       </c>
       <c r="I342" s="5"/>
       <c r="J342" s="5" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="K342" s="2"/>
       <c r="L342" s="2"/>
@@ -19822,7 +19826,7 @@
         <v>1478</v>
       </c>
       <c r="I344" s="5" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="J344" s="5"/>
       <c r="K344" s="2"/>
@@ -19932,10 +19936,10 @@
         <v>1485</v>
       </c>
       <c r="I348" s="5" t="s">
+        <v>2290</v>
+      </c>
+      <c r="J348" s="5" t="s">
         <v>2291</v>
-      </c>
-      <c r="J348" s="5" t="s">
-        <v>2292</v>
       </c>
       <c r="K348" s="2"/>
       <c r="L348" s="2"/>
@@ -19964,7 +19968,7 @@
       </c>
       <c r="I349" s="5"/>
       <c r="J349" s="5" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="K349" s="2"/>
       <c r="L349" s="2"/>
@@ -20048,7 +20052,7 @@
         <v>1492</v>
       </c>
       <c r="I352" s="5" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="J352" s="5"/>
       <c r="K352" s="2"/>
@@ -20079,7 +20083,7 @@
         <v>1494</v>
       </c>
       <c r="I353" s="5" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="J353" s="5"/>
       <c r="K353" s="2"/>
@@ -20164,7 +20168,7 @@
         <v>1499</v>
       </c>
       <c r="I356" s="5" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="J356" s="5"/>
       <c r="K356" s="2"/>
@@ -20193,7 +20197,7 @@
       <c r="G357" s="2"/>
       <c r="H357" s="2"/>
       <c r="I357" s="5" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="J357" s="5"/>
       <c r="K357" s="2"/>
@@ -20333,7 +20337,7 @@
       </c>
       <c r="I362" s="5"/>
       <c r="J362" s="5" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="K362" s="2"/>
       <c r="L362" s="2"/>
@@ -20361,7 +20365,7 @@
       <c r="G363" s="2"/>
       <c r="H363" s="2"/>
       <c r="I363" s="5" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="J363" s="5"/>
       <c r="K363" s="2"/>
@@ -20390,7 +20394,7 @@
         <v>1513</v>
       </c>
       <c r="I364" s="5" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="J364" s="5"/>
       <c r="K364" s="2"/>
@@ -20444,7 +20448,7 @@
         <v>1515</v>
       </c>
       <c r="I366" s="5" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="J366" s="5"/>
       <c r="K366" s="2"/>
@@ -20554,7 +20558,7 @@
         <v>1520</v>
       </c>
       <c r="I370" s="5" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="J370" s="5"/>
       <c r="K370" s="2"/>
@@ -20583,7 +20587,7 @@
         <v>1522</v>
       </c>
       <c r="I371" s="5" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="J371" s="5"/>
       <c r="K371" s="2"/>
@@ -20668,7 +20672,7 @@
       <c r="G374" s="2"/>
       <c r="H374" s="2"/>
       <c r="I374" s="5" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="J374" s="5"/>
       <c r="K374" s="2"/>
@@ -20697,7 +20701,7 @@
         <v>1530</v>
       </c>
       <c r="I375" s="5" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="J375" s="5"/>
       <c r="K375" s="2"/>
@@ -20834,7 +20838,7 @@
         <v>1536</v>
       </c>
       <c r="I380" s="5" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="J380" s="5"/>
       <c r="K380" s="2"/>
@@ -20866,7 +20870,7 @@
       </c>
       <c r="I381" s="5"/>
       <c r="J381" s="5" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="K381" s="2"/>
       <c r="L381" s="2"/>
@@ -20894,7 +20898,7 @@
         <v>1539</v>
       </c>
       <c r="I382" s="5" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="J382" s="5"/>
       <c r="K382" s="2"/>
@@ -20925,7 +20929,7 @@
         <v>1541</v>
       </c>
       <c r="I383" s="5" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="J383" s="5"/>
       <c r="K383" s="2"/>
@@ -21010,7 +21014,7 @@
         <v>1547</v>
       </c>
       <c r="I386" s="5" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="J386" s="5"/>
       <c r="K386" s="2"/>
@@ -21039,7 +21043,7 @@
         <v>1549</v>
       </c>
       <c r="I387" s="5" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="J387" s="5"/>
       <c r="K387" s="2"/>
@@ -21070,7 +21074,7 @@
         <v>1551</v>
       </c>
       <c r="I388" s="5" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="J388" s="5"/>
       <c r="K388" s="2"/>
@@ -21101,7 +21105,7 @@
         <v>1554</v>
       </c>
       <c r="I389" s="5" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="J389" s="5"/>
       <c r="K389" s="2"/>
@@ -21130,7 +21134,7 @@
         <v>1556</v>
       </c>
       <c r="I390" s="5" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="J390" s="5"/>
       <c r="K390" s="2"/>
@@ -21161,7 +21165,7 @@
         <v>588</v>
       </c>
       <c r="I391" s="5" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="J391" s="5"/>
       <c r="K391" s="2"/>
@@ -21217,7 +21221,7 @@
         <v>1561</v>
       </c>
       <c r="I393" s="5" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="J393" s="5"/>
       <c r="K393" s="2"/>
@@ -21302,7 +21306,7 @@
         <v>1567</v>
       </c>
       <c r="I396" s="5" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="J396" s="5"/>
       <c r="K396" s="2"/>
@@ -21389,7 +21393,7 @@
         <v>1574</v>
       </c>
       <c r="I399" s="5" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="J399" s="5"/>
       <c r="K399" s="2"/>
@@ -21530,7 +21534,7 @@
         <v>1583</v>
       </c>
       <c r="I404" s="5" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="J404" s="5"/>
       <c r="K404" s="2"/>
@@ -21621,7 +21625,7 @@
         <v>1589</v>
       </c>
       <c r="I407" s="5" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="J407" s="5"/>
       <c r="K407" s="2"/>
@@ -21677,7 +21681,7 @@
         <v>1592</v>
       </c>
       <c r="I409" s="5" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="J409" s="5"/>
       <c r="K409" s="2"/>
@@ -21706,7 +21710,7 @@
       <c r="G410" s="2"/>
       <c r="H410" s="2"/>
       <c r="I410" s="5" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="J410" s="5"/>
       <c r="K410" s="2"/>
@@ -21735,7 +21739,7 @@
       <c r="G411" s="2"/>
       <c r="H411" s="2"/>
       <c r="I411" s="5" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="J411" s="5"/>
       <c r="K411" s="2"/>
@@ -21766,7 +21770,7 @@
         <v>1597</v>
       </c>
       <c r="I412" s="5" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
       <c r="J412" s="5"/>
       <c r="K412" s="2" t="s">
@@ -21799,7 +21803,7 @@
         <v>1599</v>
       </c>
       <c r="I413" s="5" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="J413" s="5"/>
       <c r="K413" s="2" t="s">
@@ -21857,7 +21861,7 @@
         <v>884</v>
       </c>
       <c r="I415" s="5" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="J415" s="5"/>
       <c r="K415" s="2"/>
@@ -21913,7 +21917,7 @@
         <v>1606</v>
       </c>
       <c r="I417" s="5" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="J417" s="5"/>
       <c r="K417" s="2"/>
@@ -21998,10 +22002,10 @@
         <v>710</v>
       </c>
       <c r="I420" s="5" t="s">
+        <v>2324</v>
+      </c>
+      <c r="J420" s="5" t="s">
         <v>2325</v>
-      </c>
-      <c r="J420" s="5" t="s">
-        <v>2326</v>
       </c>
       <c r="K420" s="2"/>
       <c r="L420" s="2"/>
@@ -22031,7 +22035,7 @@
         <v>1609</v>
       </c>
       <c r="I421" s="5" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="J421" s="5"/>
       <c r="K421" s="2"/>
@@ -22060,7 +22064,7 @@
         <v>1611</v>
       </c>
       <c r="I422" s="5" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="J422" s="5"/>
       <c r="K422" s="2"/>
@@ -22116,7 +22120,7 @@
         <v>1613</v>
       </c>
       <c r="I424" s="5" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="J424" s="5"/>
       <c r="K424" s="2"/>
@@ -22145,7 +22149,7 @@
         <v>1615</v>
       </c>
       <c r="I425" s="5" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="J425" s="5"/>
       <c r="K425" s="2"/>
@@ -22174,7 +22178,7 @@
         <v>1617</v>
       </c>
       <c r="I426" s="5" t="s">
-        <v>2331</v>
+        <v>2330</v>
       </c>
       <c r="J426" s="5"/>
       <c r="K426" s="2"/>
@@ -22203,7 +22207,7 @@
         <v>1619</v>
       </c>
       <c r="I427" s="5" t="s">
-        <v>2332</v>
+        <v>2331</v>
       </c>
       <c r="J427" s="5"/>
       <c r="K427" s="2"/>
@@ -22340,7 +22344,7 @@
       <c r="G432" s="2"/>
       <c r="H432" s="2"/>
       <c r="I432" s="5" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="J432" s="5"/>
       <c r="K432" s="2"/>
@@ -22369,7 +22373,7 @@
       <c r="G433" s="2"/>
       <c r="H433" s="2"/>
       <c r="I433" s="5" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="J433" s="5"/>
       <c r="K433" s="2"/>
@@ -22423,7 +22427,7 @@
         <v>1569</v>
       </c>
       <c r="I435" s="5" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="J435" s="5"/>
       <c r="K435" s="2" t="s">
@@ -22452,7 +22456,7 @@
       <c r="G436" s="2"/>
       <c r="H436" s="2"/>
       <c r="I436" s="5" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="J436" s="5"/>
       <c r="K436" s="2"/>
@@ -22539,7 +22543,7 @@
         <v>284</v>
       </c>
       <c r="I439" s="5" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
       <c r="J439" s="5"/>
       <c r="K439" s="2"/>
@@ -22566,7 +22570,7 @@
       <c r="G440" s="2"/>
       <c r="H440" s="2"/>
       <c r="I440" s="5" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="J440" s="5"/>
       <c r="K440" s="2"/>
@@ -22674,7 +22678,7 @@
       <c r="G444" s="2"/>
       <c r="H444" s="2"/>
       <c r="I444" s="5" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
       <c r="J444" s="5"/>
       <c r="K444" s="2"/>
@@ -22701,7 +22705,7 @@
       <c r="G445" s="2"/>
       <c r="H445" s="2"/>
       <c r="I445" s="5" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="J445" s="5"/>
       <c r="K445" s="2"/>
@@ -22755,7 +22759,7 @@
       <c r="G447" s="2"/>
       <c r="H447" s="2"/>
       <c r="I447" s="5" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="J447" s="5"/>
       <c r="K447" s="2"/>
@@ -22839,7 +22843,7 @@
       </c>
       <c r="I450" s="5"/>
       <c r="J450" s="5" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="K450" s="2"/>
       <c r="L450" s="2"/>
@@ -22890,7 +22894,7 @@
       <c r="G452" s="2"/>
       <c r="H452" s="2"/>
       <c r="I452" s="5" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="J452" s="5"/>
       <c r="K452" s="2"/>
@@ -22948,7 +22952,7 @@
         <v>1651</v>
       </c>
       <c r="I454" s="5" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="J454" s="5"/>
       <c r="K454" s="2" t="s">
@@ -23002,7 +23006,7 @@
       <c r="G456" s="2"/>
       <c r="H456" s="2"/>
       <c r="I456" s="5" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="J456" s="5"/>
       <c r="K456" s="2"/>
@@ -23083,10 +23087,10 @@
         <v>1655</v>
       </c>
       <c r="I459" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="J459" s="5" t="s">
         <v>2346</v>
-      </c>
-      <c r="J459" s="5" t="s">
-        <v>2347</v>
       </c>
       <c r="K459" s="2"/>
       <c r="L459" s="2"/>
@@ -23139,7 +23143,7 @@
         <v>1660</v>
       </c>
       <c r="I461" s="5" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="J461" s="5"/>
       <c r="K461" s="2"/>
@@ -23168,7 +23172,7 @@
         <v>1662</v>
       </c>
       <c r="I462" s="5" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="J462" s="5"/>
       <c r="K462" s="2"/>
@@ -23199,7 +23203,7 @@
         <v>1664</v>
       </c>
       <c r="I463" s="5" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="J463" s="5"/>
       <c r="K463" s="2"/>
@@ -23307,7 +23311,7 @@
       <c r="G467" s="2"/>
       <c r="H467" s="2"/>
       <c r="I467" s="5" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="J467" s="5"/>
       <c r="K467" s="2"/>
@@ -23336,7 +23340,7 @@
         <v>521</v>
       </c>
       <c r="I468" s="5" t="s">
-        <v>2351</v>
+        <v>2350</v>
       </c>
       <c r="J468" s="5"/>
       <c r="K468" s="2"/>
@@ -23419,7 +23423,7 @@
         <v>1672</v>
       </c>
       <c r="I471" s="5" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="J471" s="5"/>
       <c r="K471" s="2"/>
@@ -23529,7 +23533,7 @@
         <v>1675</v>
       </c>
       <c r="I475" s="5" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="J475" s="5"/>
       <c r="K475" s="2"/>
@@ -23559,7 +23563,7 @@
       </c>
       <c r="I476" s="5"/>
       <c r="J476" s="5" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="K476" s="2"/>
       <c r="L476" s="2"/>
@@ -23695,7 +23699,7 @@
         <v>1686</v>
       </c>
       <c r="I481" s="5" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="J481" s="5"/>
       <c r="K481" s="2"/>
@@ -23726,7 +23730,7 @@
         <v>1688</v>
       </c>
       <c r="I482" s="5" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="J482" s="5"/>
       <c r="K482" s="2"/>
@@ -23757,7 +23761,7 @@
         <v>1690</v>
       </c>
       <c r="I483" s="5" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="J483" s="5"/>
       <c r="K483" s="2"/>
@@ -23813,7 +23817,7 @@
         <v>1660</v>
       </c>
       <c r="I485" s="5" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
       <c r="J485" s="5"/>
       <c r="K485" s="2"/>
@@ -23842,7 +23846,7 @@
         <v>1694</v>
       </c>
       <c r="I486" s="5" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="J486" s="5"/>
       <c r="K486" s="2"/>
@@ -23869,7 +23873,7 @@
       <c r="G487" s="2"/>
       <c r="H487" s="2"/>
       <c r="I487" s="5" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="J487" s="5"/>
       <c r="K487" s="2"/>
@@ -23925,7 +23929,7 @@
       <c r="G489" s="2"/>
       <c r="H489" s="2"/>
       <c r="I489" s="5" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="J489" s="5"/>
       <c r="K489" s="2"/>
@@ -23954,7 +23958,7 @@
         <v>1699</v>
       </c>
       <c r="I490" s="5" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="J490" s="5"/>
       <c r="K490" s="2"/>
@@ -24012,7 +24016,7 @@
         <v>1703</v>
       </c>
       <c r="I492" s="5" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="J492" s="5"/>
       <c r="K492" s="2"/>
@@ -24043,7 +24047,7 @@
         <v>1705</v>
       </c>
       <c r="I493" s="5" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="J493" s="5"/>
       <c r="K493" s="2"/>
@@ -24072,7 +24076,7 @@
         <v>1707</v>
       </c>
       <c r="I494" s="5" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="J494" s="5"/>
       <c r="K494" s="2"/>
@@ -24156,7 +24160,7 @@
       <c r="H497" s="2"/>
       <c r="I497" s="5"/>
       <c r="J497" s="5" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="K497" s="2"/>
       <c r="L497" s="2"/>
@@ -24211,7 +24215,7 @@
         <v>1716</v>
       </c>
       <c r="I499" s="5" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="J499" s="5"/>
       <c r="K499" s="2"/>
@@ -24240,7 +24244,7 @@
         <v>1086</v>
       </c>
       <c r="I500" s="5" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="J500" s="5"/>
       <c r="K500" s="2"/>
@@ -24269,7 +24273,7 @@
       <c r="G501" s="2"/>
       <c r="H501" s="2"/>
       <c r="I501" s="5" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="J501" s="5"/>
       <c r="K501" s="2"/>
@@ -24298,7 +24302,7 @@
         <v>1720</v>
       </c>
       <c r="I502" s="5" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="J502" s="5"/>
       <c r="K502" s="2"/>
@@ -24331,10 +24335,10 @@
         <v>1722</v>
       </c>
       <c r="I503" s="5" t="s">
+        <v>2370</v>
+      </c>
+      <c r="J503" s="5" t="s">
         <v>2371</v>
-      </c>
-      <c r="J503" s="5" t="s">
-        <v>2372</v>
       </c>
       <c r="K503" s="2" t="s">
         <v>556</v>
@@ -24362,7 +24366,7 @@
       <c r="G504" s="2"/>
       <c r="H504" s="2"/>
       <c r="I504" s="5" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="J504" s="5"/>
       <c r="K504" s="2"/>
@@ -24391,7 +24395,7 @@
         <v>1725</v>
       </c>
       <c r="I505" s="5" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="J505" s="5"/>
       <c r="K505" s="2"/>
@@ -24418,7 +24422,7 @@
       <c r="G506" s="2"/>
       <c r="H506" s="2"/>
       <c r="I506" s="5" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="J506" s="5"/>
       <c r="K506" s="2"/>
@@ -24447,7 +24451,7 @@
         <v>521</v>
       </c>
       <c r="I507" s="5" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="J507" s="5"/>
       <c r="K507" s="2"/>
@@ -24475,7 +24479,7 @@
       <c r="H508" s="2"/>
       <c r="I508" s="5"/>
       <c r="J508" s="5" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="K508" s="2"/>
       <c r="L508" s="2"/>
@@ -24505,7 +24509,7 @@
         <v>1730</v>
       </c>
       <c r="I509" s="5" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="J509" s="5"/>
       <c r="K509" s="2"/>
@@ -24534,7 +24538,7 @@
       <c r="G510" s="2"/>
       <c r="H510" s="2"/>
       <c r="I510" s="5" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="J510" s="5"/>
       <c r="K510" s="2"/>
@@ -24565,7 +24569,7 @@
         <v>1733</v>
       </c>
       <c r="I511" s="5" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="J511" s="10"/>
       <c r="K511" s="2"/>
@@ -24619,7 +24623,7 @@
       <c r="G513" s="2"/>
       <c r="H513" s="2"/>
       <c r="I513" s="5" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="J513" s="11"/>
       <c r="K513" s="2"/>
@@ -24723,7 +24727,7 @@
         <v>1740</v>
       </c>
       <c r="I517" s="5" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="J517" s="5"/>
       <c r="K517" s="2"/>
@@ -24808,7 +24812,7 @@
         <v>1746</v>
       </c>
       <c r="I520" s="5" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="J520" s="5"/>
       <c r="K520" s="2"/>
@@ -24837,7 +24841,7 @@
         <v>1748</v>
       </c>
       <c r="I521" s="5" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="J521" s="5"/>
       <c r="K521" s="2"/>
@@ -24864,10 +24868,10 @@
       <c r="G522" s="2"/>
       <c r="H522" s="2"/>
       <c r="I522" s="5" t="s">
+        <v>2384</v>
+      </c>
+      <c r="J522" s="5" t="s">
         <v>2385</v>
-      </c>
-      <c r="J522" s="5" t="s">
-        <v>2386</v>
       </c>
       <c r="K522" s="2"/>
       <c r="L522" s="2"/>
@@ -24898,7 +24902,7 @@
       </c>
       <c r="I523" s="5"/>
       <c r="J523" s="5" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="K523" s="2"/>
       <c r="L523" s="2"/>
@@ -24927,7 +24931,7 @@
       <c r="H524" s="2"/>
       <c r="I524" s="5"/>
       <c r="J524" s="5" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="K524" s="2"/>
       <c r="L524" s="2"/>
@@ -24982,7 +24986,7 @@
         <v>1756</v>
       </c>
       <c r="I526" s="5" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="J526" s="5"/>
       <c r="K526" s="2" t="s">
@@ -25013,7 +25017,7 @@
         <v>1758</v>
       </c>
       <c r="I527" s="5" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="J527" s="5"/>
       <c r="K527" s="2"/>
@@ -25065,7 +25069,7 @@
       <c r="G529" s="2"/>
       <c r="H529" s="2"/>
       <c r="I529" s="5" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="J529" s="5"/>
       <c r="K529" s="2"/>
@@ -25146,7 +25150,7 @@
       <c r="G532" s="2"/>
       <c r="H532" s="2"/>
       <c r="I532" s="5" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="J532" s="5"/>
       <c r="K532" s="2"/>
@@ -25173,7 +25177,7 @@
       <c r="G533" s="2"/>
       <c r="H533" s="2"/>
       <c r="I533" s="5" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="J533" s="5"/>
       <c r="K533" s="2"/>
@@ -25204,7 +25208,7 @@
         <v>1223</v>
       </c>
       <c r="I534" s="5" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="J534" s="5"/>
       <c r="K534" s="2"/>
@@ -25235,7 +25239,7 @@
         <v>1765</v>
       </c>
       <c r="I535" s="5" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="J535" s="5"/>
       <c r="K535" s="2"/>
@@ -25264,7 +25268,7 @@
       <c r="G536" s="2"/>
       <c r="H536" s="2"/>
       <c r="I536" s="5" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="J536" s="5"/>
       <c r="K536" s="2"/>
@@ -25293,7 +25297,7 @@
         <v>1768</v>
       </c>
       <c r="I537" s="5" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="J537" s="5"/>
       <c r="K537" s="2"/>
@@ -25322,7 +25326,7 @@
         <v>1770</v>
       </c>
       <c r="I538" s="5" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="J538" s="5"/>
       <c r="K538" s="2"/>
@@ -25351,7 +25355,7 @@
         <v>1772</v>
       </c>
       <c r="I539" s="5" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="J539" s="5"/>
       <c r="K539" s="2"/>
@@ -25436,7 +25440,7 @@
         <v>920</v>
       </c>
       <c r="I542" s="5" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="J542" s="5"/>
       <c r="K542" s="2"/>
@@ -25492,7 +25496,7 @@
         <v>1779</v>
       </c>
       <c r="I544" s="5" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="J544" s="5"/>
       <c r="K544" s="2"/>
@@ -25548,7 +25552,7 @@
         <v>1783</v>
       </c>
       <c r="I546" s="5" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
       <c r="J546" s="5"/>
       <c r="K546" s="2"/>
@@ -25627,7 +25631,7 @@
       <c r="G549" s="2"/>
       <c r="H549" s="2"/>
       <c r="I549" s="5" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
       <c r="J549" s="5"/>
       <c r="K549" s="2"/>
@@ -25656,7 +25660,7 @@
         <v>284</v>
       </c>
       <c r="I550" s="5" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
       <c r="J550" s="5"/>
       <c r="K550" s="2"/>
@@ -25741,7 +25745,7 @@
         <v>1790</v>
       </c>
       <c r="I553" s="5" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="J553" s="5"/>
       <c r="K553" s="2"/>
@@ -25772,7 +25776,7 @@
         <v>1541</v>
       </c>
       <c r="I554" s="5" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="J554" s="5"/>
       <c r="K554" s="2"/>
@@ -25828,7 +25832,7 @@
         <v>1794</v>
       </c>
       <c r="I556" s="5" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="J556" s="5"/>
       <c r="K556" s="2"/>
@@ -25855,7 +25859,7 @@
       <c r="G557" s="2"/>
       <c r="H557" s="2"/>
       <c r="I557" s="5" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="J557" s="5"/>
       <c r="K557" s="2"/>
@@ -25913,7 +25917,7 @@
         <v>521</v>
       </c>
       <c r="I559" s="5" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="J559" s="5"/>
       <c r="K559" s="2"/>
@@ -25996,7 +26000,7 @@
         <v>1801</v>
       </c>
       <c r="I562" s="5" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="J562" s="5"/>
       <c r="K562" s="2"/>
@@ -26054,7 +26058,7 @@
         <v>521</v>
       </c>
       <c r="I564" s="5" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="J564" s="5"/>
       <c r="K564" s="2"/>
@@ -26083,7 +26087,7 @@
         <v>1804</v>
       </c>
       <c r="I565" s="5" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="J565" s="5"/>
       <c r="K565" s="2"/>
@@ -26114,7 +26118,7 @@
         <v>1158</v>
       </c>
       <c r="I566" s="5" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
       <c r="J566" s="5"/>
       <c r="K566" s="2"/>
@@ -26147,10 +26151,10 @@
         <v>1807</v>
       </c>
       <c r="I567" s="5" t="s">
+        <v>2412</v>
+      </c>
+      <c r="J567" s="5" t="s">
         <v>2413</v>
-      </c>
-      <c r="J567" s="5" t="s">
-        <v>2414</v>
       </c>
       <c r="K567" s="2"/>
       <c r="L567" s="2"/>
@@ -26232,7 +26236,7 @@
         <v>510</v>
       </c>
       <c r="I570" s="5" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
       <c r="J570" s="5"/>
       <c r="K570" s="2"/>
@@ -26313,7 +26317,7 @@
       <c r="G573" s="2"/>
       <c r="H573" s="2"/>
       <c r="I573" s="5" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="J573" s="5"/>
       <c r="K573" s="2"/>
@@ -26396,10 +26400,10 @@
       <c r="G576" s="2"/>
       <c r="H576" s="2"/>
       <c r="I576" s="5" t="s">
+        <v>2416</v>
+      </c>
+      <c r="J576" s="5" t="s">
         <v>2417</v>
-      </c>
-      <c r="J576" s="5" t="s">
-        <v>2418</v>
       </c>
       <c r="K576" s="2"/>
       <c r="L576" s="2"/>
@@ -26427,7 +26431,7 @@
       <c r="G577" s="2"/>
       <c r="H577" s="2"/>
       <c r="I577" s="5" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="J577" s="5"/>
       <c r="K577" s="2" t="s">
@@ -26485,7 +26489,7 @@
         <v>1824</v>
       </c>
       <c r="I579" s="5" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="J579" s="5"/>
       <c r="K579" s="2"/>
@@ -26539,7 +26543,7 @@
         <v>1827</v>
       </c>
       <c r="I581" s="5" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="J581" s="5"/>
       <c r="K581" s="2"/>
@@ -26568,7 +26572,7 @@
         <v>1829</v>
       </c>
       <c r="I582" s="5" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="J582" s="5"/>
       <c r="K582" s="2"/>
@@ -26597,7 +26601,7 @@
         <v>1831</v>
       </c>
       <c r="I583" s="5" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="J583" s="5"/>
       <c r="K583" s="2"/>
@@ -26626,7 +26630,7 @@
         <v>521</v>
       </c>
       <c r="I584" s="5" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="J584" s="5"/>
       <c r="K584" s="2"/>
@@ -26711,7 +26715,7 @@
         <v>1086</v>
       </c>
       <c r="I587" s="5" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="J587" s="5"/>
       <c r="K587" s="2"/>
@@ -26740,11 +26744,11 @@
       <c r="G588" s="2"/>
       <c r="H588" s="2"/>
       <c r="I588" s="5" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="J588" s="5"/>
       <c r="K588" s="2" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="L588" s="2"/>
       <c r="M588" s="2"/>
@@ -26771,7 +26775,7 @@
         <v>1838</v>
       </c>
       <c r="I589" s="5" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="J589" s="5"/>
       <c r="K589" s="2"/>
@@ -26798,10 +26802,10 @@
       <c r="G590" s="2"/>
       <c r="H590" s="2"/>
       <c r="I590" s="5" t="s">
+        <v>2427</v>
+      </c>
+      <c r="J590" s="5" t="s">
         <v>2428</v>
-      </c>
-      <c r="J590" s="5" t="s">
-        <v>2429</v>
       </c>
       <c r="K590" s="2"/>
       <c r="L590" s="2"/>
@@ -26829,7 +26833,7 @@
       <c r="G591" s="2"/>
       <c r="H591" s="2"/>
       <c r="I591" s="5" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="J591" s="5"/>
       <c r="K591" s="2"/>
@@ -26856,7 +26860,7 @@
       <c r="G592" s="2"/>
       <c r="H592" s="2"/>
       <c r="I592" s="5" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="J592" s="5"/>
       <c r="K592" s="2"/>
@@ -26885,7 +26889,7 @@
         <v>375</v>
       </c>
       <c r="I593" s="5" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="J593" s="5"/>
       <c r="K593" s="2"/>
@@ -26914,7 +26918,7 @@
         <v>1844</v>
       </c>
       <c r="I594" s="5" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="J594" s="5"/>
       <c r="K594" s="2"/>
@@ -26941,7 +26945,7 @@
       <c r="G595" s="2"/>
       <c r="H595" s="2"/>
       <c r="I595" s="5" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="J595" s="5"/>
       <c r="K595" s="2"/>
@@ -27047,7 +27051,7 @@
         <v>1850</v>
       </c>
       <c r="I599" s="5" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="J599" s="5"/>
       <c r="K599" s="2"/>
@@ -27076,7 +27080,7 @@
         <v>1852</v>
       </c>
       <c r="I600" s="5" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="J600" s="5"/>
       <c r="K600" s="2"/>
@@ -27103,7 +27107,7 @@
       <c r="G601" s="2"/>
       <c r="H601" s="2"/>
       <c r="I601" s="5" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
       <c r="J601" s="5"/>
       <c r="K601" s="2"/>
@@ -27159,7 +27163,7 @@
         <v>1725</v>
       </c>
       <c r="I603" s="5" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="J603" s="5"/>
       <c r="K603" s="2"/>
@@ -27215,7 +27219,7 @@
         <v>1860</v>
       </c>
       <c r="I605" s="5" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="J605" s="5"/>
       <c r="K605" s="2"/>
@@ -27246,7 +27250,7 @@
         <v>911</v>
       </c>
       <c r="I606" s="5" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="J606" s="5"/>
       <c r="K606" s="2"/>
@@ -27302,10 +27306,10 @@
       <c r="G608" s="2"/>
       <c r="H608" s="2"/>
       <c r="I608" s="5" t="s">
+        <v>2440</v>
+      </c>
+      <c r="J608" s="5" t="s">
         <v>2441</v>
-      </c>
-      <c r="J608" s="5" t="s">
-        <v>2442</v>
       </c>
       <c r="K608" s="2"/>
       <c r="L608" s="2"/>
@@ -27335,7 +27339,7 @@
         <v>1855</v>
       </c>
       <c r="I609" s="5" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="J609" s="5"/>
       <c r="K609" s="2"/>
@@ -27418,7 +27422,7 @@
         <v>1870</v>
       </c>
       <c r="I612" s="5" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="J612" s="5"/>
       <c r="K612" s="2"/>
@@ -27447,7 +27451,7 @@
         <v>1872</v>
       </c>
       <c r="I613" s="5" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="J613" s="5"/>
       <c r="K613" s="2"/>
@@ -27474,7 +27478,7 @@
       <c r="G614" s="2"/>
       <c r="H614" s="2"/>
       <c r="I614" s="5" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="J614" s="5"/>
       <c r="K614" s="2"/>
@@ -27532,7 +27536,7 @@
         <v>1876</v>
       </c>
       <c r="I616" s="5" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="J616" s="5"/>
       <c r="K616" s="2"/>
@@ -27588,7 +27592,7 @@
         <v>1880</v>
       </c>
       <c r="I618" s="5" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="J618" s="5"/>
       <c r="K618" s="2"/>
@@ -27617,10 +27621,10 @@
         <v>1074</v>
       </c>
       <c r="I619" s="5" t="s">
+        <v>2448</v>
+      </c>
+      <c r="J619" s="5" t="s">
         <v>2449</v>
-      </c>
-      <c r="J619" s="5" t="s">
-        <v>2450</v>
       </c>
       <c r="K619" s="2"/>
       <c r="L619" s="2"/>
@@ -27673,7 +27677,7 @@
       <c r="G621" s="2"/>
       <c r="H621" s="2"/>
       <c r="I621" s="5" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="J621" s="5"/>
       <c r="K621" s="2"/>
@@ -27731,7 +27735,7 @@
         <v>1885</v>
       </c>
       <c r="I623" s="5" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="J623" s="5"/>
       <c r="K623" s="2"/>
@@ -27820,7 +27824,7 @@
         <v>1086</v>
       </c>
       <c r="I626" s="5" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="J626" s="5"/>
       <c r="K626" s="2"/>
@@ -27880,10 +27884,10 @@
         <v>1888</v>
       </c>
       <c r="I628" s="5" t="s">
+        <v>2453</v>
+      </c>
+      <c r="J628" s="5" t="s">
         <v>2454</v>
-      </c>
-      <c r="J628" s="5" t="s">
-        <v>2455</v>
       </c>
       <c r="K628" s="2" t="s">
         <v>1086</v>
@@ -27911,7 +27915,7 @@
       <c r="G629" s="2"/>
       <c r="H629" s="2"/>
       <c r="I629" s="5" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="J629" s="5"/>
       <c r="K629" s="2"/>
@@ -27940,7 +27944,7 @@
         <v>1894</v>
       </c>
       <c r="I630" s="5" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
       <c r="J630" s="5"/>
       <c r="K630" s="2"/>
@@ -28102,10 +28106,10 @@
         <v>1086</v>
       </c>
       <c r="I636" s="5" t="s">
+        <v>2457</v>
+      </c>
+      <c r="J636" s="5" t="s">
         <v>2458</v>
-      </c>
-      <c r="J636" s="5" t="s">
-        <v>2459</v>
       </c>
       <c r="K636" s="2"/>
       <c r="L636" s="2"/>
@@ -28160,10 +28164,10 @@
         <v>1686</v>
       </c>
       <c r="I638" s="5" t="s">
+        <v>2459</v>
+      </c>
+      <c r="J638" s="5" t="s">
         <v>2460</v>
-      </c>
-      <c r="J638" s="5" t="s">
-        <v>2461</v>
       </c>
       <c r="K638" s="2"/>
       <c r="L638" s="2"/>
@@ -28191,10 +28195,10 @@
         <v>1906</v>
       </c>
       <c r="I639" s="5" t="s">
+        <v>2461</v>
+      </c>
+      <c r="J639" s="5" t="s">
         <v>2462</v>
-      </c>
-      <c r="J639" s="5" t="s">
-        <v>2463</v>
       </c>
       <c r="K639" s="2"/>
       <c r="L639" s="2"/>
@@ -28249,10 +28253,10 @@
         <v>1909</v>
       </c>
       <c r="I641" s="5" t="s">
+        <v>2463</v>
+      </c>
+      <c r="J641" s="5" t="s">
         <v>2464</v>
-      </c>
-      <c r="J641" s="5" t="s">
-        <v>2465</v>
       </c>
       <c r="K641" s="2"/>
       <c r="L641" s="2"/>
@@ -28386,7 +28390,7 @@
       <c r="G646" s="2"/>
       <c r="H646" s="2"/>
       <c r="I646" s="5" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="J646" s="5"/>
       <c r="K646" s="2"/>
@@ -28446,7 +28450,7 @@
         <v>1316</v>
       </c>
       <c r="I648" s="5" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="J648" s="5"/>
       <c r="K648" s="2"/>
@@ -28473,7 +28477,7 @@
       <c r="G649" s="2"/>
       <c r="H649" s="2"/>
       <c r="I649" s="5" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="J649" s="5"/>
       <c r="K649" s="2"/>
@@ -28504,11 +28508,11 @@
         <v>1920</v>
       </c>
       <c r="I650" s="5" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="J650" s="5"/>
       <c r="K650" s="2" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="L650" s="2"/>
       <c r="M650" s="2"/>
@@ -28533,7 +28537,7 @@
       <c r="G651" s="2"/>
       <c r="H651" s="2"/>
       <c r="I651" s="5" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="J651" s="5"/>
       <c r="K651" s="2"/>
@@ -28560,7 +28564,7 @@
       <c r="G652" s="2"/>
       <c r="H652" s="2"/>
       <c r="I652" s="5" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="J652" s="5"/>
       <c r="K652" s="2"/>
@@ -28589,7 +28593,7 @@
       <c r="G653" s="2"/>
       <c r="H653" s="2"/>
       <c r="I653" s="5" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="J653" s="5"/>
       <c r="K653" s="2"/>
@@ -28697,7 +28701,7 @@
       <c r="G657" s="2"/>
       <c r="H657" s="2"/>
       <c r="I657" s="5" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="J657" s="5"/>
       <c r="K657" s="2"/>
@@ -28724,7 +28728,7 @@
       <c r="G658" s="2"/>
       <c r="H658" s="2"/>
       <c r="I658" s="5" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
       <c r="J658" s="5"/>
       <c r="K658" s="2"/>
@@ -28811,7 +28815,7 @@
         <v>875</v>
       </c>
       <c r="I661" s="5" t="s">
-        <v>2474</v>
+        <v>2473</v>
       </c>
       <c r="J661" s="5"/>
       <c r="K661" s="2"/>
@@ -28894,7 +28898,7 @@
       <c r="G664" s="2"/>
       <c r="H664" s="2"/>
       <c r="I664" s="5" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="J664" s="5"/>
       <c r="K664" s="2"/>
@@ -29056,7 +29060,7 @@
         <v>1949</v>
       </c>
       <c r="I670" s="5" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="J670" s="5"/>
       <c r="K670" s="2"/>
@@ -29085,7 +29089,7 @@
         <v>1951</v>
       </c>
       <c r="I671" s="5" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="J671" s="5"/>
       <c r="K671" s="2"/>
@@ -29114,7 +29118,7 @@
         <v>1794</v>
       </c>
       <c r="I672" s="5" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="J672" s="5"/>
       <c r="K672" s="2"/>
@@ -29143,7 +29147,7 @@
         <v>1954</v>
       </c>
       <c r="I673" s="5" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="J673" s="5"/>
       <c r="K673" s="2"/>
@@ -29199,7 +29203,7 @@
         <v>1957</v>
       </c>
       <c r="I675" s="5" t="s">
-        <v>2480</v>
+        <v>2479</v>
       </c>
       <c r="J675" s="5"/>
       <c r="K675" s="2"/>
@@ -29228,10 +29232,10 @@
         <v>1959</v>
       </c>
       <c r="I676" s="5" t="s">
+        <v>2480</v>
+      </c>
+      <c r="J676" s="5" t="s">
         <v>2481</v>
-      </c>
-      <c r="J676" s="5" t="s">
-        <v>2482</v>
       </c>
       <c r="K676" s="2"/>
       <c r="L676" s="2"/>
@@ -29315,7 +29319,7 @@
         <v>1965</v>
       </c>
       <c r="I679" s="5" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="J679" s="5"/>
       <c r="K679" s="2"/>
@@ -29344,7 +29348,7 @@
       <c r="G680" s="2"/>
       <c r="H680" s="2"/>
       <c r="I680" s="5" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="J680" s="5"/>
       <c r="K680" s="2"/>
@@ -29427,7 +29431,7 @@
         <v>1972</v>
       </c>
       <c r="I683" s="5" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="J683" s="5"/>
       <c r="K683" s="2"/>
@@ -29485,7 +29489,7 @@
         <v>1977</v>
       </c>
       <c r="I685" s="5" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="J685" s="5"/>
       <c r="K685" s="2"/>
@@ -29514,7 +29518,7 @@
         <v>1979</v>
       </c>
       <c r="I686" s="5" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="J686" s="5"/>
       <c r="K686" s="2"/>
@@ -29599,7 +29603,7 @@
       <c r="G689" s="2"/>
       <c r="H689" s="2"/>
       <c r="I689" s="5" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="J689" s="5"/>
       <c r="K689" s="2"/>
@@ -29626,7 +29630,7 @@
       <c r="G690" s="2"/>
       <c r="H690" s="2"/>
       <c r="I690" s="5" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="J690" s="5"/>
       <c r="K690" s="2"/>
@@ -29653,7 +29657,7 @@
       <c r="G691" s="2"/>
       <c r="H691" s="2"/>
       <c r="I691" s="5" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="J691" s="5"/>
       <c r="K691" s="2" t="s">
@@ -29684,10 +29688,10 @@
         <v>1987</v>
       </c>
       <c r="I692" s="5" t="s">
+        <v>2490</v>
+      </c>
+      <c r="J692" s="5" t="s">
         <v>2491</v>
-      </c>
-      <c r="J692" s="5" t="s">
-        <v>2492</v>
       </c>
       <c r="K692" s="2"/>
       <c r="L692" s="2"/>
@@ -29765,7 +29769,7 @@
       <c r="G695" s="2"/>
       <c r="H695" s="2"/>
       <c r="I695" s="5" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="J695" s="5"/>
       <c r="K695" s="2"/>
@@ -29823,7 +29827,7 @@
         <v>1994</v>
       </c>
       <c r="I697" s="5" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="J697" s="5"/>
       <c r="K697" s="2"/>
@@ -29879,7 +29883,7 @@
         <v>1510</v>
       </c>
       <c r="I699" s="5" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
       <c r="J699" s="5"/>
       <c r="K699" s="2"/>
@@ -29910,7 +29914,7 @@
         <v>1999</v>
       </c>
       <c r="I700" s="5" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="J700" s="5"/>
       <c r="K700" s="2"/>
@@ -29941,7 +29945,7 @@
         <v>2001</v>
       </c>
       <c r="I701" s="5" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="J701" s="5"/>
       <c r="K701" s="2"/>
@@ -29970,7 +29974,7 @@
       <c r="G702" s="2"/>
       <c r="H702" s="2"/>
       <c r="I702" s="5" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="J702" s="5"/>
       <c r="K702" s="2" t="s">
@@ -30001,7 +30005,7 @@
       <c r="G703" s="2"/>
       <c r="H703" s="2"/>
       <c r="I703" s="5" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
       <c r="J703" s="5"/>
       <c r="K703" s="2"/>
@@ -30030,7 +30034,7 @@
         <v>2005</v>
       </c>
       <c r="I704" s="5" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="J704" s="5"/>
       <c r="K704" s="2"/>
@@ -30059,7 +30063,7 @@
         <v>2007</v>
       </c>
       <c r="I705" s="5" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="J705" s="5"/>
       <c r="K705" s="2"/>
@@ -30088,7 +30092,7 @@
       <c r="G706" s="2"/>
       <c r="H706" s="2"/>
       <c r="I706" s="5" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="J706" s="5"/>
       <c r="K706" s="2"/>
@@ -30115,7 +30119,7 @@
       <c r="G707" s="2"/>
       <c r="H707" s="2"/>
       <c r="I707" s="5" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="J707" s="5"/>
       <c r="K707" s="2"/>
@@ -30144,7 +30148,7 @@
         <v>2011</v>
       </c>
       <c r="I708" s="5" t="s">
-        <v>2504</v>
+        <v>2503</v>
       </c>
       <c r="J708" s="5"/>
       <c r="K708" s="2"/>
@@ -30198,7 +30202,7 @@
       <c r="G710" s="2"/>
       <c r="H710" s="2"/>
       <c r="I710" s="5" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="J710" s="5"/>
       <c r="K710" s="2"/>
@@ -30227,10 +30231,10 @@
         <v>375</v>
       </c>
       <c r="I711" s="5" t="s">
+        <v>2505</v>
+      </c>
+      <c r="J711" s="5" t="s">
         <v>2506</v>
-      </c>
-      <c r="J711" s="5" t="s">
-        <v>2507</v>
       </c>
       <c r="K711" s="2"/>
       <c r="L711" s="2"/>
@@ -30256,7 +30260,7 @@
       <c r="G712" s="2"/>
       <c r="H712" s="2"/>
       <c r="I712" s="5" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="J712" s="5"/>
       <c r="K712" s="2"/>
@@ -30316,7 +30320,7 @@
         <v>1725</v>
       </c>
       <c r="I714" s="5" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
       <c r="J714" s="5"/>
       <c r="K714" s="2"/>
@@ -30347,7 +30351,7 @@
         <v>2019</v>
       </c>
       <c r="I715" s="5" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="J715" s="5"/>
       <c r="K715" s="2"/>
@@ -30401,7 +30405,7 @@
         <v>2022</v>
       </c>
       <c r="I717" s="5" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="J717" s="5"/>
       <c r="K717" s="2"/>
@@ -30542,7 +30546,7 @@
       <c r="G722" s="2"/>
       <c r="H722" s="2"/>
       <c r="I722" s="5" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="J722" s="5"/>
       <c r="K722" s="2"/>
@@ -30758,7 +30762,7 @@
         <v>2040</v>
       </c>
       <c r="I730" s="5" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="J730" s="5"/>
       <c r="K730" s="2"/>
@@ -30787,7 +30791,7 @@
         <v>284</v>
       </c>
       <c r="I731" s="5" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="J731" s="5"/>
       <c r="K731" s="2"/>
@@ -30845,7 +30849,7 @@
         <v>2045</v>
       </c>
       <c r="I733" s="5" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="J733" s="5"/>
       <c r="K733" s="2"/>
@@ -30949,7 +30953,7 @@
         <v>2049</v>
       </c>
       <c r="I737" s="5" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="J737" s="5"/>
       <c r="K737" s="2"/>
@@ -31038,7 +31042,7 @@
         <v>1196</v>
       </c>
       <c r="I740" s="5" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="J740" s="5"/>
       <c r="K740" s="2" t="s">
@@ -31096,7 +31100,7 @@
         <v>2058</v>
       </c>
       <c r="I742" s="5" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="J742" s="5"/>
       <c r="K742" s="2"/>
@@ -31125,7 +31129,7 @@
         <v>2060</v>
       </c>
       <c r="I743" s="5" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
       <c r="J743" s="5"/>
       <c r="K743" s="2"/>
@@ -31154,7 +31158,7 @@
         <v>2062</v>
       </c>
       <c r="I744" s="5" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="J744" s="5"/>
       <c r="K744" s="2"/>
@@ -31239,7 +31243,7 @@
       <c r="G747" s="2"/>
       <c r="H747" s="2"/>
       <c r="I747" s="5" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="J747" s="5"/>
       <c r="K747" s="2"/>
@@ -31322,7 +31326,7 @@
       <c r="G750" s="2"/>
       <c r="H750" s="2"/>
       <c r="I750" s="5" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="J750" s="5"/>
       <c r="K750" s="2"/>
@@ -31488,7 +31492,7 @@
         <v>2079</v>
       </c>
       <c r="I756" s="5" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
       <c r="J756" s="5"/>
       <c r="K756" s="2"/>

--- a/begrippen-nlsbb.xlsx
+++ b/begrippen-nlsbb.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\apps\github\IMProRail\spoorse-begrippen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F0D62C3-DFBE-4BEB-8E20-04159030BC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F0D89A0-5E2C-4F40-9AA5-A5D3EEB324DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-3255" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{647FEE87-BCEB-4E3A-ABA6-7EA97748041A}"/>
   </bookViews>
@@ -7055,12 +7055,6 @@
   </si>
   <si>
     <t xml:space="preserve">Zie ook: https://otl.prorail.nl/otl/vigerend/Bevloering </t>
-  </si>
-  <si>
-    <t>Er zijn 3 soorten bewegingmaterieelrelaties: 
-•	Overgaan: al het materieel van één aanvoerende bewegingsactiviteit wordt in één afvoerende bewegingsactiviteit ingezet;
-•	combineren: het materieel uit meer dan één aanvoerende bewegingsactiviteiten wordt in één af-voerende bewegingsactiviteit ingezet;
-•	splitsen: het materieel uit één aanvoerende bewegingsactiviteit wordt in meer dan één bewe-gingsactiviteiten ingezet.</t>
   </si>
   <si>
     <t>Bij aankomst gaat 12-JAN-1998 512 over in vertrek van 12-JAN-1998 517
@@ -9212,6 +9206,12 @@
 * Aankomst in Asa spoor 4 om 7:30, 
 * Vertrek in Asa spoor 4 om 7:31, 
 * Aankomst in Ut spoor 4 om 7:50, …. etc. van beweging (trein) 3023</t>
+  </si>
+  <si>
+    <t>Er zijn 3 soorten bewegingmaterieelrelaties: 
+* overgaan: al het materieel van één aanvoerende bewegingsactiviteit wordt in één afvoerende bewegingsactiviteit ingezet;
+* combineren: het materieel uit meer dan één aanvoerende bewegingsactiviteiten wordt in één af-voerende bewegingsactiviteit ingezet;
+* splitsen: het materieel uit één aanvoerende bewegingsactiviteit wordt in meer dan één bewe-gingsactiviteiten ingezet.</t>
   </si>
 </sst>
 </file>
@@ -9897,61 +9897,61 @@
   <sheetData>
     <row r="1" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>2524</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>2525</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2526</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2527</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>2528</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>2529</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>2530</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>2531</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="4" t="s">
         <v>2532</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>2533</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="1" t="s">
         <v>2534</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>2535</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>2536</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>2537</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>2538</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>2539</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>2540</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>2541</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>2542</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>2543</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="38.25" x14ac:dyDescent="0.2">
@@ -10084,7 +10084,7 @@
         <v>872</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="2"/>
@@ -12572,7 +12572,7 @@
         <v>1025</v>
       </c>
       <c r="I92" s="5" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="J92" s="5"/>
       <c r="K92" s="2"/>
@@ -12603,10 +12603,10 @@
         <v>1028</v>
       </c>
       <c r="I93" s="5" t="s">
+        <v>2546</v>
+      </c>
+      <c r="J93" s="5" t="s">
         <v>2142</v>
-      </c>
-      <c r="J93" s="5" t="s">
-        <v>2143</v>
       </c>
       <c r="K93" s="2"/>
       <c r="L93" s="2"/>
@@ -12635,7 +12635,7 @@
       </c>
       <c r="I94" s="5"/>
       <c r="J94" s="5" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="K94" s="2"/>
       <c r="L94" s="2"/>
@@ -12775,7 +12775,7 @@
         <v>1041</v>
       </c>
       <c r="I99" s="5" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="J99" s="5"/>
       <c r="K99" s="2"/>
@@ -12807,7 +12807,7 @@
       </c>
       <c r="I100" s="5"/>
       <c r="J100" s="5" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="K100" s="2"/>
       <c r="L100" s="2"/>
@@ -12835,7 +12835,7 @@
         <v>1045</v>
       </c>
       <c r="I101" s="5" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="J101" s="5"/>
       <c r="K101" s="2"/>
@@ -12895,7 +12895,7 @@
         <v>1049</v>
       </c>
       <c r="I103" s="5" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="J103" s="5"/>
       <c r="K103" s="2"/>
@@ -12984,7 +12984,7 @@
         <v>1056</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="J106" s="5"/>
       <c r="K106" s="2"/>
@@ -13038,7 +13038,7 @@
         <v>1058</v>
       </c>
       <c r="I108" s="5" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="J108" s="5"/>
       <c r="K108" s="2"/>
@@ -13094,10 +13094,10 @@
         <v>1060</v>
       </c>
       <c r="I110" s="5" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="J110" s="5" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="K110" s="2"/>
       <c r="L110" s="2"/>
@@ -13125,7 +13125,7 @@
         <v>1063</v>
       </c>
       <c r="I111" s="5" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="J111" s="5"/>
       <c r="K111" s="2"/>
@@ -13154,10 +13154,10 @@
         <v>1065</v>
       </c>
       <c r="I112" s="5" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="J112" s="5" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="K112" s="2"/>
       <c r="L112" s="2"/>
@@ -13185,7 +13185,7 @@
         <v>1067</v>
       </c>
       <c r="I113" s="5" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="J113" s="5"/>
       <c r="K113" s="2"/>
@@ -13243,7 +13243,7 @@
         <v>510</v>
       </c>
       <c r="I115" s="5" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="J115" s="5"/>
       <c r="K115" s="2"/>
@@ -13301,7 +13301,7 @@
         <v>1075</v>
       </c>
       <c r="I117" s="5" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="J117" s="5"/>
       <c r="K117" s="2"/>
@@ -13361,7 +13361,7 @@
         <v>1079</v>
       </c>
       <c r="I119" s="5" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="J119" s="5"/>
       <c r="K119" s="2"/>
@@ -13421,7 +13421,7 @@
         <v>1082</v>
       </c>
       <c r="I121" s="5" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="J121" s="5"/>
       <c r="K121" s="2"/>
@@ -13450,7 +13450,7 @@
         <v>1084</v>
       </c>
       <c r="I122" s="5" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="J122" s="5"/>
       <c r="K122" s="2"/>
@@ -13479,7 +13479,7 @@
         <v>1086</v>
       </c>
       <c r="I123" s="5" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="J123" s="5"/>
       <c r="K123" s="2"/>
@@ -13509,7 +13509,7 @@
       <c r="H124" s="2"/>
       <c r="I124" s="5"/>
       <c r="J124" s="5" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="K124" s="2"/>
       <c r="L124" s="2"/>
@@ -13593,7 +13593,7 @@
         <v>1093</v>
       </c>
       <c r="I127" s="5" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="J127" s="5"/>
       <c r="K127" s="2"/>
@@ -13705,7 +13705,7 @@
         <v>1099</v>
       </c>
       <c r="I131" s="5" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="J131" s="5"/>
       <c r="K131" s="2"/>
@@ -13736,7 +13736,7 @@
         <v>1102</v>
       </c>
       <c r="I132" s="5" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="J132" s="5"/>
       <c r="K132" s="2"/>
@@ -13794,7 +13794,7 @@
         <v>1106</v>
       </c>
       <c r="I134" s="5" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="J134" s="5"/>
       <c r="K134" s="2"/>
@@ -13823,7 +13823,7 @@
         <v>1108</v>
       </c>
       <c r="I135" s="5" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="J135" s="5"/>
       <c r="K135" s="2"/>
@@ -13906,7 +13906,7 @@
         <v>1113</v>
       </c>
       <c r="I138" s="5" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="J138" s="5"/>
       <c r="K138" s="2"/>
@@ -13991,7 +13991,7 @@
         <v>1118</v>
       </c>
       <c r="I141" s="5" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="J141" s="5"/>
       <c r="K141" s="2"/>
@@ -14047,7 +14047,7 @@
         <v>1122</v>
       </c>
       <c r="I143" s="5" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="J143" s="5"/>
       <c r="K143" s="2"/>
@@ -14155,7 +14155,7 @@
         <v>1129</v>
       </c>
       <c r="I147" s="5" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="J147" s="5"/>
       <c r="K147" s="2"/>
@@ -14184,7 +14184,7 @@
         <v>1131</v>
       </c>
       <c r="I148" s="5" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="J148" s="5"/>
       <c r="K148" s="2"/>
@@ -14240,7 +14240,7 @@
         <v>1135</v>
       </c>
       <c r="I150" s="5" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="J150" s="5"/>
       <c r="K150" s="2"/>
@@ -14269,10 +14269,10 @@
         <v>1137</v>
       </c>
       <c r="I151" s="5" t="s">
+        <v>2170</v>
+      </c>
+      <c r="J151" s="5" t="s">
         <v>2171</v>
-      </c>
-      <c r="J151" s="5" t="s">
-        <v>2172</v>
       </c>
       <c r="K151" s="2"/>
       <c r="L151" s="2"/>
@@ -14327,7 +14327,7 @@
         <v>1140</v>
       </c>
       <c r="I153" s="5" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="J153" s="5"/>
       <c r="K153" s="2"/>
@@ -14356,7 +14356,7 @@
         <v>1142</v>
       </c>
       <c r="I154" s="5" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="J154" s="5"/>
       <c r="K154" s="2"/>
@@ -14385,7 +14385,7 @@
         <v>1144</v>
       </c>
       <c r="I155" s="5" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="J155" s="5"/>
       <c r="K155" s="2"/>
@@ -14472,7 +14472,7 @@
         <v>1150</v>
       </c>
       <c r="I158" s="5" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="J158" s="5"/>
       <c r="K158" s="2"/>
@@ -14501,10 +14501,10 @@
         <v>1152</v>
       </c>
       <c r="I159" s="5" t="s">
+        <v>2176</v>
+      </c>
+      <c r="J159" s="5" t="s">
         <v>2177</v>
-      </c>
-      <c r="J159" s="5" t="s">
-        <v>2178</v>
       </c>
       <c r="K159" s="2"/>
       <c r="L159" s="2"/>
@@ -14532,7 +14532,7 @@
         <v>1154</v>
       </c>
       <c r="I160" s="5" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="J160" s="5"/>
       <c r="K160" s="2"/>
@@ -14561,7 +14561,7 @@
         <v>1156</v>
       </c>
       <c r="I161" s="5" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="J161" s="5"/>
       <c r="K161" s="2"/>
@@ -14644,7 +14644,7 @@
         <v>1160</v>
       </c>
       <c r="I164" s="5" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="J164" s="5"/>
       <c r="K164" s="2"/>
@@ -14675,7 +14675,7 @@
         <v>1163</v>
       </c>
       <c r="I165" s="5" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="J165" s="5"/>
       <c r="K165" s="2"/>
@@ -14733,7 +14733,7 @@
         <v>1167</v>
       </c>
       <c r="I167" s="5" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="J167" s="5"/>
       <c r="K167" s="2"/>
@@ -14814,7 +14814,7 @@
         <v>1172</v>
       </c>
       <c r="I170" s="5" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="J170" s="5"/>
       <c r="K170" s="2"/>
@@ -14843,7 +14843,7 @@
         <v>1174</v>
       </c>
       <c r="I171" s="5" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="J171" s="5"/>
       <c r="K171" s="2"/>
@@ -14901,7 +14901,7 @@
         <v>1178</v>
       </c>
       <c r="I173" s="5" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="J173" s="5"/>
       <c r="K173" s="2"/>
@@ -14928,7 +14928,7 @@
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
       <c r="I174" s="5" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="J174" s="5"/>
       <c r="K174" s="2"/>
@@ -14957,7 +14957,7 @@
         <v>1181</v>
       </c>
       <c r="I175" s="5" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="J175" s="5"/>
       <c r="K175" s="2"/>
@@ -14986,7 +14986,7 @@
         <v>1183</v>
       </c>
       <c r="I176" s="5" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="J176" s="5"/>
       <c r="K176" s="2"/>
@@ -15015,7 +15015,7 @@
         <v>1185</v>
       </c>
       <c r="I177" s="5" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="J177" s="5"/>
       <c r="K177" s="2"/>
@@ -15100,7 +15100,7 @@
         <v>1191</v>
       </c>
       <c r="I180" s="5" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="J180" s="5"/>
       <c r="K180" s="2"/>
@@ -15133,7 +15133,7 @@
         <v>1194</v>
       </c>
       <c r="I181" s="5" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="J181" s="5"/>
       <c r="K181" s="2"/>
@@ -15164,7 +15164,7 @@
         <v>1197</v>
       </c>
       <c r="I182" s="5" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="J182" s="5"/>
       <c r="K182" s="2"/>
@@ -15193,7 +15193,7 @@
       <c r="G183" s="2"/>
       <c r="H183" s="2"/>
       <c r="I183" s="5" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="J183" s="5"/>
       <c r="K183" s="2"/>
@@ -15253,7 +15253,7 @@
         <v>1203</v>
       </c>
       <c r="I185" s="5" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="J185" s="5"/>
       <c r="K185" s="2"/>
@@ -15311,7 +15311,7 @@
         <v>1206</v>
       </c>
       <c r="I187" s="5" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="J187" s="5"/>
       <c r="K187" s="2"/>
@@ -15371,7 +15371,7 @@
         <v>1209</v>
       </c>
       <c r="I189" s="5" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="J189" s="5"/>
       <c r="K189" s="2"/>
@@ -15402,7 +15402,7 @@
         <v>1212</v>
       </c>
       <c r="I190" s="5" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="J190" s="5"/>
       <c r="K190" s="2"/>
@@ -15433,7 +15433,7 @@
         <v>1214</v>
       </c>
       <c r="I191" s="5" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="J191" s="5"/>
       <c r="K191" s="2"/>
@@ -15462,7 +15462,7 @@
         <v>920</v>
       </c>
       <c r="I192" s="5" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="J192" s="5"/>
       <c r="K192" s="2"/>
@@ -15493,7 +15493,7 @@
         <v>1217</v>
       </c>
       <c r="I193" s="5" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="J193" s="5"/>
       <c r="K193" s="2"/>
@@ -15522,7 +15522,7 @@
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
       <c r="I194" s="5" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="J194" s="5"/>
       <c r="K194" s="2"/>
@@ -15580,7 +15580,7 @@
         <v>1223</v>
       </c>
       <c r="I196" s="5" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="J196" s="5"/>
       <c r="K196" s="2"/>
@@ -15663,7 +15663,7 @@
         <v>1229</v>
       </c>
       <c r="I199" s="5" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="J199" s="5"/>
       <c r="K199" s="2"/>
@@ -15721,7 +15721,7 @@
         <v>1233</v>
       </c>
       <c r="I201" s="5" t="s">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="J201" s="5"/>
       <c r="K201" s="2"/>
@@ -15837,7 +15837,7 @@
         <v>1237</v>
       </c>
       <c r="I205" s="5" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="J205" s="5"/>
       <c r="K205" s="2"/>
@@ -15866,7 +15866,7 @@
         <v>1239</v>
       </c>
       <c r="I206" s="5" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="J206" s="5"/>
       <c r="K206" s="2"/>
@@ -15953,7 +15953,7 @@
         <v>1245</v>
       </c>
       <c r="I209" s="5" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="J209" s="5"/>
       <c r="K209" s="2"/>
@@ -15984,7 +15984,7 @@
         <v>1248</v>
       </c>
       <c r="I210" s="5" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="J210" s="5"/>
       <c r="K210" s="2"/>
@@ -16015,10 +16015,10 @@
         <v>1251</v>
       </c>
       <c r="I211" s="5" t="s">
+        <v>2208</v>
+      </c>
+      <c r="J211" s="5" t="s">
         <v>2209</v>
-      </c>
-      <c r="J211" s="5" t="s">
-        <v>2210</v>
       </c>
       <c r="K211" s="2"/>
       <c r="L211" s="2"/>
@@ -16044,7 +16044,7 @@
       <c r="G212" s="2"/>
       <c r="H212" s="2"/>
       <c r="I212" s="5" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="J212" s="5"/>
       <c r="K212" s="2"/>
@@ -16073,7 +16073,7 @@
         <v>944</v>
       </c>
       <c r="I213" s="5" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="J213" s="5"/>
       <c r="K213" s="2"/>
@@ -16131,7 +16131,7 @@
         <v>1196</v>
       </c>
       <c r="I215" s="5" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="J215" s="5"/>
       <c r="K215" s="2"/>
@@ -16160,10 +16160,10 @@
         <v>1258</v>
       </c>
       <c r="I216" s="5" t="s">
+        <v>2213</v>
+      </c>
+      <c r="J216" s="5" t="s">
         <v>2214</v>
-      </c>
-      <c r="J216" s="5" t="s">
-        <v>2215</v>
       </c>
       <c r="K216" s="2"/>
       <c r="L216" s="2"/>
@@ -16189,7 +16189,7 @@
       <c r="G217" s="2"/>
       <c r="H217" s="2"/>
       <c r="I217" s="5" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="J217" s="5"/>
       <c r="K217" s="2"/>
@@ -16250,7 +16250,7 @@
       </c>
       <c r="I219" s="5"/>
       <c r="J219" s="5" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="K219" s="2"/>
       <c r="L219" s="2"/>
@@ -16334,7 +16334,7 @@
         <v>1271</v>
       </c>
       <c r="I222" s="5" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="J222" s="5"/>
       <c r="K222" s="2"/>
@@ -16413,7 +16413,7 @@
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
       <c r="I225" s="5" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="J225" s="5"/>
       <c r="K225" s="2"/>
@@ -16444,7 +16444,7 @@
         <v>1101</v>
       </c>
       <c r="I226" s="5" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="J226" s="5"/>
       <c r="K226" s="2"/>
@@ -16475,7 +16475,7 @@
         <v>1278</v>
       </c>
       <c r="I227" s="5" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="J227" s="5"/>
       <c r="K227" s="2"/>
@@ -16502,7 +16502,7 @@
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
       <c r="I228" s="5" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="J228" s="5"/>
       <c r="K228" s="2"/>
@@ -16531,7 +16531,7 @@
       </c>
       <c r="H229" s="2"/>
       <c r="I229" s="5" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="J229" s="5"/>
       <c r="K229" s="2"/>
@@ -16562,7 +16562,7 @@
         <v>1284</v>
       </c>
       <c r="I230" s="5" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="J230" s="5"/>
       <c r="K230" s="2"/>
@@ -16651,7 +16651,7 @@
         <v>1289</v>
       </c>
       <c r="I233" s="5" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="J233" s="5"/>
       <c r="K233" s="2"/>
@@ -16765,7 +16765,7 @@
         <v>1296</v>
       </c>
       <c r="I237" s="5" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="J237" s="5"/>
       <c r="K237" s="2"/>
@@ -16794,7 +16794,7 @@
         <v>1298</v>
       </c>
       <c r="I238" s="5" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="J238" s="5"/>
       <c r="K238" s="2"/>
@@ -16877,7 +16877,7 @@
         <v>1304</v>
       </c>
       <c r="I241" s="5" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="J241" s="5"/>
       <c r="K241" s="2"/>
@@ -16933,7 +16933,7 @@
         <v>1308</v>
       </c>
       <c r="I243" s="5" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
       <c r="J243" s="5"/>
       <c r="K243" s="2"/>
@@ -16964,7 +16964,7 @@
         <v>1311</v>
       </c>
       <c r="I244" s="5" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="J244" s="5"/>
       <c r="K244" s="2"/>
@@ -16993,7 +16993,7 @@
         <v>1313</v>
       </c>
       <c r="I245" s="5" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="J245" s="5"/>
       <c r="K245" s="2"/>
@@ -17078,7 +17078,7 @@
         <v>1319</v>
       </c>
       <c r="I248" s="5" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="J248" s="5"/>
       <c r="K248" s="2"/>
@@ -17107,7 +17107,7 @@
         <v>1321</v>
       </c>
       <c r="I249" s="5" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="J249" s="5"/>
       <c r="K249" s="2"/>
@@ -17136,7 +17136,7 @@
       <c r="G250" s="2"/>
       <c r="H250" s="2"/>
       <c r="I250" s="5" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="J250" s="5"/>
       <c r="K250" s="2"/>
@@ -17165,7 +17165,7 @@
       <c r="G251" s="2"/>
       <c r="H251" s="2"/>
       <c r="I251" s="5" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="J251" s="5"/>
       <c r="K251" s="2"/>
@@ -17198,7 +17198,7 @@
         <v>1325</v>
       </c>
       <c r="I252" s="5" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="J252" s="5"/>
       <c r="K252" s="2"/>
@@ -17252,7 +17252,7 @@
         <v>1328</v>
       </c>
       <c r="I254" s="5" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="J254" s="5"/>
       <c r="K254" s="2"/>
@@ -17283,7 +17283,7 @@
         <v>1330</v>
       </c>
       <c r="I255" s="5" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="J255" s="5"/>
       <c r="K255" s="2"/>
@@ -17430,7 +17430,7 @@
         <v>1339</v>
       </c>
       <c r="I260" s="5" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="J260" s="5"/>
       <c r="K260" s="2"/>
@@ -17538,7 +17538,7 @@
         <v>1344</v>
       </c>
       <c r="I264" s="5" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="J264" s="5"/>
       <c r="K264" s="2"/>
@@ -17567,7 +17567,7 @@
         <v>1346</v>
       </c>
       <c r="I265" s="5" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="J265" s="5"/>
       <c r="K265" s="2"/>
@@ -17596,7 +17596,7 @@
         <v>1348</v>
       </c>
       <c r="I266" s="5" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="J266" s="5"/>
       <c r="K266" s="2"/>
@@ -17625,7 +17625,7 @@
         <v>1350</v>
       </c>
       <c r="I267" s="5" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="J267" s="5"/>
       <c r="K267" s="2"/>
@@ -17684,7 +17684,7 @@
       </c>
       <c r="I269" s="5"/>
       <c r="J269" s="5" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="K269" s="2"/>
       <c r="L269" s="2"/>
@@ -17795,7 +17795,7 @@
         <v>1363</v>
       </c>
       <c r="I273" s="5" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="J273" s="5"/>
       <c r="K273" s="2"/>
@@ -17824,10 +17824,10 @@
         <v>1365</v>
       </c>
       <c r="I274" s="5" t="s">
+        <v>2243</v>
+      </c>
+      <c r="J274" s="5" t="s">
         <v>2244</v>
-      </c>
-      <c r="J274" s="5" t="s">
-        <v>2245</v>
       </c>
       <c r="K274" s="2"/>
       <c r="L274" s="2"/>
@@ -17857,7 +17857,7 @@
         <v>1367</v>
       </c>
       <c r="I275" s="5" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="J275" s="5"/>
       <c r="K275" s="2"/>
@@ -17886,10 +17886,10 @@
         <v>1369</v>
       </c>
       <c r="I276" s="5" t="s">
+        <v>2246</v>
+      </c>
+      <c r="J276" s="5" t="s">
         <v>2247</v>
-      </c>
-      <c r="J276" s="5" t="s">
-        <v>2248</v>
       </c>
       <c r="K276" s="2"/>
       <c r="L276" s="2"/>
@@ -18129,7 +18129,7 @@
         <v>1379</v>
       </c>
       <c r="I285" s="5" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="J285" s="5"/>
       <c r="K285" s="2"/>
@@ -18212,7 +18212,7 @@
         <v>1385</v>
       </c>
       <c r="I288" s="5" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="J288" s="5"/>
       <c r="K288" s="2"/>
@@ -18243,7 +18243,7 @@
         <v>1388</v>
       </c>
       <c r="I289" s="5" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="J289" s="5"/>
       <c r="K289" s="2"/>
@@ -18376,7 +18376,7 @@
         <v>1395</v>
       </c>
       <c r="I294" s="5" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="J294" s="5"/>
       <c r="K294" s="2"/>
@@ -18434,7 +18434,7 @@
         <v>1398</v>
       </c>
       <c r="I296" s="5" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="J296" s="5"/>
       <c r="K296" s="2"/>
@@ -18463,7 +18463,7 @@
         <v>1400</v>
       </c>
       <c r="I297" s="5" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="J297" s="5"/>
       <c r="K297" s="2"/>
@@ -18492,7 +18492,7 @@
         <v>1116</v>
       </c>
       <c r="I298" s="5" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
       <c r="J298" s="5"/>
       <c r="K298" s="2"/>
@@ -18521,7 +18521,7 @@
         <v>1223</v>
       </c>
       <c r="I299" s="5" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="J299" s="5"/>
       <c r="K299" s="2"/>
@@ -18550,7 +18550,7 @@
         <v>1404</v>
       </c>
       <c r="I300" s="5" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="J300" s="5"/>
       <c r="K300" s="2"/>
@@ -18583,7 +18583,7 @@
         <v>1407</v>
       </c>
       <c r="I301" s="5" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="J301" s="5"/>
       <c r="K301" s="2"/>
@@ -18614,7 +18614,7 @@
         <v>1410</v>
       </c>
       <c r="I302" s="5" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="J302" s="5"/>
       <c r="K302" s="2"/>
@@ -18672,7 +18672,7 @@
         <v>1414</v>
       </c>
       <c r="I304" s="5" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="J304" s="5"/>
       <c r="K304" s="2"/>
@@ -18728,7 +18728,7 @@
         <v>1418</v>
       </c>
       <c r="I306" s="5" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="J306" s="5"/>
       <c r="K306" s="2"/>
@@ -18784,10 +18784,10 @@
       <c r="G308" s="2"/>
       <c r="H308" s="2"/>
       <c r="I308" s="5" t="s">
+        <v>2261</v>
+      </c>
+      <c r="J308" s="5" t="s">
         <v>2262</v>
-      </c>
-      <c r="J308" s="5" t="s">
-        <v>2263</v>
       </c>
       <c r="K308" s="2"/>
       <c r="L308" s="2"/>
@@ -18817,7 +18817,7 @@
         <v>1423</v>
       </c>
       <c r="I309" s="5" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="J309" s="5"/>
       <c r="K309" s="2"/>
@@ -18846,7 +18846,7 @@
         <v>1425</v>
       </c>
       <c r="I310" s="5" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="J310" s="5"/>
       <c r="K310" s="2"/>
@@ -18902,7 +18902,7 @@
         <v>1428</v>
       </c>
       <c r="I312" s="5" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="J312" s="5"/>
       <c r="K312" s="2"/>
@@ -18929,7 +18929,7 @@
       <c r="G313" s="2"/>
       <c r="H313" s="2"/>
       <c r="I313" s="5" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="J313" s="5"/>
       <c r="K313" s="2"/>
@@ -18956,10 +18956,10 @@
       <c r="G314" s="2"/>
       <c r="H314" s="2"/>
       <c r="I314" s="5" t="s">
+        <v>2267</v>
+      </c>
+      <c r="J314" s="5" t="s">
         <v>2268</v>
-      </c>
-      <c r="J314" s="5" t="s">
-        <v>2269</v>
       </c>
       <c r="K314" s="2"/>
       <c r="L314" s="2"/>
@@ -18989,7 +18989,7 @@
         <v>1431</v>
       </c>
       <c r="I315" s="5" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="J315" s="5"/>
       <c r="K315" s="2"/>
@@ -19020,7 +19020,7 @@
         <v>1434</v>
       </c>
       <c r="I316" s="5" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="J316" s="5"/>
       <c r="K316" s="2"/>
@@ -19074,7 +19074,7 @@
         <v>1436</v>
       </c>
       <c r="I318" s="5" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="J318" s="5"/>
       <c r="K318" s="2"/>
@@ -19105,7 +19105,7 @@
         <v>510</v>
       </c>
       <c r="I319" s="5" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="J319" s="5"/>
       <c r="K319" s="2"/>
@@ -19188,7 +19188,7 @@
       <c r="G322" s="2"/>
       <c r="H322" s="2"/>
       <c r="I322" s="5" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="J322" s="5"/>
       <c r="K322" s="2"/>
@@ -19219,7 +19219,7 @@
         <v>1049</v>
       </c>
       <c r="I323" s="5" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="J323" s="5"/>
       <c r="K323" s="2"/>
@@ -19248,7 +19248,7 @@
         <v>1445</v>
       </c>
       <c r="I324" s="5" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="J324" s="5"/>
       <c r="K324" s="2"/>
@@ -19277,10 +19277,10 @@
         <v>1447</v>
       </c>
       <c r="I325" s="5" t="s">
+        <v>2276</v>
+      </c>
+      <c r="J325" s="9" t="s">
         <v>2277</v>
-      </c>
-      <c r="J325" s="9" t="s">
-        <v>2278</v>
       </c>
       <c r="K325" s="2"/>
       <c r="L325" s="2"/>
@@ -19426,7 +19426,7 @@
         <v>1434</v>
       </c>
       <c r="I330" s="5" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="J330" s="5"/>
       <c r="K330" s="2"/>
@@ -19480,7 +19480,7 @@
         <v>1456</v>
       </c>
       <c r="I332" s="5" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="J332" s="5"/>
       <c r="K332" s="2"/>
@@ -19509,7 +19509,7 @@
         <v>1458</v>
       </c>
       <c r="I333" s="5" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="J333" s="5"/>
       <c r="K333" s="2"/>
@@ -19538,10 +19538,10 @@
         <v>1460</v>
       </c>
       <c r="I334" s="5" t="s">
+        <v>2280</v>
+      </c>
+      <c r="J334" s="5" t="s">
         <v>2281</v>
-      </c>
-      <c r="J334" s="5" t="s">
-        <v>2282</v>
       </c>
       <c r="K334" s="2"/>
       <c r="L334" s="2"/>
@@ -19569,7 +19569,7 @@
         <v>1462</v>
       </c>
       <c r="I335" s="5" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="J335" s="5"/>
       <c r="K335" s="2"/>
@@ -19598,10 +19598,10 @@
         <v>1464</v>
       </c>
       <c r="I336" s="5" t="s">
+        <v>2283</v>
+      </c>
+      <c r="J336" s="9" t="s">
         <v>2284</v>
-      </c>
-      <c r="J336" s="9" t="s">
-        <v>2285</v>
       </c>
       <c r="K336" s="2"/>
       <c r="L336" s="2"/>
@@ -19710,7 +19710,7 @@
         <v>1471</v>
       </c>
       <c r="I340" s="5" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="J340" s="5"/>
       <c r="K340" s="2"/>
@@ -19739,7 +19739,7 @@
         <v>1473</v>
       </c>
       <c r="I341" s="5" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="J341" s="5"/>
       <c r="K341" s="2"/>
@@ -19771,7 +19771,7 @@
       </c>
       <c r="I342" s="5"/>
       <c r="J342" s="5" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="K342" s="2"/>
       <c r="L342" s="2"/>
@@ -19826,7 +19826,7 @@
         <v>1478</v>
       </c>
       <c r="I344" s="5" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="J344" s="5"/>
       <c r="K344" s="2"/>
@@ -19936,10 +19936,10 @@
         <v>1485</v>
       </c>
       <c r="I348" s="5" t="s">
+        <v>2289</v>
+      </c>
+      <c r="J348" s="5" t="s">
         <v>2290</v>
-      </c>
-      <c r="J348" s="5" t="s">
-        <v>2291</v>
       </c>
       <c r="K348" s="2"/>
       <c r="L348" s="2"/>
@@ -19968,7 +19968,7 @@
       </c>
       <c r="I349" s="5"/>
       <c r="J349" s="5" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="K349" s="2"/>
       <c r="L349" s="2"/>
@@ -20052,7 +20052,7 @@
         <v>1492</v>
       </c>
       <c r="I352" s="5" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="J352" s="5"/>
       <c r="K352" s="2"/>
@@ -20083,7 +20083,7 @@
         <v>1494</v>
       </c>
       <c r="I353" s="5" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="J353" s="5"/>
       <c r="K353" s="2"/>
@@ -20168,7 +20168,7 @@
         <v>1499</v>
       </c>
       <c r="I356" s="5" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="J356" s="5"/>
       <c r="K356" s="2"/>
@@ -20197,7 +20197,7 @@
       <c r="G357" s="2"/>
       <c r="H357" s="2"/>
       <c r="I357" s="5" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="J357" s="5"/>
       <c r="K357" s="2"/>
@@ -20337,7 +20337,7 @@
       </c>
       <c r="I362" s="5"/>
       <c r="J362" s="5" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="K362" s="2"/>
       <c r="L362" s="2"/>
@@ -20365,7 +20365,7 @@
       <c r="G363" s="2"/>
       <c r="H363" s="2"/>
       <c r="I363" s="5" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="J363" s="5"/>
       <c r="K363" s="2"/>
@@ -20394,7 +20394,7 @@
         <v>1513</v>
       </c>
       <c r="I364" s="5" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="J364" s="5"/>
       <c r="K364" s="2"/>
@@ -20448,7 +20448,7 @@
         <v>1515</v>
       </c>
       <c r="I366" s="5" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="J366" s="5"/>
       <c r="K366" s="2"/>
@@ -20558,7 +20558,7 @@
         <v>1520</v>
       </c>
       <c r="I370" s="5" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="J370" s="5"/>
       <c r="K370" s="2"/>
@@ -20587,7 +20587,7 @@
         <v>1522</v>
       </c>
       <c r="I371" s="5" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="J371" s="5"/>
       <c r="K371" s="2"/>
@@ -20672,7 +20672,7 @@
       <c r="G374" s="2"/>
       <c r="H374" s="2"/>
       <c r="I374" s="5" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="J374" s="5"/>
       <c r="K374" s="2"/>
@@ -20701,7 +20701,7 @@
         <v>1530</v>
       </c>
       <c r="I375" s="5" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="J375" s="5"/>
       <c r="K375" s="2"/>
@@ -20838,7 +20838,7 @@
         <v>1536</v>
       </c>
       <c r="I380" s="5" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="J380" s="5"/>
       <c r="K380" s="2"/>
@@ -20870,7 +20870,7 @@
       </c>
       <c r="I381" s="5"/>
       <c r="J381" s="5" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="K381" s="2"/>
       <c r="L381" s="2"/>
@@ -20898,7 +20898,7 @@
         <v>1539</v>
       </c>
       <c r="I382" s="5" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="J382" s="5"/>
       <c r="K382" s="2"/>
@@ -20929,7 +20929,7 @@
         <v>1541</v>
       </c>
       <c r="I383" s="5" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="J383" s="5"/>
       <c r="K383" s="2"/>
@@ -21014,7 +21014,7 @@
         <v>1547</v>
       </c>
       <c r="I386" s="5" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="J386" s="5"/>
       <c r="K386" s="2"/>
@@ -21043,7 +21043,7 @@
         <v>1549</v>
       </c>
       <c r="I387" s="5" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="J387" s="5"/>
       <c r="K387" s="2"/>
@@ -21074,7 +21074,7 @@
         <v>1551</v>
       </c>
       <c r="I388" s="5" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="J388" s="5"/>
       <c r="K388" s="2"/>
@@ -21105,7 +21105,7 @@
         <v>1554</v>
       </c>
       <c r="I389" s="5" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="J389" s="5"/>
       <c r="K389" s="2"/>
@@ -21134,7 +21134,7 @@
         <v>1556</v>
       </c>
       <c r="I390" s="5" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="J390" s="5"/>
       <c r="K390" s="2"/>
@@ -21165,7 +21165,7 @@
         <v>588</v>
       </c>
       <c r="I391" s="5" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="J391" s="5"/>
       <c r="K391" s="2"/>
@@ -21221,7 +21221,7 @@
         <v>1561</v>
       </c>
       <c r="I393" s="5" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="J393" s="5"/>
       <c r="K393" s="2"/>
@@ -21306,7 +21306,7 @@
         <v>1567</v>
       </c>
       <c r="I396" s="5" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="J396" s="5"/>
       <c r="K396" s="2"/>
@@ -21393,7 +21393,7 @@
         <v>1574</v>
       </c>
       <c r="I399" s="5" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="J399" s="5"/>
       <c r="K399" s="2"/>
@@ -21534,7 +21534,7 @@
         <v>1583</v>
       </c>
       <c r="I404" s="5" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="J404" s="5"/>
       <c r="K404" s="2"/>
@@ -21625,7 +21625,7 @@
         <v>1589</v>
       </c>
       <c r="I407" s="5" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="J407" s="5"/>
       <c r="K407" s="2"/>
@@ -21681,7 +21681,7 @@
         <v>1592</v>
       </c>
       <c r="I409" s="5" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="J409" s="5"/>
       <c r="K409" s="2"/>
@@ -21710,7 +21710,7 @@
       <c r="G410" s="2"/>
       <c r="H410" s="2"/>
       <c r="I410" s="5" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="J410" s="5"/>
       <c r="K410" s="2"/>
@@ -21739,7 +21739,7 @@
       <c r="G411" s="2"/>
       <c r="H411" s="2"/>
       <c r="I411" s="5" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="J411" s="5"/>
       <c r="K411" s="2"/>
@@ -21770,7 +21770,7 @@
         <v>1597</v>
       </c>
       <c r="I412" s="5" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="J412" s="5"/>
       <c r="K412" s="2" t="s">
@@ -21803,7 +21803,7 @@
         <v>1599</v>
       </c>
       <c r="I413" s="5" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
       <c r="J413" s="5"/>
       <c r="K413" s="2" t="s">
@@ -21861,7 +21861,7 @@
         <v>884</v>
       </c>
       <c r="I415" s="5" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="J415" s="5"/>
       <c r="K415" s="2"/>
@@ -21917,7 +21917,7 @@
         <v>1606</v>
       </c>
       <c r="I417" s="5" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="J417" s="5"/>
       <c r="K417" s="2"/>
@@ -22002,10 +22002,10 @@
         <v>710</v>
       </c>
       <c r="I420" s="5" t="s">
+        <v>2323</v>
+      </c>
+      <c r="J420" s="5" t="s">
         <v>2324</v>
-      </c>
-      <c r="J420" s="5" t="s">
-        <v>2325</v>
       </c>
       <c r="K420" s="2"/>
       <c r="L420" s="2"/>
@@ -22035,7 +22035,7 @@
         <v>1609</v>
       </c>
       <c r="I421" s="5" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
       <c r="J421" s="5"/>
       <c r="K421" s="2"/>
@@ -22064,7 +22064,7 @@
         <v>1611</v>
       </c>
       <c r="I422" s="5" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="J422" s="5"/>
       <c r="K422" s="2"/>
@@ -22120,7 +22120,7 @@
         <v>1613</v>
       </c>
       <c r="I424" s="5" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="J424" s="5"/>
       <c r="K424" s="2"/>
@@ -22149,7 +22149,7 @@
         <v>1615</v>
       </c>
       <c r="I425" s="5" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="J425" s="5"/>
       <c r="K425" s="2"/>
@@ -22178,7 +22178,7 @@
         <v>1617</v>
       </c>
       <c r="I426" s="5" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="J426" s="5"/>
       <c r="K426" s="2"/>
@@ -22207,7 +22207,7 @@
         <v>1619</v>
       </c>
       <c r="I427" s="5" t="s">
-        <v>2331</v>
+        <v>2330</v>
       </c>
       <c r="J427" s="5"/>
       <c r="K427" s="2"/>
@@ -22344,7 +22344,7 @@
       <c r="G432" s="2"/>
       <c r="H432" s="2"/>
       <c r="I432" s="5" t="s">
-        <v>2332</v>
+        <v>2331</v>
       </c>
       <c r="J432" s="5"/>
       <c r="K432" s="2"/>
@@ -22373,7 +22373,7 @@
       <c r="G433" s="2"/>
       <c r="H433" s="2"/>
       <c r="I433" s="5" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="J433" s="5"/>
       <c r="K433" s="2"/>
@@ -22427,7 +22427,7 @@
         <v>1569</v>
       </c>
       <c r="I435" s="5" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="J435" s="5"/>
       <c r="K435" s="2" t="s">
@@ -22456,7 +22456,7 @@
       <c r="G436" s="2"/>
       <c r="H436" s="2"/>
       <c r="I436" s="5" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="J436" s="5"/>
       <c r="K436" s="2"/>
@@ -22543,7 +22543,7 @@
         <v>284</v>
       </c>
       <c r="I439" s="5" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="J439" s="5"/>
       <c r="K439" s="2"/>
@@ -22570,7 +22570,7 @@
       <c r="G440" s="2"/>
       <c r="H440" s="2"/>
       <c r="I440" s="5" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
       <c r="J440" s="5"/>
       <c r="K440" s="2"/>
@@ -22678,7 +22678,7 @@
       <c r="G444" s="2"/>
       <c r="H444" s="2"/>
       <c r="I444" s="5" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="J444" s="5"/>
       <c r="K444" s="2"/>
@@ -22705,7 +22705,7 @@
       <c r="G445" s="2"/>
       <c r="H445" s="2"/>
       <c r="I445" s="5" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
       <c r="J445" s="5"/>
       <c r="K445" s="2"/>
@@ -22759,7 +22759,7 @@
       <c r="G447" s="2"/>
       <c r="H447" s="2"/>
       <c r="I447" s="5" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="J447" s="5"/>
       <c r="K447" s="2"/>
@@ -22843,7 +22843,7 @@
       </c>
       <c r="I450" s="5"/>
       <c r="J450" s="5" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="K450" s="2"/>
       <c r="L450" s="2"/>
@@ -22894,7 +22894,7 @@
       <c r="G452" s="2"/>
       <c r="H452" s="2"/>
       <c r="I452" s="5" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="J452" s="5"/>
       <c r="K452" s="2"/>
@@ -22952,7 +22952,7 @@
         <v>1651</v>
       </c>
       <c r="I454" s="5" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="J454" s="5"/>
       <c r="K454" s="2" t="s">
@@ -23006,7 +23006,7 @@
       <c r="G456" s="2"/>
       <c r="H456" s="2"/>
       <c r="I456" s="5" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="J456" s="5"/>
       <c r="K456" s="2"/>
@@ -23087,10 +23087,10 @@
         <v>1655</v>
       </c>
       <c r="I459" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="J459" s="5" t="s">
         <v>2345</v>
-      </c>
-      <c r="J459" s="5" t="s">
-        <v>2346</v>
       </c>
       <c r="K459" s="2"/>
       <c r="L459" s="2"/>
@@ -23143,7 +23143,7 @@
         <v>1660</v>
       </c>
       <c r="I461" s="5" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="J461" s="5"/>
       <c r="K461" s="2"/>
@@ -23172,7 +23172,7 @@
         <v>1662</v>
       </c>
       <c r="I462" s="5" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="J462" s="5"/>
       <c r="K462" s="2"/>
@@ -23203,7 +23203,7 @@
         <v>1664</v>
       </c>
       <c r="I463" s="5" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="J463" s="5"/>
       <c r="K463" s="2"/>
@@ -23311,7 +23311,7 @@
       <c r="G467" s="2"/>
       <c r="H467" s="2"/>
       <c r="I467" s="5" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="J467" s="5"/>
       <c r="K467" s="2"/>
@@ -23340,7 +23340,7 @@
         <v>521</v>
       </c>
       <c r="I468" s="5" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="J468" s="5"/>
       <c r="K468" s="2"/>
@@ -23423,7 +23423,7 @@
         <v>1672</v>
       </c>
       <c r="I471" s="5" t="s">
-        <v>2351</v>
+        <v>2350</v>
       </c>
       <c r="J471" s="5"/>
       <c r="K471" s="2"/>
@@ -23533,7 +23533,7 @@
         <v>1675</v>
       </c>
       <c r="I475" s="5" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="J475" s="5"/>
       <c r="K475" s="2"/>
@@ -23563,7 +23563,7 @@
       </c>
       <c r="I476" s="5"/>
       <c r="J476" s="5" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="K476" s="2"/>
       <c r="L476" s="2"/>
@@ -23699,7 +23699,7 @@
         <v>1686</v>
       </c>
       <c r="I481" s="5" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="J481" s="5"/>
       <c r="K481" s="2"/>
@@ -23730,7 +23730,7 @@
         <v>1688</v>
       </c>
       <c r="I482" s="5" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="J482" s="5"/>
       <c r="K482" s="2"/>
@@ -23761,7 +23761,7 @@
         <v>1690</v>
       </c>
       <c r="I483" s="5" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="J483" s="5"/>
       <c r="K483" s="2"/>
@@ -23817,7 +23817,7 @@
         <v>1660</v>
       </c>
       <c r="I485" s="5" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="J485" s="5"/>
       <c r="K485" s="2"/>
@@ -23846,7 +23846,7 @@
         <v>1694</v>
       </c>
       <c r="I486" s="5" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
       <c r="J486" s="5"/>
       <c r="K486" s="2"/>
@@ -23873,7 +23873,7 @@
       <c r="G487" s="2"/>
       <c r="H487" s="2"/>
       <c r="I487" s="5" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="J487" s="5"/>
       <c r="K487" s="2"/>
@@ -23929,7 +23929,7 @@
       <c r="G489" s="2"/>
       <c r="H489" s="2"/>
       <c r="I489" s="5" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="J489" s="5"/>
       <c r="K489" s="2"/>
@@ -23958,7 +23958,7 @@
         <v>1699</v>
       </c>
       <c r="I490" s="5" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="J490" s="5"/>
       <c r="K490" s="2"/>
@@ -24016,7 +24016,7 @@
         <v>1703</v>
       </c>
       <c r="I492" s="5" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="J492" s="5"/>
       <c r="K492" s="2"/>
@@ -24047,7 +24047,7 @@
         <v>1705</v>
       </c>
       <c r="I493" s="5" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="J493" s="5"/>
       <c r="K493" s="2"/>
@@ -24076,7 +24076,7 @@
         <v>1707</v>
       </c>
       <c r="I494" s="5" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="J494" s="5"/>
       <c r="K494" s="2"/>
@@ -24160,7 +24160,7 @@
       <c r="H497" s="2"/>
       <c r="I497" s="5"/>
       <c r="J497" s="5" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="K497" s="2"/>
       <c r="L497" s="2"/>
@@ -24215,7 +24215,7 @@
         <v>1716</v>
       </c>
       <c r="I499" s="5" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="J499" s="5"/>
       <c r="K499" s="2"/>
@@ -24244,7 +24244,7 @@
         <v>1086</v>
       </c>
       <c r="I500" s="5" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="J500" s="5"/>
       <c r="K500" s="2"/>
@@ -24273,7 +24273,7 @@
       <c r="G501" s="2"/>
       <c r="H501" s="2"/>
       <c r="I501" s="5" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="J501" s="5"/>
       <c r="K501" s="2"/>
@@ -24302,7 +24302,7 @@
         <v>1720</v>
       </c>
       <c r="I502" s="5" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="J502" s="5"/>
       <c r="K502" s="2"/>
@@ -24335,10 +24335,10 @@
         <v>1722</v>
       </c>
       <c r="I503" s="5" t="s">
+        <v>2369</v>
+      </c>
+      <c r="J503" s="5" t="s">
         <v>2370</v>
-      </c>
-      <c r="J503" s="5" t="s">
-        <v>2371</v>
       </c>
       <c r="K503" s="2" t="s">
         <v>556</v>
@@ -24366,7 +24366,7 @@
       <c r="G504" s="2"/>
       <c r="H504" s="2"/>
       <c r="I504" s="5" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="J504" s="5"/>
       <c r="K504" s="2"/>
@@ -24395,7 +24395,7 @@
         <v>1725</v>
       </c>
       <c r="I505" s="5" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="J505" s="5"/>
       <c r="K505" s="2"/>
@@ -24422,7 +24422,7 @@
       <c r="G506" s="2"/>
       <c r="H506" s="2"/>
       <c r="I506" s="5" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="J506" s="5"/>
       <c r="K506" s="2"/>
@@ -24451,7 +24451,7 @@
         <v>521</v>
       </c>
       <c r="I507" s="5" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="J507" s="5"/>
       <c r="K507" s="2"/>
@@ -24479,7 +24479,7 @@
       <c r="H508" s="2"/>
       <c r="I508" s="5"/>
       <c r="J508" s="5" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="K508" s="2"/>
       <c r="L508" s="2"/>
@@ -24509,7 +24509,7 @@
         <v>1730</v>
       </c>
       <c r="I509" s="5" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="J509" s="5"/>
       <c r="K509" s="2"/>
@@ -24538,7 +24538,7 @@
       <c r="G510" s="2"/>
       <c r="H510" s="2"/>
       <c r="I510" s="5" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="J510" s="5"/>
       <c r="K510" s="2"/>
@@ -24569,7 +24569,7 @@
         <v>1733</v>
       </c>
       <c r="I511" s="5" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="J511" s="10"/>
       <c r="K511" s="2"/>
@@ -24623,7 +24623,7 @@
       <c r="G513" s="2"/>
       <c r="H513" s="2"/>
       <c r="I513" s="5" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="J513" s="11"/>
       <c r="K513" s="2"/>
@@ -24727,7 +24727,7 @@
         <v>1740</v>
       </c>
       <c r="I517" s="5" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="J517" s="5"/>
       <c r="K517" s="2"/>
@@ -24812,7 +24812,7 @@
         <v>1746</v>
       </c>
       <c r="I520" s="5" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="J520" s="5"/>
       <c r="K520" s="2"/>
@@ -24841,7 +24841,7 @@
         <v>1748</v>
       </c>
       <c r="I521" s="5" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="J521" s="5"/>
       <c r="K521" s="2"/>
@@ -24868,10 +24868,10 @@
       <c r="G522" s="2"/>
       <c r="H522" s="2"/>
       <c r="I522" s="5" t="s">
+        <v>2383</v>
+      </c>
+      <c r="J522" s="5" t="s">
         <v>2384</v>
-      </c>
-      <c r="J522" s="5" t="s">
-        <v>2385</v>
       </c>
       <c r="K522" s="2"/>
       <c r="L522" s="2"/>
@@ -24902,7 +24902,7 @@
       </c>
       <c r="I523" s="5"/>
       <c r="J523" s="5" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="K523" s="2"/>
       <c r="L523" s="2"/>
@@ -24931,7 +24931,7 @@
       <c r="H524" s="2"/>
       <c r="I524" s="5"/>
       <c r="J524" s="5" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="K524" s="2"/>
       <c r="L524" s="2"/>
@@ -24986,7 +24986,7 @@
         <v>1756</v>
       </c>
       <c r="I526" s="5" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="J526" s="5"/>
       <c r="K526" s="2" t="s">
@@ -25017,7 +25017,7 @@
         <v>1758</v>
       </c>
       <c r="I527" s="5" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="J527" s="5"/>
       <c r="K527" s="2"/>
@@ -25069,7 +25069,7 @@
       <c r="G529" s="2"/>
       <c r="H529" s="2"/>
       <c r="I529" s="5" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="J529" s="5"/>
       <c r="K529" s="2"/>
@@ -25150,7 +25150,7 @@
       <c r="G532" s="2"/>
       <c r="H532" s="2"/>
       <c r="I532" s="5" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="J532" s="5"/>
       <c r="K532" s="2"/>
@@ -25177,7 +25177,7 @@
       <c r="G533" s="2"/>
       <c r="H533" s="2"/>
       <c r="I533" s="5" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="J533" s="5"/>
       <c r="K533" s="2"/>
@@ -25208,7 +25208,7 @@
         <v>1223</v>
       </c>
       <c r="I534" s="5" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="J534" s="5"/>
       <c r="K534" s="2"/>
@@ -25239,7 +25239,7 @@
         <v>1765</v>
       </c>
       <c r="I535" s="5" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="J535" s="5"/>
       <c r="K535" s="2"/>
@@ -25268,7 +25268,7 @@
       <c r="G536" s="2"/>
       <c r="H536" s="2"/>
       <c r="I536" s="5" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="J536" s="5"/>
       <c r="K536" s="2"/>
@@ -25297,7 +25297,7 @@
         <v>1768</v>
       </c>
       <c r="I537" s="5" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="J537" s="5"/>
       <c r="K537" s="2"/>
@@ -25326,7 +25326,7 @@
         <v>1770</v>
       </c>
       <c r="I538" s="5" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="J538" s="5"/>
       <c r="K538" s="2"/>
@@ -25355,7 +25355,7 @@
         <v>1772</v>
       </c>
       <c r="I539" s="5" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="J539" s="5"/>
       <c r="K539" s="2"/>
@@ -25440,7 +25440,7 @@
         <v>920</v>
       </c>
       <c r="I542" s="5" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="J542" s="5"/>
       <c r="K542" s="2"/>
@@ -25496,7 +25496,7 @@
         <v>1779</v>
       </c>
       <c r="I544" s="5" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="J544" s="5"/>
       <c r="K544" s="2"/>
@@ -25552,7 +25552,7 @@
         <v>1783</v>
       </c>
       <c r="I546" s="5" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="J546" s="5"/>
       <c r="K546" s="2"/>
@@ -25631,7 +25631,7 @@
       <c r="G549" s="2"/>
       <c r="H549" s="2"/>
       <c r="I549" s="5" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
       <c r="J549" s="5"/>
       <c r="K549" s="2"/>
@@ -25660,7 +25660,7 @@
         <v>284</v>
       </c>
       <c r="I550" s="5" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
       <c r="J550" s="5"/>
       <c r="K550" s="2"/>
@@ -25745,7 +25745,7 @@
         <v>1790</v>
       </c>
       <c r="I553" s="5" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
       <c r="J553" s="5"/>
       <c r="K553" s="2"/>
@@ -25776,7 +25776,7 @@
         <v>1541</v>
       </c>
       <c r="I554" s="5" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="J554" s="5"/>
       <c r="K554" s="2"/>
@@ -25832,7 +25832,7 @@
         <v>1794</v>
       </c>
       <c r="I556" s="5" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="J556" s="5"/>
       <c r="K556" s="2"/>
@@ -25859,7 +25859,7 @@
       <c r="G557" s="2"/>
       <c r="H557" s="2"/>
       <c r="I557" s="5" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="J557" s="5"/>
       <c r="K557" s="2"/>
@@ -25917,7 +25917,7 @@
         <v>521</v>
       </c>
       <c r="I559" s="5" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="J559" s="5"/>
       <c r="K559" s="2"/>
@@ -26000,7 +26000,7 @@
         <v>1801</v>
       </c>
       <c r="I562" s="5" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="J562" s="5"/>
       <c r="K562" s="2"/>
@@ -26058,7 +26058,7 @@
         <v>521</v>
       </c>
       <c r="I564" s="5" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="J564" s="5"/>
       <c r="K564" s="2"/>
@@ -26087,7 +26087,7 @@
         <v>1804</v>
       </c>
       <c r="I565" s="5" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="J565" s="5"/>
       <c r="K565" s="2"/>
@@ -26118,7 +26118,7 @@
         <v>1158</v>
       </c>
       <c r="I566" s="5" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="J566" s="5"/>
       <c r="K566" s="2"/>
@@ -26151,10 +26151,10 @@
         <v>1807</v>
       </c>
       <c r="I567" s="5" t="s">
+        <v>2411</v>
+      </c>
+      <c r="J567" s="5" t="s">
         <v>2412</v>
-      </c>
-      <c r="J567" s="5" t="s">
-        <v>2413</v>
       </c>
       <c r="K567" s="2"/>
       <c r="L567" s="2"/>
@@ -26236,7 +26236,7 @@
         <v>510</v>
       </c>
       <c r="I570" s="5" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
       <c r="J570" s="5"/>
       <c r="K570" s="2"/>
@@ -26317,7 +26317,7 @@
       <c r="G573" s="2"/>
       <c r="H573" s="2"/>
       <c r="I573" s="5" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
       <c r="J573" s="5"/>
       <c r="K573" s="2"/>
@@ -26400,10 +26400,10 @@
       <c r="G576" s="2"/>
       <c r="H576" s="2"/>
       <c r="I576" s="5" t="s">
+        <v>2415</v>
+      </c>
+      <c r="J576" s="5" t="s">
         <v>2416</v>
-      </c>
-      <c r="J576" s="5" t="s">
-        <v>2417</v>
       </c>
       <c r="K576" s="2"/>
       <c r="L576" s="2"/>
@@ -26431,7 +26431,7 @@
       <c r="G577" s="2"/>
       <c r="H577" s="2"/>
       <c r="I577" s="5" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="J577" s="5"/>
       <c r="K577" s="2" t="s">
@@ -26489,7 +26489,7 @@
         <v>1824</v>
       </c>
       <c r="I579" s="5" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="J579" s="5"/>
       <c r="K579" s="2"/>
@@ -26543,7 +26543,7 @@
         <v>1827</v>
       </c>
       <c r="I581" s="5" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="J581" s="5"/>
       <c r="K581" s="2"/>
@@ -26572,7 +26572,7 @@
         <v>1829</v>
       </c>
       <c r="I582" s="5" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="J582" s="5"/>
       <c r="K582" s="2"/>
@@ -26601,7 +26601,7 @@
         <v>1831</v>
       </c>
       <c r="I583" s="5" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="J583" s="5"/>
       <c r="K583" s="2"/>
@@ -26630,7 +26630,7 @@
         <v>521</v>
       </c>
       <c r="I584" s="5" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="J584" s="5"/>
       <c r="K584" s="2"/>
@@ -26715,7 +26715,7 @@
         <v>1086</v>
       </c>
       <c r="I587" s="5" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="J587" s="5"/>
       <c r="K587" s="2"/>
@@ -26744,11 +26744,11 @@
       <c r="G588" s="2"/>
       <c r="H588" s="2"/>
       <c r="I588" s="5" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="J588" s="5"/>
       <c r="K588" s="2" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
       <c r="L588" s="2"/>
       <c r="M588" s="2"/>
@@ -26775,7 +26775,7 @@
         <v>1838</v>
       </c>
       <c r="I589" s="5" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="J589" s="5"/>
       <c r="K589" s="2"/>
@@ -26802,10 +26802,10 @@
       <c r="G590" s="2"/>
       <c r="H590" s="2"/>
       <c r="I590" s="5" t="s">
+        <v>2426</v>
+      </c>
+      <c r="J590" s="5" t="s">
         <v>2427</v>
-      </c>
-      <c r="J590" s="5" t="s">
-        <v>2428</v>
       </c>
       <c r="K590" s="2"/>
       <c r="L590" s="2"/>
@@ -26833,7 +26833,7 @@
       <c r="G591" s="2"/>
       <c r="H591" s="2"/>
       <c r="I591" s="5" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="J591" s="5"/>
       <c r="K591" s="2"/>
@@ -26860,7 +26860,7 @@
       <c r="G592" s="2"/>
       <c r="H592" s="2"/>
       <c r="I592" s="5" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="J592" s="5"/>
       <c r="K592" s="2"/>
@@ -26889,7 +26889,7 @@
         <v>375</v>
       </c>
       <c r="I593" s="5" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="J593" s="5"/>
       <c r="K593" s="2"/>
@@ -26918,7 +26918,7 @@
         <v>1844</v>
       </c>
       <c r="I594" s="5" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="J594" s="5"/>
       <c r="K594" s="2"/>
@@ -26945,7 +26945,7 @@
       <c r="G595" s="2"/>
       <c r="H595" s="2"/>
       <c r="I595" s="5" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="J595" s="5"/>
       <c r="K595" s="2"/>
@@ -27051,7 +27051,7 @@
         <v>1850</v>
       </c>
       <c r="I599" s="5" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="J599" s="5"/>
       <c r="K599" s="2"/>
@@ -27080,7 +27080,7 @@
         <v>1852</v>
       </c>
       <c r="I600" s="5" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="J600" s="5"/>
       <c r="K600" s="2"/>
@@ -27107,7 +27107,7 @@
       <c r="G601" s="2"/>
       <c r="H601" s="2"/>
       <c r="I601" s="5" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="J601" s="5"/>
       <c r="K601" s="2"/>
@@ -27163,7 +27163,7 @@
         <v>1725</v>
       </c>
       <c r="I603" s="5" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
       <c r="J603" s="5"/>
       <c r="K603" s="2"/>
@@ -27219,7 +27219,7 @@
         <v>1860</v>
       </c>
       <c r="I605" s="5" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="J605" s="5"/>
       <c r="K605" s="2"/>
@@ -27250,7 +27250,7 @@
         <v>911</v>
       </c>
       <c r="I606" s="5" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="J606" s="5"/>
       <c r="K606" s="2"/>
@@ -27306,10 +27306,10 @@
       <c r="G608" s="2"/>
       <c r="H608" s="2"/>
       <c r="I608" s="5" t="s">
+        <v>2439</v>
+      </c>
+      <c r="J608" s="5" t="s">
         <v>2440</v>
-      </c>
-      <c r="J608" s="5" t="s">
-        <v>2441</v>
       </c>
       <c r="K608" s="2"/>
       <c r="L608" s="2"/>
@@ -27339,7 +27339,7 @@
         <v>1855</v>
       </c>
       <c r="I609" s="5" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="J609" s="5"/>
       <c r="K609" s="2"/>
@@ -27422,7 +27422,7 @@
         <v>1870</v>
       </c>
       <c r="I612" s="5" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="J612" s="5"/>
       <c r="K612" s="2"/>
@@ -27451,7 +27451,7 @@
         <v>1872</v>
       </c>
       <c r="I613" s="5" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="J613" s="5"/>
       <c r="K613" s="2"/>
@@ -27478,7 +27478,7 @@
       <c r="G614" s="2"/>
       <c r="H614" s="2"/>
       <c r="I614" s="5" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="J614" s="5"/>
       <c r="K614" s="2"/>
@@ -27536,7 +27536,7 @@
         <v>1876</v>
       </c>
       <c r="I616" s="5" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="J616" s="5"/>
       <c r="K616" s="2"/>
@@ -27592,7 +27592,7 @@
         <v>1880</v>
       </c>
       <c r="I618" s="5" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="J618" s="5"/>
       <c r="K618" s="2"/>
@@ -27621,10 +27621,10 @@
         <v>1074</v>
       </c>
       <c r="I619" s="5" t="s">
+        <v>2447</v>
+      </c>
+      <c r="J619" s="5" t="s">
         <v>2448</v>
-      </c>
-      <c r="J619" s="5" t="s">
-        <v>2449</v>
       </c>
       <c r="K619" s="2"/>
       <c r="L619" s="2"/>
@@ -27677,7 +27677,7 @@
       <c r="G621" s="2"/>
       <c r="H621" s="2"/>
       <c r="I621" s="5" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="J621" s="5"/>
       <c r="K621" s="2"/>
@@ -27735,7 +27735,7 @@
         <v>1885</v>
       </c>
       <c r="I623" s="5" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="J623" s="5"/>
       <c r="K623" s="2"/>
@@ -27824,7 +27824,7 @@
         <v>1086</v>
       </c>
       <c r="I626" s="5" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="J626" s="5"/>
       <c r="K626" s="2"/>
@@ -27884,10 +27884,10 @@
         <v>1888</v>
       </c>
       <c r="I628" s="5" t="s">
+        <v>2452</v>
+      </c>
+      <c r="J628" s="5" t="s">
         <v>2453</v>
-      </c>
-      <c r="J628" s="5" t="s">
-        <v>2454</v>
       </c>
       <c r="K628" s="2" t="s">
         <v>1086</v>
@@ -27915,7 +27915,7 @@
       <c r="G629" s="2"/>
       <c r="H629" s="2"/>
       <c r="I629" s="5" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="J629" s="5"/>
       <c r="K629" s="2"/>
@@ -27944,7 +27944,7 @@
         <v>1894</v>
       </c>
       <c r="I630" s="5" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="J630" s="5"/>
       <c r="K630" s="2"/>
@@ -28106,10 +28106,10 @@
         <v>1086</v>
       </c>
       <c r="I636" s="5" t="s">
+        <v>2456</v>
+      </c>
+      <c r="J636" s="5" t="s">
         <v>2457</v>
-      </c>
-      <c r="J636" s="5" t="s">
-        <v>2458</v>
       </c>
       <c r="K636" s="2"/>
       <c r="L636" s="2"/>
@@ -28164,10 +28164,10 @@
         <v>1686</v>
       </c>
       <c r="I638" s="5" t="s">
+        <v>2458</v>
+      </c>
+      <c r="J638" s="5" t="s">
         <v>2459</v>
-      </c>
-      <c r="J638" s="5" t="s">
-        <v>2460</v>
       </c>
       <c r="K638" s="2"/>
       <c r="L638" s="2"/>
@@ -28195,10 +28195,10 @@
         <v>1906</v>
       </c>
       <c r="I639" s="5" t="s">
+        <v>2460</v>
+      </c>
+      <c r="J639" s="5" t="s">
         <v>2461</v>
-      </c>
-      <c r="J639" s="5" t="s">
-        <v>2462</v>
       </c>
       <c r="K639" s="2"/>
       <c r="L639" s="2"/>
@@ -28253,10 +28253,10 @@
         <v>1909</v>
       </c>
       <c r="I641" s="5" t="s">
+        <v>2462</v>
+      </c>
+      <c r="J641" s="5" t="s">
         <v>2463</v>
-      </c>
-      <c r="J641" s="5" t="s">
-        <v>2464</v>
       </c>
       <c r="K641" s="2"/>
       <c r="L641" s="2"/>
@@ -28390,7 +28390,7 @@
       <c r="G646" s="2"/>
       <c r="H646" s="2"/>
       <c r="I646" s="5" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
       <c r="J646" s="5"/>
       <c r="K646" s="2"/>
@@ -28450,7 +28450,7 @@
         <v>1316</v>
       </c>
       <c r="I648" s="5" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="J648" s="5"/>
       <c r="K648" s="2"/>
@@ -28477,7 +28477,7 @@
       <c r="G649" s="2"/>
       <c r="H649" s="2"/>
       <c r="I649" s="5" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="J649" s="5"/>
       <c r="K649" s="2"/>
@@ -28508,11 +28508,11 @@
         <v>1920</v>
       </c>
       <c r="I650" s="5" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="J650" s="5"/>
       <c r="K650" s="2" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="L650" s="2"/>
       <c r="M650" s="2"/>
@@ -28537,7 +28537,7 @@
       <c r="G651" s="2"/>
       <c r="H651" s="2"/>
       <c r="I651" s="5" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="J651" s="5"/>
       <c r="K651" s="2"/>
@@ -28564,7 +28564,7 @@
       <c r="G652" s="2"/>
       <c r="H652" s="2"/>
       <c r="I652" s="5" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="J652" s="5"/>
       <c r="K652" s="2"/>
@@ -28593,7 +28593,7 @@
       <c r="G653" s="2"/>
       <c r="H653" s="2"/>
       <c r="I653" s="5" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="J653" s="5"/>
       <c r="K653" s="2"/>
@@ -28701,7 +28701,7 @@
       <c r="G657" s="2"/>
       <c r="H657" s="2"/>
       <c r="I657" s="5" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="J657" s="5"/>
       <c r="K657" s="2"/>
@@ -28728,7 +28728,7 @@
       <c r="G658" s="2"/>
       <c r="H658" s="2"/>
       <c r="I658" s="5" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="J658" s="5"/>
       <c r="K658" s="2"/>
@@ -28815,7 +28815,7 @@
         <v>875</v>
       </c>
       <c r="I661" s="5" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
       <c r="J661" s="5"/>
       <c r="K661" s="2"/>
@@ -28898,7 +28898,7 @@
       <c r="G664" s="2"/>
       <c r="H664" s="2"/>
       <c r="I664" s="5" t="s">
-        <v>2474</v>
+        <v>2473</v>
       </c>
       <c r="J664" s="5"/>
       <c r="K664" s="2"/>
@@ -29060,7 +29060,7 @@
         <v>1949</v>
       </c>
       <c r="I670" s="5" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="J670" s="5"/>
       <c r="K670" s="2"/>
@@ -29089,7 +29089,7 @@
         <v>1951</v>
       </c>
       <c r="I671" s="5" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="J671" s="5"/>
       <c r="K671" s="2"/>
@@ -29118,7 +29118,7 @@
         <v>1794</v>
       </c>
       <c r="I672" s="5" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="J672" s="5"/>
       <c r="K672" s="2"/>
@@ -29147,7 +29147,7 @@
         <v>1954</v>
       </c>
       <c r="I673" s="5" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="J673" s="5"/>
       <c r="K673" s="2"/>
@@ -29203,7 +29203,7 @@
         <v>1957</v>
       </c>
       <c r="I675" s="5" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="J675" s="5"/>
       <c r="K675" s="2"/>
@@ -29232,10 +29232,10 @@
         <v>1959</v>
       </c>
       <c r="I676" s="5" t="s">
+        <v>2479</v>
+      </c>
+      <c r="J676" s="5" t="s">
         <v>2480</v>
-      </c>
-      <c r="J676" s="5" t="s">
-        <v>2481</v>
       </c>
       <c r="K676" s="2"/>
       <c r="L676" s="2"/>
@@ -29319,7 +29319,7 @@
         <v>1965</v>
       </c>
       <c r="I679" s="5" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="J679" s="5"/>
       <c r="K679" s="2"/>
@@ -29348,7 +29348,7 @@
       <c r="G680" s="2"/>
       <c r="H680" s="2"/>
       <c r="I680" s="5" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="J680" s="5"/>
       <c r="K680" s="2"/>
@@ -29431,7 +29431,7 @@
         <v>1972</v>
       </c>
       <c r="I683" s="5" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="J683" s="5"/>
       <c r="K683" s="2"/>
@@ -29489,7 +29489,7 @@
         <v>1977</v>
       </c>
       <c r="I685" s="5" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="J685" s="5"/>
       <c r="K685" s="2"/>
@@ -29518,7 +29518,7 @@
         <v>1979</v>
       </c>
       <c r="I686" s="5" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="J686" s="5"/>
       <c r="K686" s="2"/>
@@ -29603,7 +29603,7 @@
       <c r="G689" s="2"/>
       <c r="H689" s="2"/>
       <c r="I689" s="5" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="J689" s="5"/>
       <c r="K689" s="2"/>
@@ -29630,7 +29630,7 @@
       <c r="G690" s="2"/>
       <c r="H690" s="2"/>
       <c r="I690" s="5" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="J690" s="5"/>
       <c r="K690" s="2"/>
@@ -29657,7 +29657,7 @@
       <c r="G691" s="2"/>
       <c r="H691" s="2"/>
       <c r="I691" s="5" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="J691" s="5"/>
       <c r="K691" s="2" t="s">
@@ -29688,10 +29688,10 @@
         <v>1987</v>
       </c>
       <c r="I692" s="5" t="s">
+        <v>2489</v>
+      </c>
+      <c r="J692" s="5" t="s">
         <v>2490</v>
-      </c>
-      <c r="J692" s="5" t="s">
-        <v>2491</v>
       </c>
       <c r="K692" s="2"/>
       <c r="L692" s="2"/>
@@ -29769,7 +29769,7 @@
       <c r="G695" s="2"/>
       <c r="H695" s="2"/>
       <c r="I695" s="5" t="s">
-        <v>2492</v>
+        <v>2491</v>
       </c>
       <c r="J695" s="5"/>
       <c r="K695" s="2"/>
@@ -29827,7 +29827,7 @@
         <v>1994</v>
       </c>
       <c r="I697" s="5" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="J697" s="5"/>
       <c r="K697" s="2"/>
@@ -29883,7 +29883,7 @@
         <v>1510</v>
       </c>
       <c r="I699" s="5" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="J699" s="5"/>
       <c r="K699" s="2"/>
@@ -29914,7 +29914,7 @@
         <v>1999</v>
       </c>
       <c r="I700" s="5" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
       <c r="J700" s="5"/>
       <c r="K700" s="2"/>
@@ -29945,7 +29945,7 @@
         <v>2001</v>
       </c>
       <c r="I701" s="5" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="J701" s="5"/>
       <c r="K701" s="2"/>
@@ -29974,7 +29974,7 @@
       <c r="G702" s="2"/>
       <c r="H702" s="2"/>
       <c r="I702" s="5" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="J702" s="5"/>
       <c r="K702" s="2" t="s">
@@ -30005,7 +30005,7 @@
       <c r="G703" s="2"/>
       <c r="H703" s="2"/>
       <c r="I703" s="5" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="J703" s="5"/>
       <c r="K703" s="2"/>
@@ -30034,7 +30034,7 @@
         <v>2005</v>
       </c>
       <c r="I704" s="5" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
       <c r="J704" s="5"/>
       <c r="K704" s="2"/>
@@ -30063,7 +30063,7 @@
         <v>2007</v>
       </c>
       <c r="I705" s="5" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="J705" s="5"/>
       <c r="K705" s="2"/>
@@ -30092,7 +30092,7 @@
       <c r="G706" s="2"/>
       <c r="H706" s="2"/>
       <c r="I706" s="5" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="J706" s="5"/>
       <c r="K706" s="2"/>
@@ -30119,7 +30119,7 @@
       <c r="G707" s="2"/>
       <c r="H707" s="2"/>
       <c r="I707" s="5" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="J707" s="5"/>
       <c r="K707" s="2"/>
@@ -30148,7 +30148,7 @@
         <v>2011</v>
       </c>
       <c r="I708" s="5" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="J708" s="5"/>
       <c r="K708" s="2"/>
@@ -30202,7 +30202,7 @@
       <c r="G710" s="2"/>
       <c r="H710" s="2"/>
       <c r="I710" s="5" t="s">
-        <v>2504</v>
+        <v>2503</v>
       </c>
       <c r="J710" s="5"/>
       <c r="K710" s="2"/>
@@ -30231,10 +30231,10 @@
         <v>375</v>
       </c>
       <c r="I711" s="5" t="s">
+        <v>2504</v>
+      </c>
+      <c r="J711" s="5" t="s">
         <v>2505</v>
-      </c>
-      <c r="J711" s="5" t="s">
-        <v>2506</v>
       </c>
       <c r="K711" s="2"/>
       <c r="L711" s="2"/>
@@ -30260,7 +30260,7 @@
       <c r="G712" s="2"/>
       <c r="H712" s="2"/>
       <c r="I712" s="5" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="J712" s="5"/>
       <c r="K712" s="2"/>
@@ -30320,7 +30320,7 @@
         <v>1725</v>
       </c>
       <c r="I714" s="5" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="J714" s="5"/>
       <c r="K714" s="2"/>
@@ -30351,7 +30351,7 @@
         <v>2019</v>
       </c>
       <c r="I715" s="5" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
       <c r="J715" s="5"/>
       <c r="K715" s="2"/>
@@ -30405,7 +30405,7 @@
         <v>2022</v>
       </c>
       <c r="I717" s="5" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="J717" s="5"/>
       <c r="K717" s="2"/>
@@ -30546,7 +30546,7 @@
       <c r="G722" s="2"/>
       <c r="H722" s="2"/>
       <c r="I722" s="5" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="J722" s="5"/>
       <c r="K722" s="2"/>
@@ -30762,7 +30762,7 @@
         <v>2040</v>
       </c>
       <c r="I730" s="5" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="J730" s="5"/>
       <c r="K730" s="2"/>
@@ -30791,7 +30791,7 @@
         <v>284</v>
       </c>
       <c r="I731" s="5" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="J731" s="5"/>
       <c r="K731" s="2"/>
@@ -30849,7 +30849,7 @@
         <v>2045</v>
       </c>
       <c r="I733" s="5" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="J733" s="5"/>
       <c r="K733" s="2"/>
@@ -30953,7 +30953,7 @@
         <v>2049</v>
       </c>
       <c r="I737" s="5" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="J737" s="5"/>
       <c r="K737" s="2"/>
@@ -31042,7 +31042,7 @@
         <v>1196</v>
       </c>
       <c r="I740" s="5" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="J740" s="5"/>
       <c r="K740" s="2" t="s">
@@ -31100,7 +31100,7 @@
         <v>2058</v>
       </c>
       <c r="I742" s="5" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="J742" s="5"/>
       <c r="K742" s="2"/>
@@ -31129,7 +31129,7 @@
         <v>2060</v>
       </c>
       <c r="I743" s="5" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="J743" s="5"/>
       <c r="K743" s="2"/>
@@ -31158,7 +31158,7 @@
         <v>2062</v>
       </c>
       <c r="I744" s="5" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
       <c r="J744" s="5"/>
       <c r="K744" s="2"/>
@@ -31243,7 +31243,7 @@
       <c r="G747" s="2"/>
       <c r="H747" s="2"/>
       <c r="I747" s="5" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="J747" s="5"/>
       <c r="K747" s="2"/>
@@ -31326,7 +31326,7 @@
       <c r="G750" s="2"/>
       <c r="H750" s="2"/>
       <c r="I750" s="5" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="J750" s="5"/>
       <c r="K750" s="2"/>
@@ -31492,7 +31492,7 @@
         <v>2079</v>
       </c>
       <c r="I756" s="5" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="J756" s="5"/>
       <c r="K756" s="2"/>
